--- a/resources/property classes.xlsx
+++ b/resources/property classes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mstern\Documents\GitHub\effective_property_tax\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmapil-my.sharepoint.com/personal/abahls_cmap_illinois_gov/Documents/Documents/github_repos/effective_property_tax/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A60A013-1040-4DEC-B76C-0C647DD12EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{2A60A013-1040-4DEC-B76C-0C647DD12EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF013571-E9D9-4AA3-8254-A6847BA48987}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17445" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cook" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="will" sheetId="7" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cook!$A$1:$F$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cook!$A$1:$G$150</definedName>
     <definedName name="Export_Output_2" localSheetId="0">Cook!$A$1:$E$134</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -1148,21 +1148,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1447,44 +1440,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G164"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G150"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="80.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="3" max="3" width="80.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="3" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="str">
+      <c r="B2" t="str">
         <f>TEXT(A2,"000")</f>
         <v>000</v>
       </c>
@@ -1504,11 +1497,11 @@
         <v>177</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>100</v>
       </c>
-      <c r="B3" s="4" t="str">
+      <c r="B3" t="str">
         <f t="shared" ref="B3:B66" si="0">TEXT(A3,"000")</f>
         <v>100</v>
       </c>
@@ -1524,15 +1517,15 @@
       <c r="F3">
         <v>0.1</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>190</v>
       </c>
-      <c r="B4" s="4" t="str">
+      <c r="B4" t="str">
         <f t="shared" si="0"/>
         <v>190</v>
       </c>
@@ -1548,15 +1541,15 @@
       <c r="F4">
         <v>0.1</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>200</v>
       </c>
-      <c r="B5" s="4" t="str">
+      <c r="B5" t="str">
         <f t="shared" si="0"/>
         <v>200</v>
       </c>
@@ -1572,15 +1565,15 @@
       <c r="F5">
         <v>0.1</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>201</v>
       </c>
-      <c r="B6" s="4" t="str">
+      <c r="B6" t="str">
         <f t="shared" si="0"/>
         <v>201</v>
       </c>
@@ -1596,15 +1589,15 @@
       <c r="F6">
         <v>0.1</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>202</v>
       </c>
-      <c r="B7" s="4" t="str">
+      <c r="B7" t="str">
         <f t="shared" si="0"/>
         <v>202</v>
       </c>
@@ -1620,15 +1613,15 @@
       <c r="F7">
         <v>0.1</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>203</v>
       </c>
-      <c r="B8" s="4" t="str">
+      <c r="B8" t="str">
         <f t="shared" si="0"/>
         <v>203</v>
       </c>
@@ -1644,15 +1637,15 @@
       <c r="F8">
         <v>0.1</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>204</v>
       </c>
-      <c r="B9" s="4" t="str">
+      <c r="B9" t="str">
         <f t="shared" si="0"/>
         <v>204</v>
       </c>
@@ -1668,15 +1661,15 @@
       <c r="F9">
         <v>0.1</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>205</v>
       </c>
-      <c r="B10" s="4" t="str">
+      <c r="B10" t="str">
         <f t="shared" si="0"/>
         <v>205</v>
       </c>
@@ -1692,15 +1685,15 @@
       <c r="F10">
         <v>0.1</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>206</v>
       </c>
-      <c r="B11" s="4" t="str">
+      <c r="B11" t="str">
         <f t="shared" si="0"/>
         <v>206</v>
       </c>
@@ -1716,15 +1709,15 @@
       <c r="F11">
         <v>0.1</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>207</v>
       </c>
-      <c r="B12" s="4" t="str">
+      <c r="B12" t="str">
         <f t="shared" si="0"/>
         <v>207</v>
       </c>
@@ -1740,15 +1733,15 @@
       <c r="F12">
         <v>0.1</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>208</v>
       </c>
-      <c r="B13" s="4" t="str">
+      <c r="B13" t="str">
         <f t="shared" si="0"/>
         <v>208</v>
       </c>
@@ -1764,15 +1757,15 @@
       <c r="F13">
         <v>0.1</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>209</v>
       </c>
-      <c r="B14" s="4" t="str">
+      <c r="B14" t="str">
         <f t="shared" si="0"/>
         <v>209</v>
       </c>
@@ -1788,15 +1781,15 @@
       <c r="F14">
         <v>0.1</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>210</v>
       </c>
-      <c r="B15" s="4" t="str">
+      <c r="B15" t="str">
         <f t="shared" si="0"/>
         <v>210</v>
       </c>
@@ -1812,15 +1805,15 @@
       <c r="F15">
         <v>0.1</v>
       </c>
-      <c r="G15" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>211</v>
       </c>
-      <c r="B16" s="4" t="str">
+      <c r="B16" t="str">
         <f t="shared" si="0"/>
         <v>211</v>
       </c>
@@ -1836,15 +1829,15 @@
       <c r="F16">
         <v>0.1</v>
       </c>
-      <c r="G16" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>212</v>
       </c>
-      <c r="B17" s="4" t="str">
+      <c r="B17" t="str">
         <f t="shared" si="0"/>
         <v>212</v>
       </c>
@@ -1860,15 +1853,15 @@
       <c r="F17">
         <v>0.1</v>
       </c>
-      <c r="G17" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>213</v>
       </c>
-      <c r="B18" s="4" t="str">
+      <c r="B18" t="str">
         <f t="shared" si="0"/>
         <v>213</v>
       </c>
@@ -1884,15 +1877,15 @@
       <c r="F18">
         <v>0.1</v>
       </c>
-      <c r="G18" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+      <c r="G18" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19">
         <v>218</v>
       </c>
-      <c r="B19" s="4" t="str">
+      <c r="B19" t="str">
         <f t="shared" si="0"/>
         <v>218</v>
       </c>
@@ -1908,15 +1901,15 @@
       <c r="F19">
         <v>0.1</v>
       </c>
-      <c r="G19" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+      <c r="G19" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20">
         <v>219</v>
       </c>
-      <c r="B20" s="4" t="str">
+      <c r="B20" t="str">
         <f t="shared" si="0"/>
         <v>219</v>
       </c>
@@ -1932,15 +1925,15 @@
       <c r="F20">
         <v>0.1</v>
       </c>
-      <c r="G20" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>224</v>
       </c>
-      <c r="B21" s="4" t="str">
+      <c r="B21" t="str">
         <f t="shared" si="0"/>
         <v>224</v>
       </c>
@@ -1956,15 +1949,15 @@
       <c r="F21">
         <v>0.1</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>225</v>
       </c>
-      <c r="B22" s="4" t="str">
+      <c r="B22" t="str">
         <f t="shared" si="0"/>
         <v>225</v>
       </c>
@@ -1980,15 +1973,15 @@
       <c r="F22">
         <v>0.1</v>
       </c>
-      <c r="G22" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G22" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>234</v>
       </c>
-      <c r="B23" s="4" t="str">
+      <c r="B23" t="str">
         <f t="shared" si="0"/>
         <v>234</v>
       </c>
@@ -2004,15 +1997,15 @@
       <c r="F23">
         <v>0.1</v>
       </c>
-      <c r="G23" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G23" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>239</v>
       </c>
-      <c r="B24" s="4" t="str">
+      <c r="B24" t="str">
         <f t="shared" si="0"/>
         <v>239</v>
       </c>
@@ -2028,15 +2021,15 @@
       <c r="F24">
         <v>0.1</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>241</v>
       </c>
-      <c r="B25" s="4" t="str">
+      <c r="B25" t="str">
         <f t="shared" si="0"/>
         <v>241</v>
       </c>
@@ -2052,15 +2045,15 @@
       <c r="F25">
         <v>0.1</v>
       </c>
-      <c r="G25" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G25" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>278</v>
       </c>
-      <c r="B26" s="4" t="str">
+      <c r="B26" t="str">
         <f t="shared" si="0"/>
         <v>278</v>
       </c>
@@ -2076,15 +2069,15 @@
       <c r="F26">
         <v>0.1</v>
       </c>
-      <c r="G26" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G26" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>288</v>
       </c>
-      <c r="B27" s="4" t="str">
+      <c r="B27" t="str">
         <f t="shared" si="0"/>
         <v>288</v>
       </c>
@@ -2100,15 +2093,15 @@
       <c r="F27">
         <v>0.1</v>
       </c>
-      <c r="G27" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G27" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>290</v>
       </c>
-      <c r="B28" s="4" t="str">
+      <c r="B28" t="str">
         <f t="shared" si="0"/>
         <v>290</v>
       </c>
@@ -2124,15 +2117,15 @@
       <c r="F28">
         <v>0.1</v>
       </c>
-      <c r="G28" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G28" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>295</v>
       </c>
-      <c r="B29" s="4" t="str">
+      <c r="B29" t="str">
         <f t="shared" si="0"/>
         <v>295</v>
       </c>
@@ -2148,15 +2141,15 @@
       <c r="F29">
         <v>0.1</v>
       </c>
-      <c r="G29" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G29" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>297</v>
       </c>
-      <c r="B30" s="4" t="str">
+      <c r="B30" t="str">
         <f t="shared" si="0"/>
         <v>297</v>
       </c>
@@ -2172,15 +2165,15 @@
       <c r="F30">
         <v>0.1</v>
       </c>
-      <c r="G30" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G30" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>299</v>
       </c>
-      <c r="B31" s="4" t="str">
+      <c r="B31" t="str">
         <f t="shared" si="0"/>
         <v>299</v>
       </c>
@@ -2196,15 +2189,15 @@
       <c r="F31">
         <v>0.1</v>
       </c>
-      <c r="G31" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+      <c r="G31" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32">
         <v>300</v>
       </c>
-      <c r="B32" s="4" t="str">
+      <c r="B32" t="str">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
@@ -2220,15 +2213,15 @@
       <c r="F32">
         <v>0.1</v>
       </c>
-      <c r="G32" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G32" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>301</v>
       </c>
-      <c r="B33" s="4" t="str">
+      <c r="B33" t="str">
         <f t="shared" si="0"/>
         <v>301</v>
       </c>
@@ -2244,15 +2237,15 @@
       <c r="F33">
         <v>0.1</v>
       </c>
-      <c r="G33" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G33" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>313</v>
       </c>
-      <c r="B34" s="4" t="str">
+      <c r="B34" t="str">
         <f t="shared" si="0"/>
         <v>313</v>
       </c>
@@ -2268,15 +2261,15 @@
       <c r="F34">
         <v>0.1</v>
       </c>
-      <c r="G34" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G34" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>314</v>
       </c>
-      <c r="B35" s="4" t="str">
+      <c r="B35" t="str">
         <f t="shared" si="0"/>
         <v>314</v>
       </c>
@@ -2292,15 +2285,15 @@
       <c r="F35">
         <v>0.1</v>
       </c>
-      <c r="G35" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G35" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>315</v>
       </c>
-      <c r="B36" s="4" t="str">
+      <c r="B36" t="str">
         <f t="shared" si="0"/>
         <v>315</v>
       </c>
@@ -2316,15 +2309,15 @@
       <c r="F36">
         <v>0.1</v>
       </c>
-      <c r="G36" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G36" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>318</v>
       </c>
-      <c r="B37" s="4" t="str">
+      <c r="B37" t="str">
         <f t="shared" si="0"/>
         <v>318</v>
       </c>
@@ -2340,15 +2333,15 @@
       <c r="F37">
         <v>0.1</v>
       </c>
-      <c r="G37" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
+      <c r="G37" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38">
         <v>319</v>
       </c>
-      <c r="B38" s="4" t="str">
+      <c r="B38" t="str">
         <f t="shared" si="0"/>
         <v>319</v>
       </c>
@@ -2364,15 +2357,15 @@
       <c r="F38">
         <v>0.1</v>
       </c>
-      <c r="G38" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G38" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>390</v>
       </c>
-      <c r="B39" s="4" t="str">
+      <c r="B39" t="str">
         <f t="shared" si="0"/>
         <v>390</v>
       </c>
@@ -2388,15 +2381,15 @@
       <c r="F39">
         <v>0.1</v>
       </c>
-      <c r="G39" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G39" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>391</v>
       </c>
-      <c r="B40" s="4" t="str">
+      <c r="B40" t="str">
         <f t="shared" si="0"/>
         <v>391</v>
       </c>
@@ -2412,15 +2405,15 @@
       <c r="F40">
         <v>0.1</v>
       </c>
-      <c r="G40" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G40" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>396</v>
       </c>
-      <c r="B41" s="4" t="str">
+      <c r="B41" t="str">
         <f t="shared" si="0"/>
         <v>396</v>
       </c>
@@ -2436,15 +2429,15 @@
       <c r="F41">
         <v>0.1</v>
       </c>
-      <c r="G41" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G41" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>397</v>
       </c>
-      <c r="B42" s="4" t="str">
+      <c r="B42" t="str">
         <f t="shared" si="0"/>
         <v>397</v>
       </c>
@@ -2460,15 +2453,15 @@
       <c r="F42">
         <v>0.1</v>
       </c>
-      <c r="G42" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G42" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>399</v>
       </c>
-      <c r="B43" s="4" t="str">
+      <c r="B43" t="str">
         <f t="shared" si="0"/>
         <v>399</v>
       </c>
@@ -2484,15 +2477,15 @@
       <c r="F43">
         <v>0.1</v>
       </c>
-      <c r="G43" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G43" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>401</v>
       </c>
-      <c r="B44" s="4" t="str">
+      <c r="B44" t="str">
         <f t="shared" si="0"/>
         <v>401</v>
       </c>
@@ -2508,15 +2501,15 @@
       <c r="F44">
         <v>0.2</v>
       </c>
-      <c r="G44" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G44" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>417</v>
       </c>
-      <c r="B45" s="4" t="str">
+      <c r="B45" t="str">
         <f t="shared" si="0"/>
         <v>417</v>
       </c>
@@ -2526,21 +2519,21 @@
       <c r="D45">
         <v>4</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="E45" t="s">
         <v>179</v>
       </c>
-      <c r="F45" s="4">
+      <c r="F45">
         <v>0.2</v>
       </c>
-      <c r="G45" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G45" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>418</v>
       </c>
-      <c r="B46" s="4" t="str">
+      <c r="B46" t="str">
         <f t="shared" si="0"/>
         <v>418</v>
       </c>
@@ -2550,21 +2543,21 @@
       <c r="D46">
         <v>4</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" t="s">
         <v>179</v>
       </c>
-      <c r="F46" s="4">
+      <c r="F46">
         <v>0.2</v>
       </c>
-      <c r="G46" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G46" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>422</v>
       </c>
-      <c r="B47" s="4" t="str">
+      <c r="B47" t="str">
         <f t="shared" si="0"/>
         <v>422</v>
       </c>
@@ -2574,21 +2567,21 @@
       <c r="D47">
         <v>4</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E47" t="s">
         <v>179</v>
       </c>
-      <c r="F47" s="4">
+      <c r="F47">
         <v>0.2</v>
       </c>
-      <c r="G47" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="1">
+      <c r="G47" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48">
         <v>427</v>
       </c>
-      <c r="B48" s="4" t="str">
+      <c r="B48" t="str">
         <f t="shared" si="0"/>
         <v>427</v>
       </c>
@@ -2598,21 +2591,21 @@
       <c r="D48">
         <v>4</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="E48" t="s">
         <v>179</v>
       </c>
-      <c r="F48" s="4">
+      <c r="F48">
         <v>0.2</v>
       </c>
-      <c r="G48" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G48" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>428</v>
       </c>
-      <c r="B49" s="4" t="str">
+      <c r="B49" t="str">
         <f t="shared" si="0"/>
         <v>428</v>
       </c>
@@ -2622,21 +2615,21 @@
       <c r="D49">
         <v>4</v>
       </c>
-      <c r="E49" s="4" t="s">
+      <c r="E49" t="s">
         <v>179</v>
       </c>
-      <c r="F49" s="4">
+      <c r="F49">
         <v>0.2</v>
       </c>
-      <c r="G49" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G49" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>430</v>
       </c>
-      <c r="B50" s="4" t="str">
+      <c r="B50" t="str">
         <f t="shared" si="0"/>
         <v>430</v>
       </c>
@@ -2646,21 +2639,21 @@
       <c r="D50">
         <v>4</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="E50" t="s">
         <v>179</v>
       </c>
-      <c r="F50" s="4">
+      <c r="F50">
         <v>0.2</v>
       </c>
-      <c r="G50" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G50" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>435</v>
       </c>
-      <c r="B51" s="4" t="str">
+      <c r="B51" t="str">
         <f t="shared" si="0"/>
         <v>435</v>
       </c>
@@ -2670,21 +2663,21 @@
       <c r="D51">
         <v>4</v>
       </c>
-      <c r="E51" s="4" t="s">
+      <c r="E51" t="s">
         <v>179</v>
       </c>
-      <c r="F51" s="4">
+      <c r="F51">
         <v>0.2</v>
       </c>
-      <c r="G51" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G51" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>480</v>
       </c>
-      <c r="B52" s="4" t="str">
+      <c r="B52" t="str">
         <f t="shared" si="0"/>
         <v>480</v>
       </c>
@@ -2694,21 +2687,21 @@
       <c r="D52">
         <v>4</v>
       </c>
-      <c r="E52" s="4" t="s">
+      <c r="E52" t="s">
         <v>179</v>
       </c>
-      <c r="F52" s="4">
+      <c r="F52">
         <v>0.2</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="G52" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>483</v>
       </c>
-      <c r="B53" s="4" t="str">
+      <c r="B53" t="str">
         <f t="shared" si="0"/>
         <v>483</v>
       </c>
@@ -2718,21 +2711,21 @@
       <c r="D53">
         <v>4</v>
       </c>
-      <c r="E53" s="4" t="s">
+      <c r="E53" t="s">
         <v>179</v>
       </c>
-      <c r="F53" s="4">
+      <c r="F53">
         <v>0.2</v>
       </c>
-      <c r="G53" s="4" t="s">
+      <c r="G53" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>490</v>
       </c>
-      <c r="B54" s="4" t="str">
+      <c r="B54" t="str">
         <f t="shared" si="0"/>
         <v>490</v>
       </c>
@@ -2742,21 +2735,21 @@
       <c r="D54">
         <v>4</v>
       </c>
-      <c r="E54" s="4" t="s">
+      <c r="E54" t="s">
         <v>179</v>
       </c>
-      <c r="F54" s="4">
+      <c r="F54">
         <v>0.2</v>
       </c>
-      <c r="G54" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G54" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>491</v>
       </c>
-      <c r="B55" s="4" t="str">
+      <c r="B55" t="str">
         <f t="shared" si="0"/>
         <v>491</v>
       </c>
@@ -2766,21 +2759,21 @@
       <c r="D55">
         <v>4</v>
       </c>
-      <c r="E55" s="4" t="s">
+      <c r="E55" t="s">
         <v>179</v>
       </c>
-      <c r="F55" s="4">
+      <c r="F55">
         <v>0.2</v>
       </c>
-      <c r="G55" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G55" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>492</v>
       </c>
-      <c r="B56" s="4" t="str">
+      <c r="B56" t="str">
         <f t="shared" si="0"/>
         <v>492</v>
       </c>
@@ -2790,21 +2783,21 @@
       <c r="D56">
         <v>4</v>
       </c>
-      <c r="E56" s="4" t="s">
+      <c r="E56" t="s">
         <v>179</v>
       </c>
-      <c r="F56" s="4">
+      <c r="F56">
         <v>0.2</v>
       </c>
-      <c r="G56" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G56" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>493</v>
       </c>
-      <c r="B57" s="4" t="str">
+      <c r="B57" t="str">
         <f t="shared" si="0"/>
         <v>493</v>
       </c>
@@ -2814,21 +2807,21 @@
       <c r="D57">
         <v>4</v>
       </c>
-      <c r="E57" s="4" t="s">
+      <c r="E57" t="s">
         <v>179</v>
       </c>
-      <c r="F57" s="4">
+      <c r="F57">
         <v>0.2</v>
       </c>
-      <c r="G57" s="4" t="s">
+      <c r="G57" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>497</v>
       </c>
-      <c r="B58" s="4" t="str">
+      <c r="B58" t="str">
         <f t="shared" si="0"/>
         <v>497</v>
       </c>
@@ -2838,21 +2831,21 @@
       <c r="D58">
         <v>4</v>
       </c>
-      <c r="E58" s="4" t="s">
+      <c r="E58" t="s">
         <v>179</v>
       </c>
-      <c r="F58" s="4">
+      <c r="F58">
         <v>0.2</v>
       </c>
-      <c r="G58" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G58" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>499</v>
       </c>
-      <c r="B59" s="4" t="str">
+      <c r="B59" t="str">
         <f t="shared" si="0"/>
         <v>499</v>
       </c>
@@ -2862,21 +2855,21 @@
       <c r="D59">
         <v>4</v>
       </c>
-      <c r="E59" s="4" t="s">
+      <c r="E59" t="s">
         <v>179</v>
       </c>
-      <c r="F59" s="4">
+      <c r="F59">
         <v>0.2</v>
       </c>
-      <c r="G59" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G59" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>500</v>
       </c>
-      <c r="B60" s="4" t="str">
+      <c r="B60" t="str">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
@@ -2892,15 +2885,15 @@
       <c r="F60">
         <v>0.25</v>
       </c>
-      <c r="G60" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G60" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>501</v>
       </c>
-      <c r="B61" s="4" t="str">
+      <c r="B61" t="str">
         <f t="shared" si="0"/>
         <v>501</v>
       </c>
@@ -2916,15 +2909,15 @@
       <c r="F61">
         <v>0.25</v>
       </c>
-      <c r="G61" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G61" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>516</v>
       </c>
-      <c r="B62" s="4" t="str">
+      <c r="B62" t="str">
         <f t="shared" si="0"/>
         <v>516</v>
       </c>
@@ -2940,15 +2933,15 @@
       <c r="F62">
         <v>0.25</v>
       </c>
-      <c r="G62" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G62" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>517</v>
       </c>
-      <c r="B63" s="4" t="str">
+      <c r="B63" t="str">
         <f t="shared" si="0"/>
         <v>517</v>
       </c>
@@ -2964,15 +2957,15 @@
       <c r="F63">
         <v>0.25</v>
       </c>
-      <c r="G63" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G63" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>522</v>
       </c>
-      <c r="B64" s="4" t="str">
+      <c r="B64" t="str">
         <f t="shared" si="0"/>
         <v>522</v>
       </c>
@@ -2988,15 +2981,15 @@
       <c r="F64">
         <v>0.25</v>
       </c>
-      <c r="G64" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G64" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>523</v>
       </c>
-      <c r="B65" s="4" t="str">
+      <c r="B65" t="str">
         <f t="shared" si="0"/>
         <v>523</v>
       </c>
@@ -3012,15 +3005,15 @@
       <c r="F65">
         <v>0.25</v>
       </c>
-      <c r="G65" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G65" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>526</v>
       </c>
-      <c r="B66" s="4" t="str">
+      <c r="B66" t="str">
         <f t="shared" si="0"/>
         <v>526</v>
       </c>
@@ -3036,15 +3029,15 @@
       <c r="F66">
         <v>0.25</v>
       </c>
-      <c r="G66" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G66" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>527</v>
       </c>
-      <c r="B67" s="4" t="str">
+      <c r="B67" t="str">
         <f t="shared" ref="B67:B130" si="1">TEXT(A67,"000")</f>
         <v>527</v>
       </c>
@@ -3060,15 +3053,15 @@
       <c r="F67">
         <v>0.25</v>
       </c>
-      <c r="G67" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G67" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>528</v>
       </c>
-      <c r="B68" s="4" t="str">
+      <c r="B68" t="str">
         <f t="shared" si="1"/>
         <v>528</v>
       </c>
@@ -3084,15 +3077,15 @@
       <c r="F68">
         <v>0.25</v>
       </c>
-      <c r="G68" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G68" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>529</v>
       </c>
-      <c r="B69" s="4" t="str">
+      <c r="B69" t="str">
         <f t="shared" si="1"/>
         <v>529</v>
       </c>
@@ -3108,15 +3101,15 @@
       <c r="F69">
         <v>0.25</v>
       </c>
-      <c r="G69" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G69" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>530</v>
       </c>
-      <c r="B70" s="4" t="str">
+      <c r="B70" t="str">
         <f t="shared" si="1"/>
         <v>530</v>
       </c>
@@ -3132,15 +3125,15 @@
       <c r="F70">
         <v>0.25</v>
       </c>
-      <c r="G70" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G70" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>531</v>
       </c>
-      <c r="B71" s="4" t="str">
+      <c r="B71" t="str">
         <f t="shared" si="1"/>
         <v>531</v>
       </c>
@@ -3156,15 +3149,15 @@
       <c r="F71">
         <v>0.25</v>
       </c>
-      <c r="G71" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G71" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>532</v>
       </c>
-      <c r="B72" s="4" t="str">
+      <c r="B72" t="str">
         <f t="shared" si="1"/>
         <v>532</v>
       </c>
@@ -3180,15 +3173,15 @@
       <c r="F72">
         <v>0.25</v>
       </c>
-      <c r="G72" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G72" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>533</v>
       </c>
-      <c r="B73" s="4" t="str">
+      <c r="B73" t="str">
         <f t="shared" si="1"/>
         <v>533</v>
       </c>
@@ -3204,15 +3197,15 @@
       <c r="F73">
         <v>0.25</v>
       </c>
-      <c r="G73" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G73" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>535</v>
       </c>
-      <c r="B74" s="4" t="str">
+      <c r="B74" t="str">
         <f t="shared" si="1"/>
         <v>535</v>
       </c>
@@ -3228,15 +3221,15 @@
       <c r="F74">
         <v>0.25</v>
       </c>
-      <c r="G74" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G74" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>550</v>
       </c>
-      <c r="B75" s="4" t="str">
+      <c r="B75" t="str">
         <f t="shared" si="1"/>
         <v>550</v>
       </c>
@@ -3252,15 +3245,15 @@
       <c r="F75">
         <v>0.25</v>
       </c>
-      <c r="G75" s="4" t="s">
+      <c r="G75" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>580</v>
       </c>
-      <c r="B76" s="4" t="str">
+      <c r="B76" t="str">
         <f t="shared" si="1"/>
         <v>580</v>
       </c>
@@ -3276,15 +3269,15 @@
       <c r="F76">
         <v>0.25</v>
       </c>
-      <c r="G76" s="4" t="s">
+      <c r="G76" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>581</v>
       </c>
-      <c r="B77" s="4" t="str">
+      <c r="B77" t="str">
         <f t="shared" si="1"/>
         <v>581</v>
       </c>
@@ -3300,15 +3293,15 @@
       <c r="F77">
         <v>0.25</v>
       </c>
-      <c r="G77" s="4" t="s">
+      <c r="G77" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>583</v>
       </c>
-      <c r="B78" s="4" t="str">
+      <c r="B78" t="str">
         <f t="shared" si="1"/>
         <v>583</v>
       </c>
@@ -3324,15 +3317,15 @@
       <c r="F78">
         <v>0.25</v>
       </c>
-      <c r="G78" s="4" t="s">
+      <c r="G78" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>587</v>
       </c>
-      <c r="B79" s="4" t="str">
+      <c r="B79" t="str">
         <f t="shared" si="1"/>
         <v>587</v>
       </c>
@@ -3348,15 +3341,15 @@
       <c r="F79">
         <v>0.25</v>
       </c>
-      <c r="G79" s="4" t="s">
+      <c r="G79" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>589</v>
       </c>
-      <c r="B80" s="4" t="str">
+      <c r="B80" t="str">
         <f t="shared" si="1"/>
         <v>589</v>
       </c>
@@ -3372,15 +3365,15 @@
       <c r="F80">
         <v>0.25</v>
       </c>
-      <c r="G80" s="4" t="s">
+      <c r="G80" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>590</v>
       </c>
-      <c r="B81" s="4" t="str">
+      <c r="B81" t="str">
         <f t="shared" si="1"/>
         <v>590</v>
       </c>
@@ -3396,15 +3389,15 @@
       <c r="F81">
         <v>0.25</v>
       </c>
-      <c r="G81" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G81" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>591</v>
       </c>
-      <c r="B82" s="4" t="str">
+      <c r="B82" t="str">
         <f t="shared" si="1"/>
         <v>591</v>
       </c>
@@ -3420,15 +3413,15 @@
       <c r="F82">
         <v>0.25</v>
       </c>
-      <c r="G82" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G82" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>592</v>
       </c>
-      <c r="B83" s="4" t="str">
+      <c r="B83" t="str">
         <f t="shared" si="1"/>
         <v>592</v>
       </c>
@@ -3444,15 +3437,15 @@
       <c r="F83">
         <v>0.25</v>
       </c>
-      <c r="G83" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G83" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>593</v>
       </c>
-      <c r="B84" s="4" t="str">
+      <c r="B84" t="str">
         <f t="shared" si="1"/>
         <v>593</v>
       </c>
@@ -3468,15 +3461,15 @@
       <c r="F84">
         <v>0.25</v>
       </c>
-      <c r="G84" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G84" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>597</v>
       </c>
-      <c r="B85" s="4" t="str">
+      <c r="B85" t="str">
         <f t="shared" si="1"/>
         <v>597</v>
       </c>
@@ -3492,15 +3485,15 @@
       <c r="F85">
         <v>0.25</v>
       </c>
-      <c r="G85" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G85" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>599</v>
       </c>
-      <c r="B86" s="4" t="str">
+      <c r="B86" t="str">
         <f t="shared" si="1"/>
         <v>599</v>
       </c>
@@ -3516,15 +3509,15 @@
       <c r="F86">
         <v>0.25</v>
       </c>
-      <c r="G86" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G86" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>637</v>
       </c>
-      <c r="B87" s="4" t="str">
+      <c r="B87" t="str">
         <f t="shared" si="1"/>
         <v>637</v>
       </c>
@@ -3540,15 +3533,15 @@
       <c r="F87">
         <v>0.1</v>
       </c>
-      <c r="G87" s="4" t="s">
+      <c r="G87" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>638</v>
       </c>
-      <c r="B88" s="4" t="str">
+      <c r="B88" t="str">
         <f t="shared" si="1"/>
         <v>638</v>
       </c>
@@ -3564,15 +3557,15 @@
       <c r="F88">
         <v>0.1</v>
       </c>
-      <c r="G88" s="4" t="s">
+      <c r="G88" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>654</v>
       </c>
-      <c r="B89" s="4" t="str">
+      <c r="B89" t="str">
         <f t="shared" si="1"/>
         <v>654</v>
       </c>
@@ -3588,15 +3581,15 @@
       <c r="F89">
         <v>0.1</v>
       </c>
-      <c r="G89" s="4" t="s">
+      <c r="G89" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>655</v>
       </c>
-      <c r="B90" s="4" t="str">
+      <c r="B90" t="str">
         <f t="shared" si="1"/>
         <v>655</v>
       </c>
@@ -3612,15 +3605,15 @@
       <c r="F90">
         <v>0.1</v>
       </c>
-      <c r="G90" s="4" t="s">
+      <c r="G90" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>663</v>
       </c>
-      <c r="B91" s="4" t="str">
+      <c r="B91" t="str">
         <f t="shared" si="1"/>
         <v>663</v>
       </c>
@@ -3636,15 +3629,15 @@
       <c r="F91">
         <v>0.108333</v>
       </c>
-      <c r="G91" s="4" t="s">
+      <c r="G91" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>668</v>
       </c>
-      <c r="B92" s="4" t="str">
+      <c r="B92" t="str">
         <f t="shared" si="1"/>
         <v>668</v>
       </c>
@@ -3660,15 +3653,15 @@
       <c r="F92">
         <v>0.1</v>
       </c>
-      <c r="G92" s="4" t="s">
+      <c r="G92" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>670</v>
       </c>
-      <c r="B93" s="4" t="str">
+      <c r="B93" t="str">
         <f t="shared" si="1"/>
         <v>670</v>
       </c>
@@ -3684,15 +3677,15 @@
       <c r="F93">
         <v>0.108333</v>
       </c>
-      <c r="G93" s="4" t="s">
+      <c r="G93" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>671</v>
       </c>
-      <c r="B94" s="4" t="str">
+      <c r="B94" t="str">
         <f t="shared" si="1"/>
         <v>671</v>
       </c>
@@ -3708,15 +3701,15 @@
       <c r="F94">
         <v>0.108333</v>
       </c>
-      <c r="G94" s="4" t="s">
+      <c r="G94" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>673</v>
       </c>
-      <c r="B95" s="4" t="str">
+      <c r="B95" t="str">
         <f t="shared" si="1"/>
         <v>673</v>
       </c>
@@ -3732,15 +3725,15 @@
       <c r="F95">
         <v>0.108333</v>
       </c>
-      <c r="G95" s="4" t="s">
+      <c r="G95" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>677</v>
       </c>
-      <c r="B96" s="4" t="str">
+      <c r="B96" t="str">
         <f t="shared" si="1"/>
         <v>677</v>
       </c>
@@ -3756,15 +3749,15 @@
       <c r="F96">
         <v>0.108333</v>
       </c>
-      <c r="G96" s="4" t="s">
+      <c r="G96" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>679</v>
       </c>
-      <c r="B97" s="4" t="str">
+      <c r="B97" t="str">
         <f t="shared" si="1"/>
         <v>679</v>
       </c>
@@ -3780,15 +3773,15 @@
       <c r="F97">
         <v>0.108333</v>
       </c>
-      <c r="G97" s="4" t="s">
+      <c r="G97" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>680</v>
       </c>
-      <c r="B98" s="4" t="str">
+      <c r="B98" t="str">
         <f t="shared" si="1"/>
         <v>680</v>
       </c>
@@ -3804,15 +3797,15 @@
       <c r="F98">
         <v>0.2</v>
       </c>
-      <c r="G98" s="4" t="s">
+      <c r="G98" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="1">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A99">
         <v>683</v>
       </c>
-      <c r="B99" s="4" t="str">
+      <c r="B99" t="str">
         <f t="shared" si="1"/>
         <v>683</v>
       </c>
@@ -3828,15 +3821,15 @@
       <c r="F99">
         <v>0.2</v>
       </c>
-      <c r="G99" s="4" t="s">
+      <c r="G99" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="1">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A100">
         <v>687</v>
       </c>
-      <c r="B100" s="4" t="str">
+      <c r="B100" t="str">
         <f t="shared" si="1"/>
         <v>687</v>
       </c>
@@ -3852,15 +3845,15 @@
       <c r="F100">
         <v>0.2</v>
       </c>
-      <c r="G100" s="4" t="s">
+      <c r="G100" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>693</v>
       </c>
-      <c r="B101" s="4" t="str">
+      <c r="B101" t="str">
         <f t="shared" si="1"/>
         <v>693</v>
       </c>
@@ -3876,15 +3869,15 @@
       <c r="F101">
         <v>0.2</v>
       </c>
-      <c r="G101" s="4" t="s">
+      <c r="G101" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>717</v>
       </c>
-      <c r="B102" s="4" t="str">
+      <c r="B102" t="str">
         <f t="shared" si="1"/>
         <v>717</v>
       </c>
@@ -3900,15 +3893,15 @@
       <c r="F102">
         <v>0.101743</v>
       </c>
-      <c r="G102" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="1">
+      <c r="G102" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A103">
         <v>722</v>
       </c>
-      <c r="B103" s="4" t="str">
+      <c r="B103" t="str">
         <f t="shared" si="1"/>
         <v>722</v>
       </c>
@@ -3924,15 +3917,15 @@
       <c r="F103">
         <v>0.101743</v>
       </c>
-      <c r="G103" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G103" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>723</v>
       </c>
-      <c r="B104" s="4" t="str">
+      <c r="B104" t="str">
         <f t="shared" si="1"/>
         <v>723</v>
       </c>
@@ -3948,15 +3941,15 @@
       <c r="F104">
         <v>0.101743</v>
       </c>
-      <c r="G104" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G104" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>728</v>
       </c>
-      <c r="B105" s="4" t="str">
+      <c r="B105" t="str">
         <f t="shared" si="1"/>
         <v>728</v>
       </c>
@@ -3972,15 +3965,15 @@
       <c r="F105">
         <v>0.101743</v>
       </c>
-      <c r="G105" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G105" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>729</v>
       </c>
-      <c r="B106" s="4" t="str">
+      <c r="B106" t="str">
         <f t="shared" si="1"/>
         <v>729</v>
       </c>
@@ -3996,15 +3989,15 @@
       <c r="F106">
         <v>0.101743</v>
       </c>
-      <c r="G106" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="1">
+      <c r="G106" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A107">
         <v>730</v>
       </c>
-      <c r="B107" s="4" t="str">
+      <c r="B107" t="str">
         <f t="shared" si="1"/>
         <v>730</v>
       </c>
@@ -4020,15 +4013,15 @@
       <c r="F107">
         <v>0.101743</v>
       </c>
-      <c r="G107" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="1">
+      <c r="G107" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A108">
         <v>731</v>
       </c>
-      <c r="B108" s="4" t="str">
+      <c r="B108" t="str">
         <f t="shared" si="1"/>
         <v>731</v>
       </c>
@@ -4044,15 +4037,15 @@
       <c r="F108">
         <v>0.101743</v>
       </c>
-      <c r="G108" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G108" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>746</v>
       </c>
-      <c r="B109" s="4" t="str">
+      <c r="B109" t="str">
         <f t="shared" si="1"/>
         <v>746</v>
       </c>
@@ -4068,15 +4061,15 @@
       <c r="F109">
         <v>0.101743</v>
       </c>
-      <c r="G109" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A110" s="1">
+      <c r="G109" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A110">
         <v>748</v>
       </c>
-      <c r="B110" s="4" t="str">
+      <c r="B110" t="str">
         <f t="shared" si="1"/>
         <v>748</v>
       </c>
@@ -4092,15 +4085,15 @@
       <c r="F110">
         <v>0.101743</v>
       </c>
-      <c r="G110" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G110" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>752</v>
       </c>
-      <c r="B111" s="4" t="str">
+      <c r="B111" t="str">
         <f t="shared" si="1"/>
         <v>752</v>
       </c>
@@ -4116,15 +4109,15 @@
       <c r="F111">
         <v>0.101743</v>
       </c>
-      <c r="G111" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A112" s="1">
+      <c r="G111" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A112">
         <v>760</v>
       </c>
-      <c r="B112" s="4" t="str">
+      <c r="B112" t="str">
         <f t="shared" si="1"/>
         <v>760</v>
       </c>
@@ -4140,15 +4133,15 @@
       <c r="F112">
         <v>0.101743</v>
       </c>
-      <c r="G112" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113" s="1">
+      <c r="G112" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A113">
         <v>765</v>
       </c>
-      <c r="B113" s="4" t="str">
+      <c r="B113" t="str">
         <f t="shared" si="1"/>
         <v>765</v>
       </c>
@@ -4164,15 +4157,15 @@
       <c r="F113">
         <v>0.101743</v>
       </c>
-      <c r="G113" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A114" s="1">
+      <c r="G113" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A114">
         <v>767</v>
       </c>
-      <c r="B114" s="4" t="str">
+      <c r="B114" t="str">
         <f t="shared" si="1"/>
         <v>767</v>
       </c>
@@ -4188,15 +4181,15 @@
       <c r="F114">
         <v>0.101743</v>
       </c>
-      <c r="G114" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G114" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>774</v>
       </c>
-      <c r="B115" s="4" t="str">
+      <c r="B115" t="str">
         <f t="shared" si="1"/>
         <v>774</v>
       </c>
@@ -4212,15 +4205,15 @@
       <c r="F115">
         <v>0.101743</v>
       </c>
-      <c r="G115" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G115" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>790</v>
       </c>
-      <c r="B116" s="4" t="str">
+      <c r="B116" t="str">
         <f t="shared" si="1"/>
         <v>790</v>
       </c>
@@ -4236,15 +4229,15 @@
       <c r="F116">
         <v>0.101743</v>
       </c>
-      <c r="G116" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G116" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>791</v>
       </c>
-      <c r="B117" s="4" t="str">
+      <c r="B117" t="str">
         <f t="shared" si="1"/>
         <v>791</v>
       </c>
@@ -4260,15 +4253,15 @@
       <c r="F117">
         <v>0.101743</v>
       </c>
-      <c r="G117" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G117" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>792</v>
       </c>
-      <c r="B118" s="4" t="str">
+      <c r="B118" t="str">
         <f t="shared" si="1"/>
         <v>792</v>
       </c>
@@ -4284,15 +4277,15 @@
       <c r="F118">
         <v>0.101743</v>
       </c>
-      <c r="G118" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G118" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>797</v>
       </c>
-      <c r="B119" s="4" t="str">
+      <c r="B119" t="str">
         <f t="shared" si="1"/>
         <v>797</v>
       </c>
@@ -4308,15 +4301,15 @@
       <c r="F119">
         <v>0.101743</v>
       </c>
-      <c r="G119" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A120" s="1">
+      <c r="G119" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A120">
         <v>799</v>
       </c>
-      <c r="B120" s="4" t="str">
+      <c r="B120" t="str">
         <f t="shared" si="1"/>
         <v>799</v>
       </c>
@@ -4332,15 +4325,15 @@
       <c r="F120">
         <v>0.101743</v>
       </c>
-      <c r="G120" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G120" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>801</v>
       </c>
-      <c r="B121" s="4" t="str">
+      <c r="B121" t="str">
         <f t="shared" si="1"/>
         <v>801</v>
       </c>
@@ -4356,15 +4349,15 @@
       <c r="F121">
         <v>0.101743</v>
       </c>
-      <c r="G121" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G121" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>817</v>
       </c>
-      <c r="B122" s="4" t="str">
+      <c r="B122" t="str">
         <f t="shared" si="1"/>
         <v>817</v>
       </c>
@@ -4380,15 +4373,15 @@
       <c r="F122">
         <v>0.101743</v>
       </c>
-      <c r="G122" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G122" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>823</v>
       </c>
-      <c r="B123" s="4" t="str">
+      <c r="B123" t="str">
         <f t="shared" si="1"/>
         <v>823</v>
       </c>
@@ -4404,15 +4397,15 @@
       <c r="F123">
         <v>0.101743</v>
       </c>
-      <c r="G123" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G123" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>827</v>
       </c>
-      <c r="B124" s="4" t="str">
+      <c r="B124" t="str">
         <f t="shared" si="1"/>
         <v>827</v>
       </c>
@@ -4428,15 +4421,15 @@
       <c r="F124">
         <v>0.101743</v>
       </c>
-      <c r="G124" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G124" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>828</v>
       </c>
-      <c r="B125" s="4" t="str">
+      <c r="B125" t="str">
         <f t="shared" si="1"/>
         <v>828</v>
       </c>
@@ -4452,15 +4445,15 @@
       <c r="F125">
         <v>0.101743</v>
       </c>
-      <c r="G125" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G125" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>829</v>
       </c>
-      <c r="B126" s="4" t="str">
+      <c r="B126" t="str">
         <f t="shared" si="1"/>
         <v>829</v>
       </c>
@@ -4476,15 +4469,15 @@
       <c r="F126">
         <v>0.101743</v>
       </c>
-      <c r="G126" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G126" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>830</v>
       </c>
-      <c r="B127" s="4" t="str">
+      <c r="B127" t="str">
         <f t="shared" si="1"/>
         <v>830</v>
       </c>
@@ -4500,15 +4493,15 @@
       <c r="F127">
         <v>0.101743</v>
       </c>
-      <c r="G127" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G127" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>831</v>
       </c>
-      <c r="B128" s="4" t="str">
+      <c r="B128" t="str">
         <f t="shared" si="1"/>
         <v>831</v>
       </c>
@@ -4524,15 +4517,15 @@
       <c r="F128">
         <v>0.101743</v>
       </c>
-      <c r="G128" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G128" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>833</v>
       </c>
-      <c r="B129" s="4" t="str">
+      <c r="B129" t="str">
         <f t="shared" si="1"/>
         <v>833</v>
       </c>
@@ -4548,15 +4541,15 @@
       <c r="F129">
         <v>0.101743</v>
       </c>
-      <c r="G129" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G129" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>880</v>
       </c>
-      <c r="B130" s="4" t="str">
+      <c r="B130" t="str">
         <f t="shared" si="1"/>
         <v>880</v>
       </c>
@@ -4572,15 +4565,15 @@
       <c r="F130">
         <v>0.101743</v>
       </c>
-      <c r="G130" s="4" t="s">
+      <c r="G130" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A131" s="1">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A131">
         <v>881</v>
       </c>
-      <c r="B131" s="4" t="str">
+      <c r="B131" t="str">
         <f t="shared" ref="B131:B150" si="2">TEXT(A131,"000")</f>
         <v>881</v>
       </c>
@@ -4596,15 +4589,15 @@
       <c r="F131">
         <v>0.101743</v>
       </c>
-      <c r="G131" s="4" t="s">
+      <c r="G131" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>883</v>
       </c>
-      <c r="B132" s="4" t="str">
+      <c r="B132" t="str">
         <f t="shared" si="2"/>
         <v>883</v>
       </c>
@@ -4620,15 +4613,15 @@
       <c r="F132">
         <v>0.101743</v>
       </c>
-      <c r="G132" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G132" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>887</v>
       </c>
-      <c r="B133" s="4" t="str">
+      <c r="B133" t="str">
         <f t="shared" si="2"/>
         <v>887</v>
       </c>
@@ -4644,15 +4637,15 @@
       <c r="F133">
         <v>0.101743</v>
       </c>
-      <c r="G133" s="4" t="s">
+      <c r="G133" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>889</v>
       </c>
-      <c r="B134" s="4" t="str">
+      <c r="B134" t="str">
         <f t="shared" si="2"/>
         <v>889</v>
       </c>
@@ -4668,15 +4661,15 @@
       <c r="F134">
         <v>0.101743</v>
       </c>
-      <c r="G134" s="4" t="s">
+      <c r="G134" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>890</v>
       </c>
-      <c r="B135" s="4" t="str">
+      <c r="B135" t="str">
         <f t="shared" si="2"/>
         <v>890</v>
       </c>
@@ -4692,15 +4685,15 @@
       <c r="F135">
         <v>0.101743</v>
       </c>
-      <c r="G135" s="4" t="s">
+      <c r="G135" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>891</v>
       </c>
-      <c r="B136" s="4" t="str">
+      <c r="B136" t="str">
         <f t="shared" si="2"/>
         <v>891</v>
       </c>
@@ -4716,15 +4709,15 @@
       <c r="F136">
         <v>0.101743</v>
       </c>
-      <c r="G136" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G136" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>892</v>
       </c>
-      <c r="B137" s="4" t="str">
+      <c r="B137" t="str">
         <f t="shared" si="2"/>
         <v>892</v>
       </c>
@@ -4740,15 +4733,15 @@
       <c r="F137">
         <v>0.101743</v>
       </c>
-      <c r="G137" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G137" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>893</v>
       </c>
-      <c r="B138" s="4" t="str">
+      <c r="B138" t="str">
         <f t="shared" si="2"/>
         <v>893</v>
       </c>
@@ -4764,15 +4757,15 @@
       <c r="F138">
         <v>0.101743</v>
       </c>
-      <c r="G138" s="4" t="s">
+      <c r="G138" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>897</v>
       </c>
-      <c r="B139" s="4" t="str">
+      <c r="B139" t="str">
         <f t="shared" si="2"/>
         <v>897</v>
       </c>
@@ -4788,15 +4781,15 @@
       <c r="F139">
         <v>0.101743</v>
       </c>
-      <c r="G139" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G139" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>899</v>
       </c>
-      <c r="B140" s="4" t="str">
+      <c r="B140" t="str">
         <f t="shared" si="2"/>
         <v>899</v>
       </c>
@@ -4812,15 +4805,15 @@
       <c r="F140">
         <v>0.101743</v>
       </c>
-      <c r="G140" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G140" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>900</v>
       </c>
-      <c r="B141" s="4" t="str">
+      <c r="B141" t="str">
         <f t="shared" si="2"/>
         <v>900</v>
       </c>
@@ -4836,15 +4829,15 @@
       <c r="F141">
         <v>0.1</v>
       </c>
-      <c r="G141" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G141" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>913</v>
       </c>
-      <c r="B142" s="4" t="str">
+      <c r="B142" t="str">
         <f t="shared" si="2"/>
         <v>913</v>
       </c>
@@ -4860,15 +4853,15 @@
       <c r="F142">
         <v>0.1</v>
       </c>
-      <c r="G142" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G142" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>914</v>
       </c>
-      <c r="B143" s="4" t="str">
+      <c r="B143" t="str">
         <f t="shared" si="2"/>
         <v>914</v>
       </c>
@@ -4884,15 +4877,15 @@
       <c r="F143">
         <v>0.1</v>
       </c>
-      <c r="G143" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G143" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>915</v>
       </c>
-      <c r="B144" s="4" t="str">
+      <c r="B144" t="str">
         <f t="shared" si="2"/>
         <v>915</v>
       </c>
@@ -4908,15 +4901,15 @@
       <c r="F144">
         <v>0.1</v>
       </c>
-      <c r="G144" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G144" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>918</v>
       </c>
-      <c r="B145" s="4" t="str">
+      <c r="B145" t="str">
         <f t="shared" si="2"/>
         <v>918</v>
       </c>
@@ -4932,15 +4925,15 @@
       <c r="F145">
         <v>0.1</v>
       </c>
-      <c r="G145" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G145" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>919</v>
       </c>
-      <c r="B146" s="4" t="str">
+      <c r="B146" t="str">
         <f t="shared" si="2"/>
         <v>919</v>
       </c>
@@ -4956,15 +4949,15 @@
       <c r="F146">
         <v>0.1</v>
       </c>
-      <c r="G146" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G146" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>990</v>
       </c>
-      <c r="B147" s="4" t="str">
+      <c r="B147" t="str">
         <f t="shared" si="2"/>
         <v>990</v>
       </c>
@@ -4980,15 +4973,15 @@
       <c r="F147">
         <v>0.1</v>
       </c>
-      <c r="G147" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G147" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>991</v>
       </c>
-      <c r="B148" s="4" t="str">
+      <c r="B148" t="str">
         <f t="shared" si="2"/>
         <v>991</v>
       </c>
@@ -5004,15 +4997,15 @@
       <c r="F148">
         <v>0.1</v>
       </c>
-      <c r="G148" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G148" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>996</v>
       </c>
-      <c r="B149" s="4" t="str">
+      <c r="B149" t="str">
         <f t="shared" si="2"/>
         <v>996</v>
       </c>
@@ -5028,15 +5021,15 @@
       <c r="F149">
         <v>0.1</v>
       </c>
-      <c r="G149" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G149" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>997</v>
       </c>
-      <c r="B150" s="4" t="str">
+      <c r="B150" t="str">
         <f t="shared" si="2"/>
         <v>997</v>
       </c>
@@ -5052,68 +5045,12 @@
       <c r="F150">
         <v>0.1</v>
       </c>
-      <c r="G150" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A151" s="1"/>
-      <c r="B151" s="1"/>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A152" s="1"/>
-      <c r="B152" s="1"/>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A153" s="1"/>
-      <c r="B153" s="1"/>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A154" s="1"/>
-      <c r="B154" s="1"/>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A155" s="1"/>
-      <c r="B155" s="1"/>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A156" s="1"/>
-      <c r="B156" s="1"/>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A157" s="1"/>
-      <c r="B157" s="1"/>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A158" s="1"/>
-      <c r="B158" s="1"/>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A159" s="1"/>
-      <c r="B159" s="1"/>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A160" s="1"/>
-      <c r="B160" s="1"/>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A161" s="1"/>
-      <c r="B161" s="1"/>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A162" s="1"/>
-      <c r="B162" s="1"/>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A163" s="1"/>
-      <c r="B163" s="1"/>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A164" s="1"/>
-      <c r="B164" s="1"/>
+      <c r="G150" t="s">
+        <v>145</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F150" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G150" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -5122,192 +5059,192 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="3" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>180</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" t="s">
         <v>181</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="C2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>182</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" t="s">
         <v>183</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="C3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>184</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="B4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>185</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" t="s">
         <v>186</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="C5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>187</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" t="s">
         <v>188</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>189</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" t="s">
         <v>139</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>190</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" t="s">
         <v>157</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>191</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" t="s">
         <v>192</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="C9" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>193</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" t="s">
         <v>194</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="C10" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>195</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" t="s">
         <v>196</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="C11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>197</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" t="s">
         <v>198</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="C12" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>199</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" t="s">
         <v>200</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="C13" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>201</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="B14" t="s">
+        <v>145</v>
+      </c>
+      <c r="C14" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>202</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" t="s">
         <v>203</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="C15" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>204</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" t="s">
         <v>205</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="C16" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>206</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" t="s">
         <v>207</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" t="s">
         <v>145</v>
       </c>
     </row>
@@ -5319,253 +5256,253 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="3" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>138</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>140</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>141</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>143</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>144</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="B6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>146</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="B7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>147</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="B8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>148</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="B9" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>149</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="B10" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>150</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="B11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>152</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="B12" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>153</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="B13" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>154</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="B14" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>155</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="B15" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>156</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>158</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>159</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>161</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="B19" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>162</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>164</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>166</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>167</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>168</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="B24" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>169</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+      <c r="B25" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>170</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="B26" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>171</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>172</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>173</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
+      <c r="B29" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>174</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
+      <c r="B30" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>175</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -5577,229 +5514,229 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="3" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>138</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" t="s">
         <v>208</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>140</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" t="s">
         <v>210</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
         <v>141</v>
       </c>
       <c r="B4" t="s">
         <v>260</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>144</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" t="s">
         <v>211</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="C5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>146</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" t="s">
         <v>212</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="C6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>147</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" t="s">
         <v>213</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="C7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>148</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" t="s">
         <v>214</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="C8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>149</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" t="s">
         <v>215</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="C9" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>150</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" t="s">
         <v>216</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="C10" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>152</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" t="s">
         <v>217</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="C11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>153</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" t="s">
         <v>218</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="C12" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>154</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" t="s">
         <v>219</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="C13" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>156</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" t="s">
         <v>220</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>221</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" t="s">
         <v>222</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>158</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" t="s">
         <v>223</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>224</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" t="s">
         <v>225</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>226</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" t="s">
         <v>227</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>159</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" t="s">
         <v>229</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="C19" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>230</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" t="s">
         <v>231</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" t="s">
         <v>151</v>
       </c>
     </row>
@@ -5811,250 +5748,250 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="3" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>102</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" t="s">
         <v>232</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+      <c r="C2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>103</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" t="s">
         <v>233</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+      <c r="C3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>104</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" t="s">
         <v>234</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="C4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>105</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" t="s">
         <v>235</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+      <c r="C5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
         <v>106</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" t="s">
         <v>236</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+      <c r="C6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>118</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" t="s">
         <v>237</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>119</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" t="s">
         <v>238</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>120</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" t="s">
         <v>239</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+      <c r="C9" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10">
         <v>181</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" t="s">
         <v>240</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11">
         <v>191</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" t="s">
         <v>241</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12">
         <v>314</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" t="s">
         <v>242</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
+      <c r="C12" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13">
         <v>317</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" t="s">
         <v>243</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
+      <c r="C13" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14">
         <v>320</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" t="s">
         <v>244</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
+      <c r="C14" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15">
         <v>321</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" t="s">
         <v>245</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="6">
+      <c r="C15" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16">
         <v>328</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" t="s">
         <v>246</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
+      <c r="C16" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17">
         <v>401</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" t="s">
         <v>247</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18">
         <v>402</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" t="s">
         <v>248</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19">
         <v>403</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" t="s">
         <v>249</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20">
         <v>415</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" t="s">
         <v>250</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21">
         <v>610</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" t="s">
         <v>251</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22">
         <v>999</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" t="s">
         <v>252</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" t="s">
         <v>188</v>
       </c>
     </row>
@@ -6066,283 +6003,283 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="3" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="str">
         <f>LEFT(B2,2)</f>
         <v>11</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" t="s">
         <v>317</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="str">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="str">
         <f t="shared" ref="A3:A23" si="0">LEFT(B3,2)</f>
         <v>12</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" t="s">
         <v>318</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="str">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="str">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" t="s">
         <v>319</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="str">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="str">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" t="s">
         <v>320</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="str">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="str">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" t="s">
         <v>321</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="str">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="str">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" t="s">
         <v>322</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="str">
+      <c r="C7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="str">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" t="s">
         <v>323</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="str">
+      <c r="C8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="str">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" t="s">
         <v>324</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="str">
+      <c r="C9" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="str">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" t="s">
         <v>325</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="str">
+      <c r="C10" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="str">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" t="s">
         <v>326</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="str">
+      <c r="C11" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="str">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" t="s">
         <v>327</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="str">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="str">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="str">
+      <c r="C13" s="5" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="str">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="str">
+      <c r="C14" s="5" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="str">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" t="s">
         <v>330</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="str">
+      <c r="C15" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="str">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" t="s">
         <v>331</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="str">
+      <c r="C16" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="str">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" t="s">
         <v>332</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="str">
+      <c r="C17" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="str">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" t="s">
         <v>333</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="str">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="str">
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" t="s">
         <v>334</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="str">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="str">
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" t="s">
         <v>335</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="str">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="str">
         <f t="shared" si="0"/>
         <v>83</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" t="s">
         <v>336</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="str">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="str">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" t="s">
         <v>337</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="str">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="str">
         <f t="shared" si="0"/>
         <v>MH</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" t="s">
         <v>338</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" t="s">
         <v>145</v>
       </c>
     </row>
@@ -6355,463 +6292,463 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" s="9" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="3" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="2">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>253</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>254</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>165</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2">
         <f>1/3</f>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="2">
         <v>21</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>255</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>256</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" t="s">
         <v>165</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3">
         <f>1/3</f>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="2">
         <v>27</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>258</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" t="s">
         <v>259</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" t="s">
         <v>165</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="2">
         <v>28</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>260</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" t="s">
         <v>261</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" t="s">
         <v>165</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5">
         <f>1/3</f>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="2">
         <v>29</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>262</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" t="s">
         <v>263</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" t="s">
         <v>165</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="2">
         <v>30</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>264</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" t="s">
         <v>265</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F7" s="2">
+      <c r="E7" t="s">
+        <v>145</v>
+      </c>
+      <c r="F7">
         <f t="shared" ref="F7:F22" si="0">1/3</f>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="2">
         <v>32</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" t="s">
         <v>266</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" t="s">
         <v>267</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F8" s="2">
+      <c r="E8" t="s">
+        <v>145</v>
+      </c>
+      <c r="F8">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
+    <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="2">
         <v>40</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" t="s">
         <v>268</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" t="s">
         <v>269</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F9" s="2">
+      <c r="E9" t="s">
+        <v>145</v>
+      </c>
+      <c r="F9">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="2">
         <v>41</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" t="s">
         <v>270</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" t="s">
         <v>271</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F10" s="2">
+      <c r="E10" t="s">
+        <v>145</v>
+      </c>
+      <c r="F10">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
+    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="2">
         <v>50</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" t="s">
         <v>272</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" t="s">
         <v>273</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F11" s="2">
+      <c r="E11" t="s">
+        <v>145</v>
+      </c>
+      <c r="F11">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+    <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="2">
         <v>52</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" t="s">
         <v>274</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" t="s">
         <v>275</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F12" s="2">
+      <c r="E12" t="s">
+        <v>151</v>
+      </c>
+      <c r="F12">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
+    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="2">
         <v>60</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" t="s">
         <v>276</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" t="s">
         <v>277</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F13" s="2">
+      <c r="E13" t="s">
+        <v>151</v>
+      </c>
+      <c r="F13">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
+    <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="2">
         <v>62</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" t="s">
         <v>274</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" t="s">
         <v>278</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F14" s="2">
+      <c r="E14" t="s">
+        <v>151</v>
+      </c>
+      <c r="F14">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
+    <row r="15" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="2">
         <v>70</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" t="s">
         <v>279</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" t="s">
         <v>280</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F15" s="2">
+      <c r="E15" t="s">
+        <v>151</v>
+      </c>
+      <c r="F15">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="2">
         <v>72</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" t="s">
         <v>274</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" t="s">
         <v>281</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F16" s="2">
+      <c r="E16" t="s">
+        <v>151</v>
+      </c>
+      <c r="F16">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="2">
         <v>80</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" t="s">
         <v>282</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" t="s">
         <v>283</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" t="s">
         <v>157</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="2">
         <v>82</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" t="s">
         <v>284</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" t="s">
         <v>285</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" t="s">
         <v>157</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="2">
         <v>90</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" t="s">
         <v>286</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" t="s">
         <v>287</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F19" s="2">
+      <c r="E19" t="s">
+        <v>145</v>
+      </c>
+      <c r="F19">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="2">
         <v>4600</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" t="s">
         <v>288</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" t="s">
         <v>289</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F20" s="2">
+      <c r="E20" t="s">
+        <v>151</v>
+      </c>
+      <c r="F20">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
+    <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="2">
         <v>5000</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" t="s">
         <v>290</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" t="s">
         <v>291</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F21" s="2">
+      <c r="E21" t="s">
+        <v>151</v>
+      </c>
+      <c r="F21">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
+    <row r="22" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="2">
         <v>7400</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" t="s">
         <v>293</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" t="s">
         <v>294</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" t="s">
         <v>295</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
@@ -6824,159 +6761,159 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="3" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>184</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="B2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>187</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" t="s">
         <v>188</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>189</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" t="s">
         <v>139</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>296</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" t="s">
         <v>297</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="C5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>298</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" t="s">
         <v>299</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="C6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>190</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" t="s">
         <v>157</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>300</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" t="s">
         <v>301</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>191</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" t="s">
         <v>302</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>195</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" t="s">
         <v>303</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>201</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" t="s">
         <v>304</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+      <c r="C11" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>206</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" t="s">
         <v>305</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>306</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" t="s">
         <v>307</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>308</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" t="s">
         <v>309</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" t="s">
         <v>151</v>
       </c>
     </row>

--- a/resources/property classes.xlsx
+++ b/resources/property classes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmapil-my.sharepoint.com/personal/abahls_cmap_illinois_gov/Documents/Documents/github_repos/effective_property_tax/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{2A60A013-1040-4DEC-B76C-0C647DD12EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF013571-E9D9-4AA3-8254-A6847BA48987}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{2A60A013-1040-4DEC-B76C-0C647DD12EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB25FC7B-8658-46C7-B506-0720494CE9E0}"/>
   <bookViews>
-    <workbookView xWindow="17445" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-11355" yWindow="-16365" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cook" sheetId="1" r:id="rId1"/>
@@ -23,8 +23,8 @@
     <sheet name="will" sheetId="7" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cook!$A$1:$G$150</definedName>
-    <definedName name="Export_Output_2" localSheetId="0">Cook!$A$1:$E$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cook!$A$1:$G$152</definedName>
+    <definedName name="Export_Output_2" localSheetId="0">Cook!$A$1:$E$136</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="343">
   <si>
     <t>overall_class</t>
   </si>
@@ -1071,6 +1071,9 @@
   </si>
   <si>
     <t>land_use_code</t>
+  </si>
+  <si>
+    <t>Commercial incentive land</t>
   </si>
 </sst>
 </file>
@@ -1440,7 +1443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G150"/>
+  <dimension ref="A1:G152"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
@@ -3038,7 +3041,7 @@
         <v>527</v>
       </c>
       <c r="B67" t="str">
-        <f t="shared" ref="B67:B130" si="1">TEXT(A67,"000")</f>
+        <f t="shared" ref="B67:B132" si="1">TEXT(A67,"000")</f>
         <v>527</v>
       </c>
       <c r="C67" t="s">
@@ -4331,14 +4334,14 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B121" t="str">
         <f t="shared" si="1"/>
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C121" t="s">
-        <v>121</v>
+        <v>342</v>
       </c>
       <c r="D121" t="s">
         <v>122</v>
@@ -4355,14 +4358,14 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122">
-        <v>817</v>
+        <v>801</v>
       </c>
       <c r="B122" t="str">
         <f t="shared" si="1"/>
-        <v>817</v>
+        <v>801</v>
       </c>
       <c r="C122" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="D122" t="s">
         <v>122</v>
@@ -4379,14 +4382,14 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="B123" t="str">
         <f t="shared" si="1"/>
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="C123" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="D123" t="s">
         <v>122</v>
@@ -4403,14 +4406,14 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="B124" t="str">
         <f t="shared" si="1"/>
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="C124" t="s">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="D124" t="s">
         <v>122</v>
@@ -4427,14 +4430,14 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B125" t="str">
         <f t="shared" si="1"/>
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C125" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D125" t="s">
         <v>122</v>
@@ -4451,14 +4454,14 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="B126" t="str">
         <f t="shared" si="1"/>
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C126" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D126" t="s">
         <v>122</v>
@@ -4475,14 +4478,14 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B127" t="str">
         <f t="shared" si="1"/>
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="C127" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D127" t="s">
         <v>122</v>
@@ -4499,14 +4502,14 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B128" t="str">
         <f t="shared" si="1"/>
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C128" t="s">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="D128" t="s">
         <v>122</v>
@@ -4523,14 +4526,14 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="B129" t="str">
         <f t="shared" si="1"/>
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="C129" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D129" t="s">
         <v>122</v>
@@ -4547,17 +4550,17 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130">
-        <v>880</v>
+        <v>831</v>
       </c>
       <c r="B130" t="str">
         <f t="shared" si="1"/>
-        <v>880</v>
+        <v>831</v>
       </c>
       <c r="C130" t="s">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="D130" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E130" t="s">
         <v>123</v>
@@ -4566,22 +4569,22 @@
         <v>0.101743</v>
       </c>
       <c r="G130" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131">
-        <v>881</v>
+        <v>833</v>
       </c>
       <c r="B131" t="str">
-        <f t="shared" ref="B131:B150" si="2">TEXT(A131,"000")</f>
-        <v>881</v>
+        <f t="shared" si="1"/>
+        <v>833</v>
       </c>
       <c r="C131" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="D131" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E131" t="s">
         <v>123</v>
@@ -4590,467 +4593,515 @@
         <v>0.101743</v>
       </c>
       <c r="G131" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132">
+        <v>880</v>
+      </c>
+      <c r="B132" t="str">
+        <f t="shared" si="1"/>
+        <v>880</v>
+      </c>
+      <c r="C132" t="s">
+        <v>85</v>
+      </c>
+      <c r="D132" t="s">
+        <v>126</v>
+      </c>
+      <c r="E132" t="s">
+        <v>123</v>
+      </c>
+      <c r="F132">
+        <v>0.101743</v>
+      </c>
+      <c r="G132" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A133">
+        <v>881</v>
+      </c>
+      <c r="B133" t="str">
+        <f t="shared" ref="B133:B152" si="2">TEXT(A133,"000")</f>
+        <v>881</v>
+      </c>
+      <c r="C133" t="s">
+        <v>105</v>
+      </c>
+      <c r="D133" t="s">
+        <v>126</v>
+      </c>
+      <c r="E133" t="s">
+        <v>123</v>
+      </c>
+      <c r="F133">
+        <v>0.101743</v>
+      </c>
+      <c r="G133" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A134">
         <v>883</v>
       </c>
-      <c r="B132" t="str">
+      <c r="B134" t="str">
         <f t="shared" si="2"/>
         <v>883</v>
       </c>
-      <c r="C132" t="s">
+      <c r="C134" t="s">
         <v>80</v>
       </c>
-      <c r="D132" t="s">
+      <c r="D134" t="s">
         <v>126</v>
       </c>
-      <c r="E132" t="s">
+      <c r="E134" t="s">
         <v>123</v>
       </c>
-      <c r="F132">
+      <c r="F134">
         <v>0.101743</v>
       </c>
-      <c r="G132" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A133">
+      <c r="G134" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A135">
         <v>887</v>
       </c>
-      <c r="B133" t="str">
+      <c r="B135" t="str">
         <f t="shared" si="2"/>
         <v>887</v>
       </c>
-      <c r="C133" t="s">
+      <c r="C135" t="s">
         <v>88</v>
       </c>
-      <c r="D133" t="s">
+      <c r="D135" t="s">
         <v>126</v>
       </c>
-      <c r="E133" t="s">
+      <c r="E135" t="s">
         <v>123</v>
       </c>
-      <c r="F133">
+      <c r="F135">
         <v>0.101743</v>
       </c>
-      <c r="G133" t="s">
+      <c r="G135" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A134">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A136">
         <v>889</v>
       </c>
-      <c r="B134" t="str">
+      <c r="B136" t="str">
         <f t="shared" si="2"/>
         <v>889</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C136" t="s">
         <v>89</v>
       </c>
-      <c r="D134" t="s">
+      <c r="D136" t="s">
         <v>126</v>
       </c>
-      <c r="E134" t="s">
+      <c r="E136" t="s">
         <v>123</v>
       </c>
-      <c r="F134">
+      <c r="F136">
         <v>0.101743</v>
       </c>
-      <c r="G134" t="s">
+      <c r="G136" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A135">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A137">
         <v>890</v>
       </c>
-      <c r="B135" t="str">
+      <c r="B137" t="str">
         <f t="shared" si="2"/>
         <v>890</v>
       </c>
-      <c r="C135" t="s">
+      <c r="C137" t="s">
         <v>127</v>
       </c>
-      <c r="D135" t="s">
+      <c r="D137" t="s">
         <v>126</v>
       </c>
-      <c r="E135" t="s">
+      <c r="E137" t="s">
         <v>123</v>
       </c>
-      <c r="F135">
+      <c r="F137">
         <v>0.101743</v>
       </c>
-      <c r="G135" t="s">
+      <c r="G137" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A136">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A138">
         <v>891</v>
       </c>
-      <c r="B136" t="str">
+      <c r="B138" t="str">
         <f t="shared" si="2"/>
         <v>891</v>
       </c>
-      <c r="C136" t="s">
+      <c r="C138" t="s">
         <v>117</v>
       </c>
-      <c r="D136" t="s">
+      <c r="D138" t="s">
         <v>122</v>
       </c>
-      <c r="E136" t="s">
+      <c r="E138" t="s">
         <v>123</v>
       </c>
-      <c r="F136">
+      <c r="F138">
         <v>0.101743</v>
       </c>
-      <c r="G136" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A137">
+      <c r="G138" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A139">
         <v>892</v>
       </c>
-      <c r="B137" t="str">
+      <c r="B139" t="str">
         <f t="shared" si="2"/>
         <v>892</v>
       </c>
-      <c r="C137" t="s">
+      <c r="C139" t="s">
         <v>92</v>
       </c>
-      <c r="D137" t="s">
+      <c r="D139" t="s">
         <v>122</v>
       </c>
-      <c r="E137" t="s">
+      <c r="E139" t="s">
         <v>123</v>
       </c>
-      <c r="F137">
+      <c r="F139">
         <v>0.101743</v>
       </c>
-      <c r="G137" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A138">
+      <c r="G139" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A140">
         <v>893</v>
       </c>
-      <c r="B138" t="str">
+      <c r="B140" t="str">
         <f t="shared" si="2"/>
         <v>893</v>
       </c>
-      <c r="C138" t="s">
+      <c r="C140" t="s">
         <v>93</v>
       </c>
-      <c r="D138" t="s">
+      <c r="D140" t="s">
         <v>126</v>
       </c>
-      <c r="E138" t="s">
+      <c r="E140" t="s">
         <v>123</v>
       </c>
-      <c r="F138">
+      <c r="F140">
         <v>0.101743</v>
       </c>
-      <c r="G138" t="s">
+      <c r="G140" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A139">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A141">
         <v>897</v>
       </c>
-      <c r="B139" t="str">
+      <c r="B141" t="str">
         <f t="shared" si="2"/>
         <v>897</v>
       </c>
-      <c r="C139" t="s">
+      <c r="C141" t="s">
         <v>94</v>
       </c>
-      <c r="D139" t="s">
+      <c r="D141" t="s">
         <v>122</v>
       </c>
-      <c r="E139" t="s">
+      <c r="E141" t="s">
         <v>123</v>
       </c>
-      <c r="F139">
+      <c r="F141">
         <v>0.101743</v>
       </c>
-      <c r="G139" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A140">
+      <c r="G141" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A142">
         <v>899</v>
       </c>
-      <c r="B140" t="str">
+      <c r="B142" t="str">
         <f t="shared" si="2"/>
         <v>899</v>
       </c>
-      <c r="C140" t="s">
+      <c r="C142" t="s">
         <v>128</v>
       </c>
-      <c r="D140" t="s">
+      <c r="D142" t="s">
         <v>126</v>
       </c>
-      <c r="E140" t="s">
+      <c r="E142" t="s">
         <v>123</v>
       </c>
-      <c r="F140">
+      <c r="F142">
         <v>0.101743</v>
       </c>
-      <c r="G140" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A141">
+      <c r="G142" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A143">
         <v>900</v>
       </c>
-      <c r="B141" t="str">
+      <c r="B143" t="str">
         <f t="shared" si="2"/>
         <v>900</v>
       </c>
-      <c r="C141" t="s">
+      <c r="C143" t="s">
         <v>129</v>
       </c>
-      <c r="D141">
+      <c r="D143">
         <v>9</v>
       </c>
-      <c r="E141" t="s">
+      <c r="E143" t="s">
         <v>130</v>
       </c>
-      <c r="F141">
+      <c r="F143">
         <v>0.1</v>
       </c>
-      <c r="G141" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A142">
+      <c r="G143" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A144">
         <v>913</v>
       </c>
-      <c r="B142" t="str">
+      <c r="B144" t="str">
         <f t="shared" si="2"/>
         <v>913</v>
       </c>
-      <c r="C142" t="s">
+      <c r="C144" t="s">
         <v>131</v>
       </c>
-      <c r="D142">
+      <c r="D144">
         <v>9</v>
       </c>
-      <c r="E142" t="s">
+      <c r="E144" t="s">
         <v>130</v>
       </c>
-      <c r="F142">
+      <c r="F144">
         <v>0.1</v>
       </c>
-      <c r="G142" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A143">
+      <c r="G144" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A145">
         <v>914</v>
       </c>
-      <c r="B143" t="str">
+      <c r="B145" t="str">
         <f t="shared" si="2"/>
         <v>914</v>
       </c>
-      <c r="C143" t="s">
+      <c r="C145" t="s">
         <v>132</v>
       </c>
-      <c r="D143">
+      <c r="D145">
         <v>9</v>
       </c>
-      <c r="E143" t="s">
+      <c r="E145" t="s">
         <v>130</v>
       </c>
-      <c r="F143">
+      <c r="F145">
         <v>0.1</v>
       </c>
-      <c r="G143" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A144">
+      <c r="G145" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A146">
         <v>915</v>
       </c>
-      <c r="B144" t="str">
+      <c r="B146" t="str">
         <f t="shared" si="2"/>
         <v>915</v>
       </c>
-      <c r="C144" t="s">
+      <c r="C146" t="s">
         <v>133</v>
       </c>
-      <c r="D144">
+      <c r="D146">
         <v>9</v>
       </c>
-      <c r="E144" t="s">
+      <c r="E146" t="s">
         <v>130</v>
       </c>
-      <c r="F144">
+      <c r="F146">
         <v>0.1</v>
       </c>
-      <c r="G144" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A145">
+      <c r="G146" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A147">
         <v>918</v>
       </c>
-      <c r="B145" t="str">
+      <c r="B147" t="str">
         <f t="shared" si="2"/>
         <v>918</v>
       </c>
-      <c r="C145" t="s">
+      <c r="C147" t="s">
         <v>134</v>
       </c>
-      <c r="D145">
+      <c r="D147">
         <v>9</v>
       </c>
-      <c r="E145" t="s">
+      <c r="E147" t="s">
         <v>130</v>
       </c>
-      <c r="F145">
+      <c r="F147">
         <v>0.1</v>
       </c>
-      <c r="G145" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A146">
+      <c r="G147" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A148">
         <v>919</v>
       </c>
-      <c r="B146" t="str">
+      <c r="B148" t="str">
         <f t="shared" si="2"/>
         <v>919</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C148" t="s">
         <v>135</v>
       </c>
-      <c r="D146">
+      <c r="D148">
         <v>9</v>
       </c>
-      <c r="E146" t="s">
+      <c r="E148" t="s">
         <v>130</v>
       </c>
-      <c r="F146">
+      <c r="F148">
         <v>0.1</v>
       </c>
-      <c r="G146" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A147">
+      <c r="G148" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A149">
         <v>990</v>
       </c>
-      <c r="B147" t="str">
+      <c r="B149" t="str">
         <f t="shared" si="2"/>
         <v>990</v>
       </c>
-      <c r="C147" t="s">
+      <c r="C149" t="s">
         <v>136</v>
       </c>
-      <c r="D147">
+      <c r="D149">
         <v>9</v>
       </c>
-      <c r="E147" t="s">
+      <c r="E149" t="s">
         <v>130</v>
       </c>
-      <c r="F147">
+      <c r="F149">
         <v>0.1</v>
       </c>
-      <c r="G147" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A148">
+      <c r="G149" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A150">
         <v>991</v>
       </c>
-      <c r="B148" t="str">
+      <c r="B150" t="str">
         <f t="shared" si="2"/>
         <v>991</v>
       </c>
-      <c r="C148" t="s">
+      <c r="C150" t="s">
         <v>137</v>
       </c>
-      <c r="D148">
+      <c r="D150">
         <v>9</v>
       </c>
-      <c r="E148" t="s">
+      <c r="E150" t="s">
         <v>130</v>
       </c>
-      <c r="F148">
+      <c r="F150">
         <v>0.1</v>
       </c>
-      <c r="G148" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A149">
+      <c r="G150" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A151">
         <v>996</v>
       </c>
-      <c r="B149" t="str">
+      <c r="B151" t="str">
         <f t="shared" si="2"/>
         <v>996</v>
       </c>
-      <c r="C149" t="s">
+      <c r="C151" t="s">
         <v>46</v>
       </c>
-      <c r="D149">
+      <c r="D151">
         <v>9</v>
       </c>
-      <c r="E149" t="s">
+      <c r="E151" t="s">
         <v>130</v>
       </c>
-      <c r="F149">
+      <c r="F151">
         <v>0.1</v>
       </c>
-      <c r="G149" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A150">
+      <c r="G151" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A152">
         <v>997</v>
       </c>
-      <c r="B150" t="str">
+      <c r="B152" t="str">
         <f t="shared" si="2"/>
         <v>997</v>
       </c>
-      <c r="C150" t="s">
+      <c r="C152" t="s">
         <v>47</v>
       </c>
-      <c r="D150">
+      <c r="D152">
         <v>9</v>
       </c>
-      <c r="E150" t="s">
+      <c r="E152" t="s">
         <v>130</v>
       </c>
-      <c r="F150">
+      <c r="F152">
         <v>0.1</v>
       </c>
-      <c r="G150" t="s">
+      <c r="G152" t="s">
         <v>145</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G150" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G152" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/resources/property classes.xlsx
+++ b/resources/property classes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmapil-my.sharepoint.com/personal/abahls_cmap_illinois_gov/Documents/Documents/github_repos/effective_property_tax/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{2A60A013-1040-4DEC-B76C-0C647DD12EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB25FC7B-8658-46C7-B506-0720494CE9E0}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{2A60A013-1040-4DEC-B76C-0C647DD12EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21273C65-3E87-4048-876E-EC8C002C0210}"/>
   <bookViews>
-    <workbookView xWindow="-11355" yWindow="-16365" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cook" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="344">
   <si>
     <t>overall_class</t>
   </si>
@@ -1074,6 +1074,9 @@
   </si>
   <si>
     <t>Commercial incentive land</t>
+  </si>
+  <si>
+    <t>5000 - Locally Assessed Railroad</t>
   </si>
 </sst>
 </file>
@@ -6053,7 +6056,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
@@ -6084,7 +6087,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
-        <f t="shared" ref="A3:A23" si="0">LEFT(B3,2)</f>
+        <f t="shared" ref="A3:A24" si="0">LEFT(B3,2)</f>
         <v>12</v>
       </c>
       <c r="B3" t="s">
@@ -6203,15 +6206,15 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>151</v>
+      <c r="A13" t="str">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="B13" t="s">
+        <v>343</v>
+      </c>
+      <c r="C13" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -6220,31 +6223,31 @@
         <v>60</v>
       </c>
       <c r="B14" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="str">
-        <f t="shared" si="0"/>
-        <v>61</v>
-      </c>
-      <c r="B15" t="s">
-        <v>330</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="C15" s="5" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f t="shared" si="0"/>
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B16" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C16" t="s">
         <v>151</v>
@@ -6253,10 +6256,10 @@
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f t="shared" si="0"/>
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B17" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C17" t="s">
         <v>151</v>
@@ -6265,22 +6268,22 @@
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f t="shared" si="0"/>
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="B18" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C18" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f t="shared" si="0"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B19" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C19" t="s">
         <v>157</v>
@@ -6289,10 +6292,10 @@
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f t="shared" si="0"/>
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B20" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C20" t="s">
         <v>157</v>
@@ -6301,10 +6304,10 @@
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f t="shared" si="0"/>
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B21" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C21" t="s">
         <v>157</v>
@@ -6313,24 +6316,36 @@
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f t="shared" si="0"/>
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B22" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C22" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="B23" t="s">
+        <v>337</v>
+      </c>
+      <c r="C23" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="str">
+        <f t="shared" si="0"/>
         <v>MH</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B24" t="s">
         <v>338</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C24" t="s">
         <v>145</v>
       </c>
     </row>

--- a/resources/property classes.xlsx
+++ b/resources/property classes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmapil-my.sharepoint.com/personal/abahls_cmap_illinois_gov/Documents/Documents/github_repos/effective_property_tax/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{2A60A013-1040-4DEC-B76C-0C647DD12EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21273C65-3E87-4048-876E-EC8C002C0210}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{2A60A013-1040-4DEC-B76C-0C647DD12EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DEE2F40-C6AF-4ABA-861A-13FCD93F345B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cook" sheetId="1" r:id="rId1"/>
@@ -5114,6 +5114,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="45.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
@@ -6359,6 +6362,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="33" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
@@ -6828,6 +6834,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">

--- a/resources/property classes.xlsx
+++ b/resources/property classes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmapil-my.sharepoint.com/personal/abahls_cmap_illinois_gov/Documents/Documents/github_repos/effective_property_tax/resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abahls\Documents\GitHub\effective_property_tax\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{2A60A013-1040-4DEC-B76C-0C647DD12EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF013571-E9D9-4AA3-8254-A6847BA48987}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E95C164E-E1BB-45F5-9E3A-2A96C1DD5F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17445" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="37320" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cook" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="lake 2018 later" sheetId="8" r:id="rId6"/>
     <sheet name="mchenry" sheetId="6" r:id="rId7"/>
     <sheet name="will" sheetId="7" r:id="rId8"/>
+    <sheet name="Notes" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cook!$A$1:$G$150</definedName>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="365">
   <si>
     <t>overall_class</t>
   </si>
@@ -1071,13 +1072,86 @@
   </si>
   <si>
     <t>land_use_code</t>
+  </si>
+  <si>
+    <t>Cook</t>
+  </si>
+  <si>
+    <t>https://prodassets.cookcountyassessor.com/s3fs-public/form_documents/classcode.pdf</t>
+  </si>
+  <si>
+    <t>https://www.cookcountyassessor.com/classifications-real-property</t>
+  </si>
+  <si>
+    <t>DuPage</t>
+  </si>
+  <si>
+    <t>Kane</t>
+  </si>
+  <si>
+    <t>Kendall</t>
+  </si>
+  <si>
+    <t>Lake</t>
+  </si>
+  <si>
+    <t>McHenry</t>
+  </si>
+  <si>
+    <t>Will</t>
+  </si>
+  <si>
+    <t>A-Apartment classed properties are 2-6 units and are residential properties.  M-Multiple classed properties are more than 6 unit apartments and are commercial properties.</t>
+  </si>
+  <si>
+    <t>email with Helen Krengel  &lt;Helen.Krengel@dupagecounty.gov&gt;</t>
+  </si>
+  <si>
+    <t>changes</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>The 0050 class is for commercial residential property.  So those parcels generally are apartment buildings</t>
+  </si>
+  <si>
+    <t>email with John Emerson &lt;EmersonJohn@KaneCountyIL.gov&gt;</t>
+  </si>
+  <si>
+    <t>0050 to commercial</t>
+  </si>
+  <si>
+    <t>0011 would just be Farm, not open space as this class only applies to property that is farmland and has buildings on it.
+0028 is used for property where land, either all or part, is in a IDNR program to conserve open space.  A property owner submits a plan and other information to the IDNR who then determines what portion of the property would qualify for this use.  
+0090 is for Tax Exempt Properties (government owned, religious, etc.) and has nothing to with railroads.  
+4500 is State Assessed Railroad. Would not fall into the Exempt category.
+5000 Railroad is local assessed railroad and would not be considered as exempt.  Local assessed railroad would be the buildings that are on the railroad right of way not the tracks themselves so this is probably you were told that it is called commercial.</t>
+  </si>
+  <si>
+    <t>Andy Nicoletti, ANicoletti@kendallcountyil.gov</t>
+  </si>
+  <si>
+    <t>relatively straightforward; can look up individual cases on the PIN search</t>
+  </si>
+  <si>
+    <t>changed 50 to commercial, based on names its clear which is which</t>
+  </si>
+  <si>
+    <t>50 to commercial</t>
+  </si>
+  <si>
+    <t>no apartment category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no change </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1111,6 +1185,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1148,7 +1228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1160,6 +1240,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1441,16 +1527,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G150"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="80.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" customWidth="1"/>
+    <col min="3" max="3" width="80.6328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="34.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1473,7 +1559,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1497,7 +1583,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>100</v>
       </c>
@@ -1521,7 +1607,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>190</v>
       </c>
@@ -1545,7 +1631,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>200</v>
       </c>
@@ -1569,7 +1655,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>201</v>
       </c>
@@ -1593,7 +1679,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>202</v>
       </c>
@@ -1617,7 +1703,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>203</v>
       </c>
@@ -1641,7 +1727,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>204</v>
       </c>
@@ -1665,7 +1751,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>205</v>
       </c>
@@ -1689,7 +1775,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>206</v>
       </c>
@@ -1713,7 +1799,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>207</v>
       </c>
@@ -1737,7 +1823,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>208</v>
       </c>
@@ -1761,7 +1847,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>209</v>
       </c>
@@ -1785,7 +1871,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>210</v>
       </c>
@@ -1809,7 +1895,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>211</v>
       </c>
@@ -1833,7 +1919,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>212</v>
       </c>
@@ -1857,7 +1943,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>213</v>
       </c>
@@ -1881,7 +1967,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>218</v>
       </c>
@@ -1905,7 +1991,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>219</v>
       </c>
@@ -1929,7 +2015,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>224</v>
       </c>
@@ -1953,7 +2039,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>225</v>
       </c>
@@ -1977,7 +2063,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>234</v>
       </c>
@@ -2001,7 +2087,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>239</v>
       </c>
@@ -2025,7 +2111,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>241</v>
       </c>
@@ -2049,7 +2135,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>278</v>
       </c>
@@ -2073,7 +2159,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>288</v>
       </c>
@@ -2097,7 +2183,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>290</v>
       </c>
@@ -2121,7 +2207,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>295</v>
       </c>
@@ -2145,7 +2231,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>297</v>
       </c>
@@ -2169,7 +2255,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>299</v>
       </c>
@@ -2193,7 +2279,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>300</v>
       </c>
@@ -2217,7 +2303,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>301</v>
       </c>
@@ -2241,7 +2327,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>313</v>
       </c>
@@ -2265,7 +2351,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>314</v>
       </c>
@@ -2289,7 +2375,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>315</v>
       </c>
@@ -2313,7 +2399,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>318</v>
       </c>
@@ -2337,7 +2423,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>319</v>
       </c>
@@ -2361,7 +2447,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>390</v>
       </c>
@@ -2385,7 +2471,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>391</v>
       </c>
@@ -2409,7 +2495,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>396</v>
       </c>
@@ -2433,7 +2519,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>397</v>
       </c>
@@ -2457,7 +2543,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>399</v>
       </c>
@@ -2481,7 +2567,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>401</v>
       </c>
@@ -2505,7 +2591,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>417</v>
       </c>
@@ -2529,7 +2615,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>418</v>
       </c>
@@ -2553,7 +2639,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>422</v>
       </c>
@@ -2577,7 +2663,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>427</v>
       </c>
@@ -2601,7 +2687,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>428</v>
       </c>
@@ -2625,7 +2711,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>430</v>
       </c>
@@ -2649,7 +2735,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>435</v>
       </c>
@@ -2673,7 +2759,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>480</v>
       </c>
@@ -2697,7 +2783,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>483</v>
       </c>
@@ -2721,7 +2807,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>490</v>
       </c>
@@ -2745,7 +2831,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>491</v>
       </c>
@@ -2769,7 +2855,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>492</v>
       </c>
@@ -2793,7 +2879,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>493</v>
       </c>
@@ -2817,7 +2903,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>497</v>
       </c>
@@ -2841,7 +2927,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>499</v>
       </c>
@@ -2865,7 +2951,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>500</v>
       </c>
@@ -2889,7 +2975,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>501</v>
       </c>
@@ -2913,7 +2999,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>516</v>
       </c>
@@ -2937,7 +3023,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>517</v>
       </c>
@@ -2961,7 +3047,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>522</v>
       </c>
@@ -2985,7 +3071,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>523</v>
       </c>
@@ -3009,7 +3095,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>526</v>
       </c>
@@ -3033,7 +3119,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>527</v>
       </c>
@@ -3057,7 +3143,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>528</v>
       </c>
@@ -3081,7 +3167,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>529</v>
       </c>
@@ -3105,7 +3191,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>530</v>
       </c>
@@ -3129,7 +3215,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>531</v>
       </c>
@@ -3153,7 +3239,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>532</v>
       </c>
@@ -3177,7 +3263,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>533</v>
       </c>
@@ -3201,7 +3287,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>535</v>
       </c>
@@ -3225,7 +3311,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>550</v>
       </c>
@@ -3249,7 +3335,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>580</v>
       </c>
@@ -3273,7 +3359,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>581</v>
       </c>
@@ -3297,7 +3383,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>583</v>
       </c>
@@ -3321,7 +3407,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>587</v>
       </c>
@@ -3345,7 +3431,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>589</v>
       </c>
@@ -3369,7 +3455,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>590</v>
       </c>
@@ -3393,7 +3479,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>591</v>
       </c>
@@ -3417,7 +3503,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>592</v>
       </c>
@@ -3441,7 +3527,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>593</v>
       </c>
@@ -3465,7 +3551,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>597</v>
       </c>
@@ -3489,7 +3575,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>599</v>
       </c>
@@ -3513,7 +3599,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>637</v>
       </c>
@@ -3537,7 +3623,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>638</v>
       </c>
@@ -3561,7 +3647,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>654</v>
       </c>
@@ -3585,7 +3671,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>655</v>
       </c>
@@ -3609,7 +3695,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>663</v>
       </c>
@@ -3633,7 +3719,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>668</v>
       </c>
@@ -3657,7 +3743,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>670</v>
       </c>
@@ -3681,7 +3767,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>671</v>
       </c>
@@ -3705,7 +3791,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>673</v>
       </c>
@@ -3729,7 +3815,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>677</v>
       </c>
@@ -3753,7 +3839,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>679</v>
       </c>
@@ -3777,7 +3863,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>680</v>
       </c>
@@ -3801,7 +3887,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>683</v>
       </c>
@@ -3825,7 +3911,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>687</v>
       </c>
@@ -3849,7 +3935,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>693</v>
       </c>
@@ -3873,7 +3959,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>717</v>
       </c>
@@ -3897,7 +3983,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>722</v>
       </c>
@@ -3921,7 +4007,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>723</v>
       </c>
@@ -3945,7 +4031,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>728</v>
       </c>
@@ -3969,7 +4055,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>729</v>
       </c>
@@ -3993,7 +4079,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>730</v>
       </c>
@@ -4017,7 +4103,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>731</v>
       </c>
@@ -4041,7 +4127,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>746</v>
       </c>
@@ -4065,7 +4151,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>748</v>
       </c>
@@ -4089,7 +4175,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>752</v>
       </c>
@@ -4113,7 +4199,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>760</v>
       </c>
@@ -4137,7 +4223,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>765</v>
       </c>
@@ -4161,7 +4247,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>767</v>
       </c>
@@ -4185,7 +4271,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>774</v>
       </c>
@@ -4209,7 +4295,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>790</v>
       </c>
@@ -4233,7 +4319,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>791</v>
       </c>
@@ -4257,7 +4343,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>792</v>
       </c>
@@ -4281,7 +4367,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>797</v>
       </c>
@@ -4305,7 +4391,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>799</v>
       </c>
@@ -4329,7 +4415,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>801</v>
       </c>
@@ -4353,7 +4439,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>817</v>
       </c>
@@ -4377,7 +4463,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>823</v>
       </c>
@@ -4401,7 +4487,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>827</v>
       </c>
@@ -4425,7 +4511,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>828</v>
       </c>
@@ -4449,7 +4535,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>829</v>
       </c>
@@ -4473,7 +4559,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>830</v>
       </c>
@@ -4497,7 +4583,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>831</v>
       </c>
@@ -4521,7 +4607,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>833</v>
       </c>
@@ -4545,7 +4631,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>880</v>
       </c>
@@ -4569,7 +4655,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>881</v>
       </c>
@@ -4593,7 +4679,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>883</v>
       </c>
@@ -4617,7 +4703,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>887</v>
       </c>
@@ -4641,7 +4727,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>889</v>
       </c>
@@ -4665,7 +4751,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>890</v>
       </c>
@@ -4689,7 +4775,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>891</v>
       </c>
@@ -4713,7 +4799,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>892</v>
       </c>
@@ -4737,7 +4823,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>893</v>
       </c>
@@ -4761,7 +4847,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>897</v>
       </c>
@@ -4785,7 +4871,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>899</v>
       </c>
@@ -4809,7 +4895,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>900</v>
       </c>
@@ -4833,7 +4919,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>913</v>
       </c>
@@ -4857,7 +4943,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>914</v>
       </c>
@@ -4881,7 +4967,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>915</v>
       </c>
@@ -4905,7 +4991,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>918</v>
       </c>
@@ -4929,7 +5015,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>919</v>
       </c>
@@ -4953,7 +5039,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>990</v>
       </c>
@@ -4977,7 +5063,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>991</v>
       </c>
@@ -5001,7 +5087,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>996</v>
       </c>
@@ -5025,7 +5111,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>997</v>
       </c>
@@ -5059,9 +5145,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="48.36328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>310</v>
       </c>
@@ -5072,7 +5161,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>180</v>
       </c>
@@ -5083,7 +5172,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>182</v>
       </c>
@@ -5094,7 +5183,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>184</v>
       </c>
@@ -5105,7 +5194,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>185</v>
       </c>
@@ -5116,7 +5205,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>187</v>
       </c>
@@ -5127,7 +5216,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>189</v>
       </c>
@@ -5138,7 +5227,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>190</v>
       </c>
@@ -5149,7 +5238,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>191</v>
       </c>
@@ -5160,7 +5249,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>193</v>
       </c>
@@ -5171,7 +5260,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>195</v>
       </c>
@@ -5182,7 +5271,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>197</v>
       </c>
@@ -5193,7 +5282,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>199</v>
       </c>
@@ -5204,7 +5293,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>201</v>
       </c>
@@ -5215,7 +5304,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>202</v>
       </c>
@@ -5226,7 +5315,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>204</v>
       </c>
@@ -5237,7 +5326,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>206</v>
       </c>
@@ -5256,9 +5345,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>176</v>
       </c>
@@ -5266,7 +5355,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>138</v>
       </c>
@@ -5274,7 +5363,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>140</v>
       </c>
@@ -5282,7 +5371,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>141</v>
       </c>
@@ -5290,7 +5379,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>143</v>
       </c>
@@ -5298,7 +5387,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>144</v>
       </c>
@@ -5306,7 +5395,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>146</v>
       </c>
@@ -5314,7 +5403,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>147</v>
       </c>
@@ -5322,7 +5411,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>148</v>
       </c>
@@ -5330,15 +5419,15 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>149</v>
       </c>
       <c r="B10" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>150</v>
       </c>
@@ -5346,7 +5435,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>152</v>
       </c>
@@ -5354,7 +5443,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>153</v>
       </c>
@@ -5362,7 +5451,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>154</v>
       </c>
@@ -5370,7 +5459,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>155</v>
       </c>
@@ -5378,7 +5467,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>156</v>
       </c>
@@ -5386,7 +5475,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>158</v>
       </c>
@@ -5394,7 +5483,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>159</v>
       </c>
@@ -5402,7 +5491,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>161</v>
       </c>
@@ -5410,7 +5499,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>162</v>
       </c>
@@ -5418,7 +5507,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>164</v>
       </c>
@@ -5426,7 +5515,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>166</v>
       </c>
@@ -5434,7 +5523,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>167</v>
       </c>
@@ -5442,7 +5531,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>168</v>
       </c>
@@ -5450,7 +5539,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>169</v>
       </c>
@@ -5458,7 +5547,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>170</v>
       </c>
@@ -5466,7 +5555,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>171</v>
       </c>
@@ -5474,7 +5563,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>172</v>
       </c>
@@ -5482,7 +5571,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>173</v>
       </c>
@@ -5490,7 +5579,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>174</v>
       </c>
@@ -5498,7 +5587,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>175</v>
       </c>
@@ -5514,13 +5603,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>310</v>
       </c>
@@ -5531,7 +5620,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>138</v>
       </c>
@@ -5542,7 +5631,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>140</v>
       </c>
@@ -5553,7 +5642,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>141</v>
       </c>
@@ -5564,7 +5653,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>144</v>
       </c>
@@ -5575,7 +5664,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>146</v>
       </c>
@@ -5586,7 +5675,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>147</v>
       </c>
@@ -5597,7 +5686,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>148</v>
       </c>
@@ -5608,7 +5697,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>149</v>
       </c>
@@ -5619,7 +5708,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>150</v>
       </c>
@@ -5630,7 +5719,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>152</v>
       </c>
@@ -5641,7 +5730,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>153</v>
       </c>
@@ -5652,7 +5741,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>154</v>
       </c>
@@ -5663,7 +5752,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>156</v>
       </c>
@@ -5674,7 +5763,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>221</v>
       </c>
@@ -5685,7 +5774,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>158</v>
       </c>
@@ -5696,7 +5785,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>224</v>
       </c>
@@ -5707,7 +5796,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>226</v>
       </c>
@@ -5718,7 +5807,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>159</v>
       </c>
@@ -5729,7 +5818,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>230</v>
       </c>
@@ -5748,12 +5837,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>310</v>
       </c>
@@ -5764,7 +5853,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>102</v>
       </c>
@@ -5775,7 +5864,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>103</v>
       </c>
@@ -5786,7 +5875,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>104</v>
       </c>
@@ -5797,7 +5886,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>105</v>
       </c>
@@ -5808,7 +5897,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>106</v>
       </c>
@@ -5819,7 +5908,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>118</v>
       </c>
@@ -5830,7 +5919,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>119</v>
       </c>
@@ -5841,7 +5930,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>120</v>
       </c>
@@ -5852,7 +5941,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>181</v>
       </c>
@@ -5863,7 +5952,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>191</v>
       </c>
@@ -5874,7 +5963,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>314</v>
       </c>
@@ -5885,7 +5974,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>317</v>
       </c>
@@ -5896,7 +5985,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>320</v>
       </c>
@@ -5907,7 +5996,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>321</v>
       </c>
@@ -5918,7 +6007,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>328</v>
       </c>
@@ -5929,7 +6018,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>401</v>
       </c>
@@ -5940,7 +6029,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>402</v>
       </c>
@@ -5951,7 +6040,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>403</v>
       </c>
@@ -5962,7 +6051,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>415</v>
       </c>
@@ -5973,7 +6062,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>610</v>
       </c>
@@ -5984,7 +6073,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>999</v>
       </c>
@@ -6003,12 +6092,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>339</v>
       </c>
@@ -6019,7 +6108,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="str">
         <f>LEFT(B2,2)</f>
         <v>11</v>
@@ -6031,7 +6120,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="str">
         <f t="shared" ref="A3:A23" si="0">LEFT(B3,2)</f>
         <v>12</v>
@@ -6043,7 +6132,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="str">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -6055,7 +6144,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="str">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -6067,7 +6156,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="str">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -6079,7 +6168,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="str">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -6091,7 +6180,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="str">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -6103,7 +6192,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="str">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -6115,7 +6204,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="str">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -6127,7 +6216,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="str">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -6139,7 +6228,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="str">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -6151,7 +6240,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="str">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -6163,7 +6252,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="str">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -6175,7 +6264,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="str">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -6187,7 +6276,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="str">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -6199,7 +6288,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="str">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -6211,7 +6300,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="str">
         <f t="shared" si="0"/>
         <v>80</v>
@@ -6223,7 +6312,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="str">
         <f t="shared" si="0"/>
         <v>81</v>
@@ -6235,7 +6324,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="str">
         <f t="shared" si="0"/>
         <v>82</v>
@@ -6247,7 +6336,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="str">
         <f t="shared" si="0"/>
         <v>83</v>
@@ -6259,7 +6348,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="str">
         <f t="shared" si="0"/>
         <v>90</v>
@@ -6271,7 +6360,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="str">
         <f t="shared" si="0"/>
         <v>MH</v>
@@ -6292,9 +6381,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>313</v>
       </c>
@@ -6314,7 +6407,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>138</v>
       </c>
@@ -6335,7 +6428,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>140</v>
       </c>
@@ -6356,7 +6449,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>257</v>
       </c>
@@ -6376,7 +6469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>141</v>
       </c>
@@ -6397,7 +6490,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>143</v>
       </c>
@@ -6417,7 +6510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>144</v>
       </c>
@@ -6438,7 +6531,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>146</v>
       </c>
@@ -6459,7 +6552,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>147</v>
       </c>
@@ -6480,7 +6573,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>148</v>
       </c>
@@ -6501,7 +6594,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>149</v>
       </c>
@@ -6515,14 +6608,14 @@
         <v>273</v>
       </c>
       <c r="E11" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="F11">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>150</v>
       </c>
@@ -6543,7 +6636,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>152</v>
       </c>
@@ -6564,7 +6657,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>153</v>
       </c>
@@ -6585,7 +6678,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>154</v>
       </c>
@@ -6606,7 +6699,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>155</v>
       </c>
@@ -6627,7 +6720,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
         <v>156</v>
       </c>
@@ -6648,7 +6741,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
         <v>158</v>
       </c>
@@ -6669,7 +6762,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>224</v>
       </c>
@@ -6690,7 +6783,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
         <v>159</v>
       </c>
@@ -6711,7 +6804,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
         <v>230</v>
       </c>
@@ -6732,7 +6825,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
         <v>292</v>
       </c>
@@ -6761,9 +6854,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="27.36328125" customWidth="1"/>
+    <col min="3" max="3" width="16.08984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>310</v>
       </c>
@@ -6774,7 +6871,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>184</v>
       </c>
@@ -6785,7 +6882,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>187</v>
       </c>
@@ -6796,7 +6893,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>189</v>
       </c>
@@ -6807,7 +6904,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>296</v>
       </c>
@@ -6818,7 +6915,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>298</v>
       </c>
@@ -6829,7 +6926,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>190</v>
       </c>
@@ -6840,7 +6937,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>300</v>
       </c>
@@ -6851,7 +6948,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>191</v>
       </c>
@@ -6862,7 +6959,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>195</v>
       </c>
@@ -6873,7 +6970,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>201</v>
       </c>
@@ -6884,7 +6981,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>206</v>
       </c>
@@ -6895,7 +6992,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>306</v>
       </c>
@@ -6906,7 +7003,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>308</v>
       </c>
@@ -6915,6 +7012,108 @@
       </c>
       <c r="C14" t="s">
         <v>151</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB14423E-3B10-4144-B6F3-4B0EE1BD3C57}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="91.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>345</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="D3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="260.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C4" t="s">
+        <v>356</v>
+      </c>
+      <c r="D4" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="146" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>347</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="C5" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>348</v>
+      </c>
+      <c r="B6" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>349</v>
+      </c>
+      <c r="B7" t="s">
+        <v>361</v>
+      </c>
+      <c r="D7" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>350</v>
+      </c>
+      <c r="B8" t="s">
+        <v>363</v>
+      </c>
+      <c r="D8" t="s">
+        <v>364</v>
       </c>
     </row>
   </sheetData>

--- a/resources/property classes.xlsx
+++ b/resources/property classes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mstern\Documents\GitHub\effective_property_tax\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abahls\Documents\GitHub\effective_property_tax\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A60A013-1040-4DEC-B76C-0C647DD12EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E95C164E-E1BB-45F5-9E3A-2A96C1DD5F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="37320" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cook" sheetId="1" r:id="rId1"/>
@@ -21,9 +21,10 @@
     <sheet name="lake 2018 later" sheetId="8" r:id="rId6"/>
     <sheet name="mchenry" sheetId="6" r:id="rId7"/>
     <sheet name="will" sheetId="7" r:id="rId8"/>
+    <sheet name="Notes" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cook!$A$1:$F$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cook!$A$1:$G$150</definedName>
     <definedName name="Export_Output_2" localSheetId="0">Cook!$A$1:$E$134</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="365">
   <si>
     <t>overall_class</t>
   </si>
@@ -1071,13 +1072,86 @@
   </si>
   <si>
     <t>land_use_code</t>
+  </si>
+  <si>
+    <t>Cook</t>
+  </si>
+  <si>
+    <t>https://prodassets.cookcountyassessor.com/s3fs-public/form_documents/classcode.pdf</t>
+  </si>
+  <si>
+    <t>https://www.cookcountyassessor.com/classifications-real-property</t>
+  </si>
+  <si>
+    <t>DuPage</t>
+  </si>
+  <si>
+    <t>Kane</t>
+  </si>
+  <si>
+    <t>Kendall</t>
+  </si>
+  <si>
+    <t>Lake</t>
+  </si>
+  <si>
+    <t>McHenry</t>
+  </si>
+  <si>
+    <t>Will</t>
+  </si>
+  <si>
+    <t>A-Apartment classed properties are 2-6 units and are residential properties.  M-Multiple classed properties are more than 6 unit apartments and are commercial properties.</t>
+  </si>
+  <si>
+    <t>email with Helen Krengel  &lt;Helen.Krengel@dupagecounty.gov&gt;</t>
+  </si>
+  <si>
+    <t>changes</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>The 0050 class is for commercial residential property.  So those parcels generally are apartment buildings</t>
+  </si>
+  <si>
+    <t>email with John Emerson &lt;EmersonJohn@KaneCountyIL.gov&gt;</t>
+  </si>
+  <si>
+    <t>0050 to commercial</t>
+  </si>
+  <si>
+    <t>0011 would just be Farm, not open space as this class only applies to property that is farmland and has buildings on it.
+0028 is used for property where land, either all or part, is in a IDNR program to conserve open space.  A property owner submits a plan and other information to the IDNR who then determines what portion of the property would qualify for this use.  
+0090 is for Tax Exempt Properties (government owned, religious, etc.) and has nothing to with railroads.  
+4500 is State Assessed Railroad. Would not fall into the Exempt category.
+5000 Railroad is local assessed railroad and would not be considered as exempt.  Local assessed railroad would be the buildings that are on the railroad right of way not the tracks themselves so this is probably you were told that it is called commercial.</t>
+  </si>
+  <si>
+    <t>Andy Nicoletti, ANicoletti@kendallcountyil.gov</t>
+  </si>
+  <si>
+    <t>relatively straightforward; can look up individual cases on the PIN search</t>
+  </si>
+  <si>
+    <t>changed 50 to commercial, based on names its clear which is which</t>
+  </si>
+  <si>
+    <t>50 to commercial</t>
+  </si>
+  <si>
+    <t>no apartment category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no change </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1111,6 +1185,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1148,25 +1228,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1447,44 +1526,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G164"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G150"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="80.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" customWidth="1"/>
+    <col min="3" max="3" width="80.6328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="3" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="str">
+      <c r="B2" t="str">
         <f>TEXT(A2,"000")</f>
         <v>000</v>
       </c>
@@ -1504,11 +1583,11 @@
         <v>177</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>100</v>
       </c>
-      <c r="B3" s="4" t="str">
+      <c r="B3" t="str">
         <f t="shared" ref="B3:B66" si="0">TEXT(A3,"000")</f>
         <v>100</v>
       </c>
@@ -1524,15 +1603,15 @@
       <c r="F3">
         <v>0.1</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>190</v>
       </c>
-      <c r="B4" s="4" t="str">
+      <c r="B4" t="str">
         <f t="shared" si="0"/>
         <v>190</v>
       </c>
@@ -1548,15 +1627,15 @@
       <c r="F4">
         <v>0.1</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>200</v>
       </c>
-      <c r="B5" s="4" t="str">
+      <c r="B5" t="str">
         <f t="shared" si="0"/>
         <v>200</v>
       </c>
@@ -1572,15 +1651,15 @@
       <c r="F5">
         <v>0.1</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>201</v>
       </c>
-      <c r="B6" s="4" t="str">
+      <c r="B6" t="str">
         <f t="shared" si="0"/>
         <v>201</v>
       </c>
@@ -1596,15 +1675,15 @@
       <c r="F6">
         <v>0.1</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>202</v>
       </c>
-      <c r="B7" s="4" t="str">
+      <c r="B7" t="str">
         <f t="shared" si="0"/>
         <v>202</v>
       </c>
@@ -1620,15 +1699,15 @@
       <c r="F7">
         <v>0.1</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>203</v>
       </c>
-      <c r="B8" s="4" t="str">
+      <c r="B8" t="str">
         <f t="shared" si="0"/>
         <v>203</v>
       </c>
@@ -1644,15 +1723,15 @@
       <c r="F8">
         <v>0.1</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>204</v>
       </c>
-      <c r="B9" s="4" t="str">
+      <c r="B9" t="str">
         <f t="shared" si="0"/>
         <v>204</v>
       </c>
@@ -1668,15 +1747,15 @@
       <c r="F9">
         <v>0.1</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>205</v>
       </c>
-      <c r="B10" s="4" t="str">
+      <c r="B10" t="str">
         <f t="shared" si="0"/>
         <v>205</v>
       </c>
@@ -1692,15 +1771,15 @@
       <c r="F10">
         <v>0.1</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>206</v>
       </c>
-      <c r="B11" s="4" t="str">
+      <c r="B11" t="str">
         <f t="shared" si="0"/>
         <v>206</v>
       </c>
@@ -1716,15 +1795,15 @@
       <c r="F11">
         <v>0.1</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>207</v>
       </c>
-      <c r="B12" s="4" t="str">
+      <c r="B12" t="str">
         <f t="shared" si="0"/>
         <v>207</v>
       </c>
@@ -1740,15 +1819,15 @@
       <c r="F12">
         <v>0.1</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>208</v>
       </c>
-      <c r="B13" s="4" t="str">
+      <c r="B13" t="str">
         <f t="shared" si="0"/>
         <v>208</v>
       </c>
@@ -1764,15 +1843,15 @@
       <c r="F13">
         <v>0.1</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>209</v>
       </c>
-      <c r="B14" s="4" t="str">
+      <c r="B14" t="str">
         <f t="shared" si="0"/>
         <v>209</v>
       </c>
@@ -1788,15 +1867,15 @@
       <c r="F14">
         <v>0.1</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>210</v>
       </c>
-      <c r="B15" s="4" t="str">
+      <c r="B15" t="str">
         <f t="shared" si="0"/>
         <v>210</v>
       </c>
@@ -1812,15 +1891,15 @@
       <c r="F15">
         <v>0.1</v>
       </c>
-      <c r="G15" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>211</v>
       </c>
-      <c r="B16" s="4" t="str">
+      <c r="B16" t="str">
         <f t="shared" si="0"/>
         <v>211</v>
       </c>
@@ -1836,15 +1915,15 @@
       <c r="F16">
         <v>0.1</v>
       </c>
-      <c r="G16" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>212</v>
       </c>
-      <c r="B17" s="4" t="str">
+      <c r="B17" t="str">
         <f t="shared" si="0"/>
         <v>212</v>
       </c>
@@ -1860,15 +1939,15 @@
       <c r="F17">
         <v>0.1</v>
       </c>
-      <c r="G17" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>213</v>
       </c>
-      <c r="B18" s="4" t="str">
+      <c r="B18" t="str">
         <f t="shared" si="0"/>
         <v>213</v>
       </c>
@@ -1884,15 +1963,15 @@
       <c r="F18">
         <v>0.1</v>
       </c>
-      <c r="G18" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+      <c r="G18" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19">
         <v>218</v>
       </c>
-      <c r="B19" s="4" t="str">
+      <c r="B19" t="str">
         <f t="shared" si="0"/>
         <v>218</v>
       </c>
@@ -1908,15 +1987,15 @@
       <c r="F19">
         <v>0.1</v>
       </c>
-      <c r="G19" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+      <c r="G19" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20">
         <v>219</v>
       </c>
-      <c r="B20" s="4" t="str">
+      <c r="B20" t="str">
         <f t="shared" si="0"/>
         <v>219</v>
       </c>
@@ -1932,15 +2011,15 @@
       <c r="F20">
         <v>0.1</v>
       </c>
-      <c r="G20" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>224</v>
       </c>
-      <c r="B21" s="4" t="str">
+      <c r="B21" t="str">
         <f t="shared" si="0"/>
         <v>224</v>
       </c>
@@ -1956,15 +2035,15 @@
       <c r="F21">
         <v>0.1</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>225</v>
       </c>
-      <c r="B22" s="4" t="str">
+      <c r="B22" t="str">
         <f t="shared" si="0"/>
         <v>225</v>
       </c>
@@ -1980,15 +2059,15 @@
       <c r="F22">
         <v>0.1</v>
       </c>
-      <c r="G22" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G22" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>234</v>
       </c>
-      <c r="B23" s="4" t="str">
+      <c r="B23" t="str">
         <f t="shared" si="0"/>
         <v>234</v>
       </c>
@@ -2004,15 +2083,15 @@
       <c r="F23">
         <v>0.1</v>
       </c>
-      <c r="G23" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G23" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>239</v>
       </c>
-      <c r="B24" s="4" t="str">
+      <c r="B24" t="str">
         <f t="shared" si="0"/>
         <v>239</v>
       </c>
@@ -2028,15 +2107,15 @@
       <c r="F24">
         <v>0.1</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>241</v>
       </c>
-      <c r="B25" s="4" t="str">
+      <c r="B25" t="str">
         <f t="shared" si="0"/>
         <v>241</v>
       </c>
@@ -2052,15 +2131,15 @@
       <c r="F25">
         <v>0.1</v>
       </c>
-      <c r="G25" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G25" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>278</v>
       </c>
-      <c r="B26" s="4" t="str">
+      <c r="B26" t="str">
         <f t="shared" si="0"/>
         <v>278</v>
       </c>
@@ -2076,15 +2155,15 @@
       <c r="F26">
         <v>0.1</v>
       </c>
-      <c r="G26" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G26" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>288</v>
       </c>
-      <c r="B27" s="4" t="str">
+      <c r="B27" t="str">
         <f t="shared" si="0"/>
         <v>288</v>
       </c>
@@ -2100,15 +2179,15 @@
       <c r="F27">
         <v>0.1</v>
       </c>
-      <c r="G27" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G27" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>290</v>
       </c>
-      <c r="B28" s="4" t="str">
+      <c r="B28" t="str">
         <f t="shared" si="0"/>
         <v>290</v>
       </c>
@@ -2124,15 +2203,15 @@
       <c r="F28">
         <v>0.1</v>
       </c>
-      <c r="G28" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G28" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>295</v>
       </c>
-      <c r="B29" s="4" t="str">
+      <c r="B29" t="str">
         <f t="shared" si="0"/>
         <v>295</v>
       </c>
@@ -2148,15 +2227,15 @@
       <c r="F29">
         <v>0.1</v>
       </c>
-      <c r="G29" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G29" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>297</v>
       </c>
-      <c r="B30" s="4" t="str">
+      <c r="B30" t="str">
         <f t="shared" si="0"/>
         <v>297</v>
       </c>
@@ -2172,15 +2251,15 @@
       <c r="F30">
         <v>0.1</v>
       </c>
-      <c r="G30" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G30" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>299</v>
       </c>
-      <c r="B31" s="4" t="str">
+      <c r="B31" t="str">
         <f t="shared" si="0"/>
         <v>299</v>
       </c>
@@ -2196,15 +2275,15 @@
       <c r="F31">
         <v>0.1</v>
       </c>
-      <c r="G31" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+      <c r="G31" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32">
         <v>300</v>
       </c>
-      <c r="B32" s="4" t="str">
+      <c r="B32" t="str">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
@@ -2220,15 +2299,15 @@
       <c r="F32">
         <v>0.1</v>
       </c>
-      <c r="G32" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G32" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>301</v>
       </c>
-      <c r="B33" s="4" t="str">
+      <c r="B33" t="str">
         <f t="shared" si="0"/>
         <v>301</v>
       </c>
@@ -2244,15 +2323,15 @@
       <c r="F33">
         <v>0.1</v>
       </c>
-      <c r="G33" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G33" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>313</v>
       </c>
-      <c r="B34" s="4" t="str">
+      <c r="B34" t="str">
         <f t="shared" si="0"/>
         <v>313</v>
       </c>
@@ -2268,15 +2347,15 @@
       <c r="F34">
         <v>0.1</v>
       </c>
-      <c r="G34" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G34" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>314</v>
       </c>
-      <c r="B35" s="4" t="str">
+      <c r="B35" t="str">
         <f t="shared" si="0"/>
         <v>314</v>
       </c>
@@ -2292,15 +2371,15 @@
       <c r="F35">
         <v>0.1</v>
       </c>
-      <c r="G35" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G35" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>315</v>
       </c>
-      <c r="B36" s="4" t="str">
+      <c r="B36" t="str">
         <f t="shared" si="0"/>
         <v>315</v>
       </c>
@@ -2316,15 +2395,15 @@
       <c r="F36">
         <v>0.1</v>
       </c>
-      <c r="G36" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G36" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>318</v>
       </c>
-      <c r="B37" s="4" t="str">
+      <c r="B37" t="str">
         <f t="shared" si="0"/>
         <v>318</v>
       </c>
@@ -2340,15 +2419,15 @@
       <c r="F37">
         <v>0.1</v>
       </c>
-      <c r="G37" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
+      <c r="G37" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38">
         <v>319</v>
       </c>
-      <c r="B38" s="4" t="str">
+      <c r="B38" t="str">
         <f t="shared" si="0"/>
         <v>319</v>
       </c>
@@ -2364,15 +2443,15 @@
       <c r="F38">
         <v>0.1</v>
       </c>
-      <c r="G38" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G38" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>390</v>
       </c>
-      <c r="B39" s="4" t="str">
+      <c r="B39" t="str">
         <f t="shared" si="0"/>
         <v>390</v>
       </c>
@@ -2388,15 +2467,15 @@
       <c r="F39">
         <v>0.1</v>
       </c>
-      <c r="G39" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G39" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>391</v>
       </c>
-      <c r="B40" s="4" t="str">
+      <c r="B40" t="str">
         <f t="shared" si="0"/>
         <v>391</v>
       </c>
@@ -2412,15 +2491,15 @@
       <c r="F40">
         <v>0.1</v>
       </c>
-      <c r="G40" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G40" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>396</v>
       </c>
-      <c r="B41" s="4" t="str">
+      <c r="B41" t="str">
         <f t="shared" si="0"/>
         <v>396</v>
       </c>
@@ -2436,15 +2515,15 @@
       <c r="F41">
         <v>0.1</v>
       </c>
-      <c r="G41" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G41" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>397</v>
       </c>
-      <c r="B42" s="4" t="str">
+      <c r="B42" t="str">
         <f t="shared" si="0"/>
         <v>397</v>
       </c>
@@ -2460,15 +2539,15 @@
       <c r="F42">
         <v>0.1</v>
       </c>
-      <c r="G42" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G42" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>399</v>
       </c>
-      <c r="B43" s="4" t="str">
+      <c r="B43" t="str">
         <f t="shared" si="0"/>
         <v>399</v>
       </c>
@@ -2484,15 +2563,15 @@
       <c r="F43">
         <v>0.1</v>
       </c>
-      <c r="G43" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G43" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>401</v>
       </c>
-      <c r="B44" s="4" t="str">
+      <c r="B44" t="str">
         <f t="shared" si="0"/>
         <v>401</v>
       </c>
@@ -2508,15 +2587,15 @@
       <c r="F44">
         <v>0.2</v>
       </c>
-      <c r="G44" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G44" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>417</v>
       </c>
-      <c r="B45" s="4" t="str">
+      <c r="B45" t="str">
         <f t="shared" si="0"/>
         <v>417</v>
       </c>
@@ -2526,21 +2605,21 @@
       <c r="D45">
         <v>4</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="E45" t="s">
         <v>179</v>
       </c>
-      <c r="F45" s="4">
+      <c r="F45">
         <v>0.2</v>
       </c>
-      <c r="G45" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G45" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>418</v>
       </c>
-      <c r="B46" s="4" t="str">
+      <c r="B46" t="str">
         <f t="shared" si="0"/>
         <v>418</v>
       </c>
@@ -2550,21 +2629,21 @@
       <c r="D46">
         <v>4</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" t="s">
         <v>179</v>
       </c>
-      <c r="F46" s="4">
+      <c r="F46">
         <v>0.2</v>
       </c>
-      <c r="G46" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G46" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>422</v>
       </c>
-      <c r="B47" s="4" t="str">
+      <c r="B47" t="str">
         <f t="shared" si="0"/>
         <v>422</v>
       </c>
@@ -2574,21 +2653,21 @@
       <c r="D47">
         <v>4</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E47" t="s">
         <v>179</v>
       </c>
-      <c r="F47" s="4">
+      <c r="F47">
         <v>0.2</v>
       </c>
-      <c r="G47" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="1">
+      <c r="G47" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48">
         <v>427</v>
       </c>
-      <c r="B48" s="4" t="str">
+      <c r="B48" t="str">
         <f t="shared" si="0"/>
         <v>427</v>
       </c>
@@ -2598,21 +2677,21 @@
       <c r="D48">
         <v>4</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="E48" t="s">
         <v>179</v>
       </c>
-      <c r="F48" s="4">
+      <c r="F48">
         <v>0.2</v>
       </c>
-      <c r="G48" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G48" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>428</v>
       </c>
-      <c r="B49" s="4" t="str">
+      <c r="B49" t="str">
         <f t="shared" si="0"/>
         <v>428</v>
       </c>
@@ -2622,21 +2701,21 @@
       <c r="D49">
         <v>4</v>
       </c>
-      <c r="E49" s="4" t="s">
+      <c r="E49" t="s">
         <v>179</v>
       </c>
-      <c r="F49" s="4">
+      <c r="F49">
         <v>0.2</v>
       </c>
-      <c r="G49" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G49" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>430</v>
       </c>
-      <c r="B50" s="4" t="str">
+      <c r="B50" t="str">
         <f t="shared" si="0"/>
         <v>430</v>
       </c>
@@ -2646,21 +2725,21 @@
       <c r="D50">
         <v>4</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="E50" t="s">
         <v>179</v>
       </c>
-      <c r="F50" s="4">
+      <c r="F50">
         <v>0.2</v>
       </c>
-      <c r="G50" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G50" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>435</v>
       </c>
-      <c r="B51" s="4" t="str">
+      <c r="B51" t="str">
         <f t="shared" si="0"/>
         <v>435</v>
       </c>
@@ -2670,21 +2749,21 @@
       <c r="D51">
         <v>4</v>
       </c>
-      <c r="E51" s="4" t="s">
+      <c r="E51" t="s">
         <v>179</v>
       </c>
-      <c r="F51" s="4">
+      <c r="F51">
         <v>0.2</v>
       </c>
-      <c r="G51" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G51" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>480</v>
       </c>
-      <c r="B52" s="4" t="str">
+      <c r="B52" t="str">
         <f t="shared" si="0"/>
         <v>480</v>
       </c>
@@ -2694,21 +2773,21 @@
       <c r="D52">
         <v>4</v>
       </c>
-      <c r="E52" s="4" t="s">
+      <c r="E52" t="s">
         <v>179</v>
       </c>
-      <c r="F52" s="4">
+      <c r="F52">
         <v>0.2</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="G52" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>483</v>
       </c>
-      <c r="B53" s="4" t="str">
+      <c r="B53" t="str">
         <f t="shared" si="0"/>
         <v>483</v>
       </c>
@@ -2718,21 +2797,21 @@
       <c r="D53">
         <v>4</v>
       </c>
-      <c r="E53" s="4" t="s">
+      <c r="E53" t="s">
         <v>179</v>
       </c>
-      <c r="F53" s="4">
+      <c r="F53">
         <v>0.2</v>
       </c>
-      <c r="G53" s="4" t="s">
+      <c r="G53" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>490</v>
       </c>
-      <c r="B54" s="4" t="str">
+      <c r="B54" t="str">
         <f t="shared" si="0"/>
         <v>490</v>
       </c>
@@ -2742,21 +2821,21 @@
       <c r="D54">
         <v>4</v>
       </c>
-      <c r="E54" s="4" t="s">
+      <c r="E54" t="s">
         <v>179</v>
       </c>
-      <c r="F54" s="4">
+      <c r="F54">
         <v>0.2</v>
       </c>
-      <c r="G54" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G54" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>491</v>
       </c>
-      <c r="B55" s="4" t="str">
+      <c r="B55" t="str">
         <f t="shared" si="0"/>
         <v>491</v>
       </c>
@@ -2766,21 +2845,21 @@
       <c r="D55">
         <v>4</v>
       </c>
-      <c r="E55" s="4" t="s">
+      <c r="E55" t="s">
         <v>179</v>
       </c>
-      <c r="F55" s="4">
+      <c r="F55">
         <v>0.2</v>
       </c>
-      <c r="G55" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G55" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>492</v>
       </c>
-      <c r="B56" s="4" t="str">
+      <c r="B56" t="str">
         <f t="shared" si="0"/>
         <v>492</v>
       </c>
@@ -2790,21 +2869,21 @@
       <c r="D56">
         <v>4</v>
       </c>
-      <c r="E56" s="4" t="s">
+      <c r="E56" t="s">
         <v>179</v>
       </c>
-      <c r="F56" s="4">
+      <c r="F56">
         <v>0.2</v>
       </c>
-      <c r="G56" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G56" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>493</v>
       </c>
-      <c r="B57" s="4" t="str">
+      <c r="B57" t="str">
         <f t="shared" si="0"/>
         <v>493</v>
       </c>
@@ -2814,21 +2893,21 @@
       <c r="D57">
         <v>4</v>
       </c>
-      <c r="E57" s="4" t="s">
+      <c r="E57" t="s">
         <v>179</v>
       </c>
-      <c r="F57" s="4">
+      <c r="F57">
         <v>0.2</v>
       </c>
-      <c r="G57" s="4" t="s">
+      <c r="G57" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>497</v>
       </c>
-      <c r="B58" s="4" t="str">
+      <c r="B58" t="str">
         <f t="shared" si="0"/>
         <v>497</v>
       </c>
@@ -2838,21 +2917,21 @@
       <c r="D58">
         <v>4</v>
       </c>
-      <c r="E58" s="4" t="s">
+      <c r="E58" t="s">
         <v>179</v>
       </c>
-      <c r="F58" s="4">
+      <c r="F58">
         <v>0.2</v>
       </c>
-      <c r="G58" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G58" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>499</v>
       </c>
-      <c r="B59" s="4" t="str">
+      <c r="B59" t="str">
         <f t="shared" si="0"/>
         <v>499</v>
       </c>
@@ -2862,21 +2941,21 @@
       <c r="D59">
         <v>4</v>
       </c>
-      <c r="E59" s="4" t="s">
+      <c r="E59" t="s">
         <v>179</v>
       </c>
-      <c r="F59" s="4">
+      <c r="F59">
         <v>0.2</v>
       </c>
-      <c r="G59" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G59" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>500</v>
       </c>
-      <c r="B60" s="4" t="str">
+      <c r="B60" t="str">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
@@ -2892,15 +2971,15 @@
       <c r="F60">
         <v>0.25</v>
       </c>
-      <c r="G60" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G60" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>501</v>
       </c>
-      <c r="B61" s="4" t="str">
+      <c r="B61" t="str">
         <f t="shared" si="0"/>
         <v>501</v>
       </c>
@@ -2916,15 +2995,15 @@
       <c r="F61">
         <v>0.25</v>
       </c>
-      <c r="G61" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G61" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>516</v>
       </c>
-      <c r="B62" s="4" t="str">
+      <c r="B62" t="str">
         <f t="shared" si="0"/>
         <v>516</v>
       </c>
@@ -2940,15 +3019,15 @@
       <c r="F62">
         <v>0.25</v>
       </c>
-      <c r="G62" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G62" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>517</v>
       </c>
-      <c r="B63" s="4" t="str">
+      <c r="B63" t="str">
         <f t="shared" si="0"/>
         <v>517</v>
       </c>
@@ -2964,15 +3043,15 @@
       <c r="F63">
         <v>0.25</v>
       </c>
-      <c r="G63" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G63" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>522</v>
       </c>
-      <c r="B64" s="4" t="str">
+      <c r="B64" t="str">
         <f t="shared" si="0"/>
         <v>522</v>
       </c>
@@ -2988,15 +3067,15 @@
       <c r="F64">
         <v>0.25</v>
       </c>
-      <c r="G64" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G64" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>523</v>
       </c>
-      <c r="B65" s="4" t="str">
+      <c r="B65" t="str">
         <f t="shared" si="0"/>
         <v>523</v>
       </c>
@@ -3012,15 +3091,15 @@
       <c r="F65">
         <v>0.25</v>
       </c>
-      <c r="G65" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G65" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>526</v>
       </c>
-      <c r="B66" s="4" t="str">
+      <c r="B66" t="str">
         <f t="shared" si="0"/>
         <v>526</v>
       </c>
@@ -3036,15 +3115,15 @@
       <c r="F66">
         <v>0.25</v>
       </c>
-      <c r="G66" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G66" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>527</v>
       </c>
-      <c r="B67" s="4" t="str">
+      <c r="B67" t="str">
         <f t="shared" ref="B67:B130" si="1">TEXT(A67,"000")</f>
         <v>527</v>
       </c>
@@ -3060,15 +3139,15 @@
       <c r="F67">
         <v>0.25</v>
       </c>
-      <c r="G67" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G67" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>528</v>
       </c>
-      <c r="B68" s="4" t="str">
+      <c r="B68" t="str">
         <f t="shared" si="1"/>
         <v>528</v>
       </c>
@@ -3084,15 +3163,15 @@
       <c r="F68">
         <v>0.25</v>
       </c>
-      <c r="G68" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G68" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>529</v>
       </c>
-      <c r="B69" s="4" t="str">
+      <c r="B69" t="str">
         <f t="shared" si="1"/>
         <v>529</v>
       </c>
@@ -3108,15 +3187,15 @@
       <c r="F69">
         <v>0.25</v>
       </c>
-      <c r="G69" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G69" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>530</v>
       </c>
-      <c r="B70" s="4" t="str">
+      <c r="B70" t="str">
         <f t="shared" si="1"/>
         <v>530</v>
       </c>
@@ -3132,15 +3211,15 @@
       <c r="F70">
         <v>0.25</v>
       </c>
-      <c r="G70" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G70" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>531</v>
       </c>
-      <c r="B71" s="4" t="str">
+      <c r="B71" t="str">
         <f t="shared" si="1"/>
         <v>531</v>
       </c>
@@ -3156,15 +3235,15 @@
       <c r="F71">
         <v>0.25</v>
       </c>
-      <c r="G71" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G71" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>532</v>
       </c>
-      <c r="B72" s="4" t="str">
+      <c r="B72" t="str">
         <f t="shared" si="1"/>
         <v>532</v>
       </c>
@@ -3180,15 +3259,15 @@
       <c r="F72">
         <v>0.25</v>
       </c>
-      <c r="G72" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G72" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>533</v>
       </c>
-      <c r="B73" s="4" t="str">
+      <c r="B73" t="str">
         <f t="shared" si="1"/>
         <v>533</v>
       </c>
@@ -3204,15 +3283,15 @@
       <c r="F73">
         <v>0.25</v>
       </c>
-      <c r="G73" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G73" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>535</v>
       </c>
-      <c r="B74" s="4" t="str">
+      <c r="B74" t="str">
         <f t="shared" si="1"/>
         <v>535</v>
       </c>
@@ -3228,15 +3307,15 @@
       <c r="F74">
         <v>0.25</v>
       </c>
-      <c r="G74" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G74" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>550</v>
       </c>
-      <c r="B75" s="4" t="str">
+      <c r="B75" t="str">
         <f t="shared" si="1"/>
         <v>550</v>
       </c>
@@ -3252,15 +3331,15 @@
       <c r="F75">
         <v>0.25</v>
       </c>
-      <c r="G75" s="4" t="s">
+      <c r="G75" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>580</v>
       </c>
-      <c r="B76" s="4" t="str">
+      <c r="B76" t="str">
         <f t="shared" si="1"/>
         <v>580</v>
       </c>
@@ -3276,15 +3355,15 @@
       <c r="F76">
         <v>0.25</v>
       </c>
-      <c r="G76" s="4" t="s">
+      <c r="G76" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>581</v>
       </c>
-      <c r="B77" s="4" t="str">
+      <c r="B77" t="str">
         <f t="shared" si="1"/>
         <v>581</v>
       </c>
@@ -3300,15 +3379,15 @@
       <c r="F77">
         <v>0.25</v>
       </c>
-      <c r="G77" s="4" t="s">
+      <c r="G77" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>583</v>
       </c>
-      <c r="B78" s="4" t="str">
+      <c r="B78" t="str">
         <f t="shared" si="1"/>
         <v>583</v>
       </c>
@@ -3324,15 +3403,15 @@
       <c r="F78">
         <v>0.25</v>
       </c>
-      <c r="G78" s="4" t="s">
+      <c r="G78" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>587</v>
       </c>
-      <c r="B79" s="4" t="str">
+      <c r="B79" t="str">
         <f t="shared" si="1"/>
         <v>587</v>
       </c>
@@ -3348,15 +3427,15 @@
       <c r="F79">
         <v>0.25</v>
       </c>
-      <c r="G79" s="4" t="s">
+      <c r="G79" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>589</v>
       </c>
-      <c r="B80" s="4" t="str">
+      <c r="B80" t="str">
         <f t="shared" si="1"/>
         <v>589</v>
       </c>
@@ -3372,15 +3451,15 @@
       <c r="F80">
         <v>0.25</v>
       </c>
-      <c r="G80" s="4" t="s">
+      <c r="G80" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>590</v>
       </c>
-      <c r="B81" s="4" t="str">
+      <c r="B81" t="str">
         <f t="shared" si="1"/>
         <v>590</v>
       </c>
@@ -3396,15 +3475,15 @@
       <c r="F81">
         <v>0.25</v>
       </c>
-      <c r="G81" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G81" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>591</v>
       </c>
-      <c r="B82" s="4" t="str">
+      <c r="B82" t="str">
         <f t="shared" si="1"/>
         <v>591</v>
       </c>
@@ -3420,15 +3499,15 @@
       <c r="F82">
         <v>0.25</v>
       </c>
-      <c r="G82" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G82" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>592</v>
       </c>
-      <c r="B83" s="4" t="str">
+      <c r="B83" t="str">
         <f t="shared" si="1"/>
         <v>592</v>
       </c>
@@ -3444,15 +3523,15 @@
       <c r="F83">
         <v>0.25</v>
       </c>
-      <c r="G83" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G83" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>593</v>
       </c>
-      <c r="B84" s="4" t="str">
+      <c r="B84" t="str">
         <f t="shared" si="1"/>
         <v>593</v>
       </c>
@@ -3468,15 +3547,15 @@
       <c r="F84">
         <v>0.25</v>
       </c>
-      <c r="G84" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G84" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>597</v>
       </c>
-      <c r="B85" s="4" t="str">
+      <c r="B85" t="str">
         <f t="shared" si="1"/>
         <v>597</v>
       </c>
@@ -3492,15 +3571,15 @@
       <c r="F85">
         <v>0.25</v>
       </c>
-      <c r="G85" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G85" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>599</v>
       </c>
-      <c r="B86" s="4" t="str">
+      <c r="B86" t="str">
         <f t="shared" si="1"/>
         <v>599</v>
       </c>
@@ -3516,15 +3595,15 @@
       <c r="F86">
         <v>0.25</v>
       </c>
-      <c r="G86" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G86" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>637</v>
       </c>
-      <c r="B87" s="4" t="str">
+      <c r="B87" t="str">
         <f t="shared" si="1"/>
         <v>637</v>
       </c>
@@ -3540,15 +3619,15 @@
       <c r="F87">
         <v>0.1</v>
       </c>
-      <c r="G87" s="4" t="s">
+      <c r="G87" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>638</v>
       </c>
-      <c r="B88" s="4" t="str">
+      <c r="B88" t="str">
         <f t="shared" si="1"/>
         <v>638</v>
       </c>
@@ -3564,15 +3643,15 @@
       <c r="F88">
         <v>0.1</v>
       </c>
-      <c r="G88" s="4" t="s">
+      <c r="G88" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>654</v>
       </c>
-      <c r="B89" s="4" t="str">
+      <c r="B89" t="str">
         <f t="shared" si="1"/>
         <v>654</v>
       </c>
@@ -3588,15 +3667,15 @@
       <c r="F89">
         <v>0.1</v>
       </c>
-      <c r="G89" s="4" t="s">
+      <c r="G89" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>655</v>
       </c>
-      <c r="B90" s="4" t="str">
+      <c r="B90" t="str">
         <f t="shared" si="1"/>
         <v>655</v>
       </c>
@@ -3612,15 +3691,15 @@
       <c r="F90">
         <v>0.1</v>
       </c>
-      <c r="G90" s="4" t="s">
+      <c r="G90" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>663</v>
       </c>
-      <c r="B91" s="4" t="str">
+      <c r="B91" t="str">
         <f t="shared" si="1"/>
         <v>663</v>
       </c>
@@ -3636,15 +3715,15 @@
       <c r="F91">
         <v>0.108333</v>
       </c>
-      <c r="G91" s="4" t="s">
+      <c r="G91" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>668</v>
       </c>
-      <c r="B92" s="4" t="str">
+      <c r="B92" t="str">
         <f t="shared" si="1"/>
         <v>668</v>
       </c>
@@ -3660,15 +3739,15 @@
       <c r="F92">
         <v>0.1</v>
       </c>
-      <c r="G92" s="4" t="s">
+      <c r="G92" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>670</v>
       </c>
-      <c r="B93" s="4" t="str">
+      <c r="B93" t="str">
         <f t="shared" si="1"/>
         <v>670</v>
       </c>
@@ -3684,15 +3763,15 @@
       <c r="F93">
         <v>0.108333</v>
       </c>
-      <c r="G93" s="4" t="s">
+      <c r="G93" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>671</v>
       </c>
-      <c r="B94" s="4" t="str">
+      <c r="B94" t="str">
         <f t="shared" si="1"/>
         <v>671</v>
       </c>
@@ -3708,15 +3787,15 @@
       <c r="F94">
         <v>0.108333</v>
       </c>
-      <c r="G94" s="4" t="s">
+      <c r="G94" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>673</v>
       </c>
-      <c r="B95" s="4" t="str">
+      <c r="B95" t="str">
         <f t="shared" si="1"/>
         <v>673</v>
       </c>
@@ -3732,15 +3811,15 @@
       <c r="F95">
         <v>0.108333</v>
       </c>
-      <c r="G95" s="4" t="s">
+      <c r="G95" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>677</v>
       </c>
-      <c r="B96" s="4" t="str">
+      <c r="B96" t="str">
         <f t="shared" si="1"/>
         <v>677</v>
       </c>
@@ -3756,15 +3835,15 @@
       <c r="F96">
         <v>0.108333</v>
       </c>
-      <c r="G96" s="4" t="s">
+      <c r="G96" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>679</v>
       </c>
-      <c r="B97" s="4" t="str">
+      <c r="B97" t="str">
         <f t="shared" si="1"/>
         <v>679</v>
       </c>
@@ -3780,15 +3859,15 @@
       <c r="F97">
         <v>0.108333</v>
       </c>
-      <c r="G97" s="4" t="s">
+      <c r="G97" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>680</v>
       </c>
-      <c r="B98" s="4" t="str">
+      <c r="B98" t="str">
         <f t="shared" si="1"/>
         <v>680</v>
       </c>
@@ -3804,15 +3883,15 @@
       <c r="F98">
         <v>0.2</v>
       </c>
-      <c r="G98" s="4" t="s">
+      <c r="G98" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="1">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A99">
         <v>683</v>
       </c>
-      <c r="B99" s="4" t="str">
+      <c r="B99" t="str">
         <f t="shared" si="1"/>
         <v>683</v>
       </c>
@@ -3828,15 +3907,15 @@
       <c r="F99">
         <v>0.2</v>
       </c>
-      <c r="G99" s="4" t="s">
+      <c r="G99" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="1">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A100">
         <v>687</v>
       </c>
-      <c r="B100" s="4" t="str">
+      <c r="B100" t="str">
         <f t="shared" si="1"/>
         <v>687</v>
       </c>
@@ -3852,15 +3931,15 @@
       <c r="F100">
         <v>0.2</v>
       </c>
-      <c r="G100" s="4" t="s">
+      <c r="G100" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>693</v>
       </c>
-      <c r="B101" s="4" t="str">
+      <c r="B101" t="str">
         <f t="shared" si="1"/>
         <v>693</v>
       </c>
@@ -3876,15 +3955,15 @@
       <c r="F101">
         <v>0.2</v>
       </c>
-      <c r="G101" s="4" t="s">
+      <c r="G101" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>717</v>
       </c>
-      <c r="B102" s="4" t="str">
+      <c r="B102" t="str">
         <f t="shared" si="1"/>
         <v>717</v>
       </c>
@@ -3900,15 +3979,15 @@
       <c r="F102">
         <v>0.101743</v>
       </c>
-      <c r="G102" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="1">
+      <c r="G102" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A103">
         <v>722</v>
       </c>
-      <c r="B103" s="4" t="str">
+      <c r="B103" t="str">
         <f t="shared" si="1"/>
         <v>722</v>
       </c>
@@ -3924,15 +4003,15 @@
       <c r="F103">
         <v>0.101743</v>
       </c>
-      <c r="G103" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G103" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>723</v>
       </c>
-      <c r="B104" s="4" t="str">
+      <c r="B104" t="str">
         <f t="shared" si="1"/>
         <v>723</v>
       </c>
@@ -3948,15 +4027,15 @@
       <c r="F104">
         <v>0.101743</v>
       </c>
-      <c r="G104" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G104" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>728</v>
       </c>
-      <c r="B105" s="4" t="str">
+      <c r="B105" t="str">
         <f t="shared" si="1"/>
         <v>728</v>
       </c>
@@ -3972,15 +4051,15 @@
       <c r="F105">
         <v>0.101743</v>
       </c>
-      <c r="G105" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G105" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>729</v>
       </c>
-      <c r="B106" s="4" t="str">
+      <c r="B106" t="str">
         <f t="shared" si="1"/>
         <v>729</v>
       </c>
@@ -3996,15 +4075,15 @@
       <c r="F106">
         <v>0.101743</v>
       </c>
-      <c r="G106" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="1">
+      <c r="G106" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A107">
         <v>730</v>
       </c>
-      <c r="B107" s="4" t="str">
+      <c r="B107" t="str">
         <f t="shared" si="1"/>
         <v>730</v>
       </c>
@@ -4020,15 +4099,15 @@
       <c r="F107">
         <v>0.101743</v>
       </c>
-      <c r="G107" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="1">
+      <c r="G107" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A108">
         <v>731</v>
       </c>
-      <c r="B108" s="4" t="str">
+      <c r="B108" t="str">
         <f t="shared" si="1"/>
         <v>731</v>
       </c>
@@ -4044,15 +4123,15 @@
       <c r="F108">
         <v>0.101743</v>
       </c>
-      <c r="G108" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G108" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>746</v>
       </c>
-      <c r="B109" s="4" t="str">
+      <c r="B109" t="str">
         <f t="shared" si="1"/>
         <v>746</v>
       </c>
@@ -4068,15 +4147,15 @@
       <c r="F109">
         <v>0.101743</v>
       </c>
-      <c r="G109" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A110" s="1">
+      <c r="G109" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A110">
         <v>748</v>
       </c>
-      <c r="B110" s="4" t="str">
+      <c r="B110" t="str">
         <f t="shared" si="1"/>
         <v>748</v>
       </c>
@@ -4092,15 +4171,15 @@
       <c r="F110">
         <v>0.101743</v>
       </c>
-      <c r="G110" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G110" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>752</v>
       </c>
-      <c r="B111" s="4" t="str">
+      <c r="B111" t="str">
         <f t="shared" si="1"/>
         <v>752</v>
       </c>
@@ -4116,15 +4195,15 @@
       <c r="F111">
         <v>0.101743</v>
       </c>
-      <c r="G111" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A112" s="1">
+      <c r="G111" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A112">
         <v>760</v>
       </c>
-      <c r="B112" s="4" t="str">
+      <c r="B112" t="str">
         <f t="shared" si="1"/>
         <v>760</v>
       </c>
@@ -4140,15 +4219,15 @@
       <c r="F112">
         <v>0.101743</v>
       </c>
-      <c r="G112" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113" s="1">
+      <c r="G112" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A113">
         <v>765</v>
       </c>
-      <c r="B113" s="4" t="str">
+      <c r="B113" t="str">
         <f t="shared" si="1"/>
         <v>765</v>
       </c>
@@ -4164,15 +4243,15 @@
       <c r="F113">
         <v>0.101743</v>
       </c>
-      <c r="G113" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A114" s="1">
+      <c r="G113" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A114">
         <v>767</v>
       </c>
-      <c r="B114" s="4" t="str">
+      <c r="B114" t="str">
         <f t="shared" si="1"/>
         <v>767</v>
       </c>
@@ -4188,15 +4267,15 @@
       <c r="F114">
         <v>0.101743</v>
       </c>
-      <c r="G114" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G114" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>774</v>
       </c>
-      <c r="B115" s="4" t="str">
+      <c r="B115" t="str">
         <f t="shared" si="1"/>
         <v>774</v>
       </c>
@@ -4212,15 +4291,15 @@
       <c r="F115">
         <v>0.101743</v>
       </c>
-      <c r="G115" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G115" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>790</v>
       </c>
-      <c r="B116" s="4" t="str">
+      <c r="B116" t="str">
         <f t="shared" si="1"/>
         <v>790</v>
       </c>
@@ -4236,15 +4315,15 @@
       <c r="F116">
         <v>0.101743</v>
       </c>
-      <c r="G116" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G116" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>791</v>
       </c>
-      <c r="B117" s="4" t="str">
+      <c r="B117" t="str">
         <f t="shared" si="1"/>
         <v>791</v>
       </c>
@@ -4260,15 +4339,15 @@
       <c r="F117">
         <v>0.101743</v>
       </c>
-      <c r="G117" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G117" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>792</v>
       </c>
-      <c r="B118" s="4" t="str">
+      <c r="B118" t="str">
         <f t="shared" si="1"/>
         <v>792</v>
       </c>
@@ -4284,15 +4363,15 @@
       <c r="F118">
         <v>0.101743</v>
       </c>
-      <c r="G118" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G118" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>797</v>
       </c>
-      <c r="B119" s="4" t="str">
+      <c r="B119" t="str">
         <f t="shared" si="1"/>
         <v>797</v>
       </c>
@@ -4308,15 +4387,15 @@
       <c r="F119">
         <v>0.101743</v>
       </c>
-      <c r="G119" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A120" s="1">
+      <c r="G119" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A120">
         <v>799</v>
       </c>
-      <c r="B120" s="4" t="str">
+      <c r="B120" t="str">
         <f t="shared" si="1"/>
         <v>799</v>
       </c>
@@ -4332,15 +4411,15 @@
       <c r="F120">
         <v>0.101743</v>
       </c>
-      <c r="G120" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G120" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>801</v>
       </c>
-      <c r="B121" s="4" t="str">
+      <c r="B121" t="str">
         <f t="shared" si="1"/>
         <v>801</v>
       </c>
@@ -4356,15 +4435,15 @@
       <c r="F121">
         <v>0.101743</v>
       </c>
-      <c r="G121" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G121" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>817</v>
       </c>
-      <c r="B122" s="4" t="str">
+      <c r="B122" t="str">
         <f t="shared" si="1"/>
         <v>817</v>
       </c>
@@ -4380,15 +4459,15 @@
       <c r="F122">
         <v>0.101743</v>
       </c>
-      <c r="G122" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G122" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>823</v>
       </c>
-      <c r="B123" s="4" t="str">
+      <c r="B123" t="str">
         <f t="shared" si="1"/>
         <v>823</v>
       </c>
@@ -4404,15 +4483,15 @@
       <c r="F123">
         <v>0.101743</v>
       </c>
-      <c r="G123" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G123" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>827</v>
       </c>
-      <c r="B124" s="4" t="str">
+      <c r="B124" t="str">
         <f t="shared" si="1"/>
         <v>827</v>
       </c>
@@ -4428,15 +4507,15 @@
       <c r="F124">
         <v>0.101743</v>
       </c>
-      <c r="G124" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G124" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>828</v>
       </c>
-      <c r="B125" s="4" t="str">
+      <c r="B125" t="str">
         <f t="shared" si="1"/>
         <v>828</v>
       </c>
@@ -4452,15 +4531,15 @@
       <c r="F125">
         <v>0.101743</v>
       </c>
-      <c r="G125" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G125" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>829</v>
       </c>
-      <c r="B126" s="4" t="str">
+      <c r="B126" t="str">
         <f t="shared" si="1"/>
         <v>829</v>
       </c>
@@ -4476,15 +4555,15 @@
       <c r="F126">
         <v>0.101743</v>
       </c>
-      <c r="G126" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G126" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>830</v>
       </c>
-      <c r="B127" s="4" t="str">
+      <c r="B127" t="str">
         <f t="shared" si="1"/>
         <v>830</v>
       </c>
@@ -4500,15 +4579,15 @@
       <c r="F127">
         <v>0.101743</v>
       </c>
-      <c r="G127" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G127" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>831</v>
       </c>
-      <c r="B128" s="4" t="str">
+      <c r="B128" t="str">
         <f t="shared" si="1"/>
         <v>831</v>
       </c>
@@ -4524,15 +4603,15 @@
       <c r="F128">
         <v>0.101743</v>
       </c>
-      <c r="G128" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G128" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>833</v>
       </c>
-      <c r="B129" s="4" t="str">
+      <c r="B129" t="str">
         <f t="shared" si="1"/>
         <v>833</v>
       </c>
@@ -4548,15 +4627,15 @@
       <c r="F129">
         <v>0.101743</v>
       </c>
-      <c r="G129" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G129" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>880</v>
       </c>
-      <c r="B130" s="4" t="str">
+      <c r="B130" t="str">
         <f t="shared" si="1"/>
         <v>880</v>
       </c>
@@ -4572,15 +4651,15 @@
       <c r="F130">
         <v>0.101743</v>
       </c>
-      <c r="G130" s="4" t="s">
+      <c r="G130" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A131" s="1">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A131">
         <v>881</v>
       </c>
-      <c r="B131" s="4" t="str">
+      <c r="B131" t="str">
         <f t="shared" ref="B131:B150" si="2">TEXT(A131,"000")</f>
         <v>881</v>
       </c>
@@ -4596,15 +4675,15 @@
       <c r="F131">
         <v>0.101743</v>
       </c>
-      <c r="G131" s="4" t="s">
+      <c r="G131" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>883</v>
       </c>
-      <c r="B132" s="4" t="str">
+      <c r="B132" t="str">
         <f t="shared" si="2"/>
         <v>883</v>
       </c>
@@ -4620,15 +4699,15 @@
       <c r="F132">
         <v>0.101743</v>
       </c>
-      <c r="G132" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G132" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>887</v>
       </c>
-      <c r="B133" s="4" t="str">
+      <c r="B133" t="str">
         <f t="shared" si="2"/>
         <v>887</v>
       </c>
@@ -4644,15 +4723,15 @@
       <c r="F133">
         <v>0.101743</v>
       </c>
-      <c r="G133" s="4" t="s">
+      <c r="G133" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>889</v>
       </c>
-      <c r="B134" s="4" t="str">
+      <c r="B134" t="str">
         <f t="shared" si="2"/>
         <v>889</v>
       </c>
@@ -4668,15 +4747,15 @@
       <c r="F134">
         <v>0.101743</v>
       </c>
-      <c r="G134" s="4" t="s">
+      <c r="G134" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>890</v>
       </c>
-      <c r="B135" s="4" t="str">
+      <c r="B135" t="str">
         <f t="shared" si="2"/>
         <v>890</v>
       </c>
@@ -4692,15 +4771,15 @@
       <c r="F135">
         <v>0.101743</v>
       </c>
-      <c r="G135" s="4" t="s">
+      <c r="G135" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>891</v>
       </c>
-      <c r="B136" s="4" t="str">
+      <c r="B136" t="str">
         <f t="shared" si="2"/>
         <v>891</v>
       </c>
@@ -4716,15 +4795,15 @@
       <c r="F136">
         <v>0.101743</v>
       </c>
-      <c r="G136" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G136" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>892</v>
       </c>
-      <c r="B137" s="4" t="str">
+      <c r="B137" t="str">
         <f t="shared" si="2"/>
         <v>892</v>
       </c>
@@ -4740,15 +4819,15 @@
       <c r="F137">
         <v>0.101743</v>
       </c>
-      <c r="G137" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G137" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>893</v>
       </c>
-      <c r="B138" s="4" t="str">
+      <c r="B138" t="str">
         <f t="shared" si="2"/>
         <v>893</v>
       </c>
@@ -4764,15 +4843,15 @@
       <c r="F138">
         <v>0.101743</v>
       </c>
-      <c r="G138" s="4" t="s">
+      <c r="G138" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>897</v>
       </c>
-      <c r="B139" s="4" t="str">
+      <c r="B139" t="str">
         <f t="shared" si="2"/>
         <v>897</v>
       </c>
@@ -4788,15 +4867,15 @@
       <c r="F139">
         <v>0.101743</v>
       </c>
-      <c r="G139" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G139" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>899</v>
       </c>
-      <c r="B140" s="4" t="str">
+      <c r="B140" t="str">
         <f t="shared" si="2"/>
         <v>899</v>
       </c>
@@ -4812,15 +4891,15 @@
       <c r="F140">
         <v>0.101743</v>
       </c>
-      <c r="G140" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G140" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>900</v>
       </c>
-      <c r="B141" s="4" t="str">
+      <c r="B141" t="str">
         <f t="shared" si="2"/>
         <v>900</v>
       </c>
@@ -4836,15 +4915,15 @@
       <c r="F141">
         <v>0.1</v>
       </c>
-      <c r="G141" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G141" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>913</v>
       </c>
-      <c r="B142" s="4" t="str">
+      <c r="B142" t="str">
         <f t="shared" si="2"/>
         <v>913</v>
       </c>
@@ -4860,15 +4939,15 @@
       <c r="F142">
         <v>0.1</v>
       </c>
-      <c r="G142" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G142" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>914</v>
       </c>
-      <c r="B143" s="4" t="str">
+      <c r="B143" t="str">
         <f t="shared" si="2"/>
         <v>914</v>
       </c>
@@ -4884,15 +4963,15 @@
       <c r="F143">
         <v>0.1</v>
       </c>
-      <c r="G143" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G143" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>915</v>
       </c>
-      <c r="B144" s="4" t="str">
+      <c r="B144" t="str">
         <f t="shared" si="2"/>
         <v>915</v>
       </c>
@@ -4908,15 +4987,15 @@
       <c r="F144">
         <v>0.1</v>
       </c>
-      <c r="G144" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G144" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>918</v>
       </c>
-      <c r="B145" s="4" t="str">
+      <c r="B145" t="str">
         <f t="shared" si="2"/>
         <v>918</v>
       </c>
@@ -4932,15 +5011,15 @@
       <c r="F145">
         <v>0.1</v>
       </c>
-      <c r="G145" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G145" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>919</v>
       </c>
-      <c r="B146" s="4" t="str">
+      <c r="B146" t="str">
         <f t="shared" si="2"/>
         <v>919</v>
       </c>
@@ -4956,15 +5035,15 @@
       <c r="F146">
         <v>0.1</v>
       </c>
-      <c r="G146" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G146" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>990</v>
       </c>
-      <c r="B147" s="4" t="str">
+      <c r="B147" t="str">
         <f t="shared" si="2"/>
         <v>990</v>
       </c>
@@ -4980,15 +5059,15 @@
       <c r="F147">
         <v>0.1</v>
       </c>
-      <c r="G147" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G147" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>991</v>
       </c>
-      <c r="B148" s="4" t="str">
+      <c r="B148" t="str">
         <f t="shared" si="2"/>
         <v>991</v>
       </c>
@@ -5004,15 +5083,15 @@
       <c r="F148">
         <v>0.1</v>
       </c>
-      <c r="G148" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G148" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>996</v>
       </c>
-      <c r="B149" s="4" t="str">
+      <c r="B149" t="str">
         <f t="shared" si="2"/>
         <v>996</v>
       </c>
@@ -5028,15 +5107,15 @@
       <c r="F149">
         <v>0.1</v>
       </c>
-      <c r="G149" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G149" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>997</v>
       </c>
-      <c r="B150" s="4" t="str">
+      <c r="B150" t="str">
         <f t="shared" si="2"/>
         <v>997</v>
       </c>
@@ -5052,68 +5131,12 @@
       <c r="F150">
         <v>0.1</v>
       </c>
-      <c r="G150" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A151" s="1"/>
-      <c r="B151" s="1"/>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A152" s="1"/>
-      <c r="B152" s="1"/>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A153" s="1"/>
-      <c r="B153" s="1"/>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A154" s="1"/>
-      <c r="B154" s="1"/>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A155" s="1"/>
-      <c r="B155" s="1"/>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A156" s="1"/>
-      <c r="B156" s="1"/>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A157" s="1"/>
-      <c r="B157" s="1"/>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A158" s="1"/>
-      <c r="B158" s="1"/>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A159" s="1"/>
-      <c r="B159" s="1"/>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A160" s="1"/>
-      <c r="B160" s="1"/>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A161" s="1"/>
-      <c r="B161" s="1"/>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A162" s="1"/>
-      <c r="B162" s="1"/>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A163" s="1"/>
-      <c r="B163" s="1"/>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A164" s="1"/>
-      <c r="B164" s="1"/>
+      <c r="G150" t="s">
+        <v>145</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F150" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G150" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -5122,192 +5145,195 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="48.36328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="3" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>180</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" t="s">
         <v>181</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="C2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>182</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" t="s">
         <v>183</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="C3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>184</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="B4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>185</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" t="s">
         <v>186</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="C5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>187</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" t="s">
         <v>188</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>189</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" t="s">
         <v>139</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>190</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" t="s">
         <v>157</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>191</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" t="s">
         <v>192</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="C9" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>193</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" t="s">
         <v>194</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="C10" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>195</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" t="s">
         <v>196</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="C11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>197</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" t="s">
         <v>198</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="C12" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>199</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" t="s">
         <v>200</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="C13" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>201</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="B14" t="s">
+        <v>145</v>
+      </c>
+      <c r="C14" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>202</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" t="s">
         <v>203</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="C15" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>204</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" t="s">
         <v>205</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="C16" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>206</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" t="s">
         <v>207</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" t="s">
         <v>145</v>
       </c>
     </row>
@@ -5319,253 +5345,253 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="3" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>138</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>140</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>141</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>143</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>144</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="B6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>146</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="B7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>147</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="B8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>148</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="B9" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>149</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="B10" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>150</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="B11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>152</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="B12" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>153</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="B13" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>154</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="B14" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>155</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="B15" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>156</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>158</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>159</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>161</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="B19" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>162</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>164</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>166</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>167</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>168</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="B24" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>169</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+      <c r="B25" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>170</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="B26" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>171</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>172</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>173</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
+      <c r="B29" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>174</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
+      <c r="B30" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>175</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" t="s">
         <v>163</v>
       </c>
     </row>
@@ -5577,229 +5603,229 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="3" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>138</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" t="s">
         <v>208</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>140</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" t="s">
         <v>210</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
         <v>141</v>
       </c>
       <c r="B4" t="s">
         <v>260</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>144</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" t="s">
         <v>211</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="C5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>146</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" t="s">
         <v>212</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="C6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>147</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" t="s">
         <v>213</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="C7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>148</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" t="s">
         <v>214</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="C8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>149</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" t="s">
         <v>215</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="C9" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>150</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" t="s">
         <v>216</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="C10" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>152</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" t="s">
         <v>217</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="C11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>153</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" t="s">
         <v>218</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="C12" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>154</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" t="s">
         <v>219</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="C13" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>156</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" t="s">
         <v>220</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>221</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" t="s">
         <v>222</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>158</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" t="s">
         <v>223</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>224</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" t="s">
         <v>225</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>226</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" t="s">
         <v>227</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>159</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" t="s">
         <v>229</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="C19" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>230</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" t="s">
         <v>231</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" t="s">
         <v>151</v>
       </c>
     </row>
@@ -5811,250 +5837,250 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="3" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2">
         <v>102</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" t="s">
         <v>232</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+      <c r="C2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3">
         <v>103</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" t="s">
         <v>233</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+      <c r="C3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4">
         <v>104</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" t="s">
         <v>234</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="C4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5">
         <v>105</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" t="s">
         <v>235</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+      <c r="C5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6">
         <v>106</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" t="s">
         <v>236</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+      <c r="C6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7">
         <v>118</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" t="s">
         <v>237</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8">
         <v>119</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" t="s">
         <v>238</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9">
         <v>120</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" t="s">
         <v>239</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+      <c r="C9" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10">
         <v>181</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" t="s">
         <v>240</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11">
         <v>191</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" t="s">
         <v>241</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12">
         <v>314</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" t="s">
         <v>242</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
+      <c r="C12" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13">
         <v>317</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" t="s">
         <v>243</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
+      <c r="C13" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14">
         <v>320</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" t="s">
         <v>244</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
+      <c r="C14" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15">
         <v>321</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" t="s">
         <v>245</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="6">
+      <c r="C15" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16">
         <v>328</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" t="s">
         <v>246</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
+      <c r="C16" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17">
         <v>401</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" t="s">
         <v>247</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18">
         <v>402</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" t="s">
         <v>248</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19">
         <v>403</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" t="s">
         <v>249</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20">
         <v>415</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" t="s">
         <v>250</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21">
         <v>610</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" t="s">
         <v>251</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22">
         <v>999</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" t="s">
         <v>252</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" t="s">
         <v>188</v>
       </c>
     </row>
@@ -6066,283 +6092,283 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="3" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="str">
         <f>LEFT(B2,2)</f>
         <v>11</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" t="s">
         <v>317</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="str">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="str">
         <f t="shared" ref="A3:A23" si="0">LEFT(B3,2)</f>
         <v>12</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" t="s">
         <v>318</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="str">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="str">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" t="s">
         <v>319</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="str">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="str">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" t="s">
         <v>320</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="str">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="str">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" t="s">
         <v>321</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="str">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="str">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" t="s">
         <v>322</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="str">
+      <c r="C7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="str">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" t="s">
         <v>323</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="str">
+      <c r="C8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="str">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" t="s">
         <v>324</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="str">
+      <c r="C9" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="str">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" t="s">
         <v>325</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="str">
+      <c r="C10" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="str">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" t="s">
         <v>326</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="str">
+      <c r="C11" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="str">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" t="s">
         <v>327</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="str">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="str">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="str">
+      <c r="C13" s="5" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="str">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="str">
+      <c r="C14" s="5" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="str">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" t="s">
         <v>330</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="str">
+      <c r="C15" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="str">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" t="s">
         <v>331</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="str">
+      <c r="C16" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="str">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" t="s">
         <v>332</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="str">
+      <c r="C17" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="str">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" t="s">
         <v>333</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="str">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="str">
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" t="s">
         <v>334</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="str">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="str">
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" t="s">
         <v>335</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="str">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="str">
         <f t="shared" si="0"/>
         <v>83</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" t="s">
         <v>336</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="str">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="str">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" t="s">
         <v>337</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="str">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="str">
         <f t="shared" si="0"/>
         <v>MH</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" t="s">
         <v>338</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" t="s">
         <v>145</v>
       </c>
     </row>
@@ -6355,463 +6381,467 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="9" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="3" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="2">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>253</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>254</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>165</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2">
         <f>1/3</f>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="2">
         <v>21</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>255</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>256</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" t="s">
         <v>165</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3">
         <f>1/3</f>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="2">
         <v>27</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>258</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" t="s">
         <v>259</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" t="s">
         <v>165</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="2">
         <v>28</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>260</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" t="s">
         <v>261</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" t="s">
         <v>165</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5">
         <f>1/3</f>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="2">
         <v>29</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>262</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" t="s">
         <v>263</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" t="s">
         <v>165</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="2">
         <v>30</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>264</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" t="s">
         <v>265</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F7" s="2">
+      <c r="E7" t="s">
+        <v>145</v>
+      </c>
+      <c r="F7">
         <f t="shared" ref="F7:F22" si="0">1/3</f>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="2">
         <v>32</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" t="s">
         <v>266</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" t="s">
         <v>267</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F8" s="2">
+      <c r="E8" t="s">
+        <v>145</v>
+      </c>
+      <c r="F8">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
+    <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="2">
         <v>40</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" t="s">
         <v>268</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" t="s">
         <v>269</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F9" s="2">
+      <c r="E9" t="s">
+        <v>145</v>
+      </c>
+      <c r="F9">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="2">
         <v>41</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" t="s">
         <v>270</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" t="s">
         <v>271</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F10" s="2">
+      <c r="E10" t="s">
+        <v>145</v>
+      </c>
+      <c r="F10">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
+    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="2">
         <v>50</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" t="s">
         <v>272</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" t="s">
         <v>273</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F11" s="2">
+      <c r="E11" t="s">
+        <v>151</v>
+      </c>
+      <c r="F11">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+    <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="2">
         <v>52</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" t="s">
         <v>274</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" t="s">
         <v>275</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F12" s="2">
+      <c r="E12" t="s">
+        <v>151</v>
+      </c>
+      <c r="F12">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
+    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="2">
         <v>60</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" t="s">
         <v>276</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" t="s">
         <v>277</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F13" s="2">
+      <c r="E13" t="s">
+        <v>151</v>
+      </c>
+      <c r="F13">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
+    <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="2">
         <v>62</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" t="s">
         <v>274</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" t="s">
         <v>278</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F14" s="2">
+      <c r="E14" t="s">
+        <v>151</v>
+      </c>
+      <c r="F14">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
+    <row r="15" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="2">
         <v>70</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" t="s">
         <v>279</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" t="s">
         <v>280</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F15" s="2">
+      <c r="E15" t="s">
+        <v>151</v>
+      </c>
+      <c r="F15">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="2">
         <v>72</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" t="s">
         <v>274</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" t="s">
         <v>281</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F16" s="2">
+      <c r="E16" t="s">
+        <v>151</v>
+      </c>
+      <c r="F16">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="2">
         <v>80</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" t="s">
         <v>282</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" t="s">
         <v>283</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" t="s">
         <v>157</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="2">
         <v>82</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" t="s">
         <v>284</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" t="s">
         <v>285</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" t="s">
         <v>157</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="2">
         <v>90</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" t="s">
         <v>286</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" t="s">
         <v>287</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F19" s="2">
+      <c r="E19" t="s">
+        <v>145</v>
+      </c>
+      <c r="F19">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="2">
         <v>4600</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" t="s">
         <v>288</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" t="s">
         <v>289</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F20" s="2">
+      <c r="E20" t="s">
+        <v>151</v>
+      </c>
+      <c r="F20">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
+    <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="2">
         <v>5000</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" t="s">
         <v>290</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" t="s">
         <v>291</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F21" s="2">
+      <c r="E21" t="s">
+        <v>151</v>
+      </c>
+      <c r="F21">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
+    <row r="22" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="2">
         <v>7400</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" t="s">
         <v>293</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" t="s">
         <v>294</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" t="s">
         <v>295</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
@@ -6824,160 +6854,266 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="27.36328125" customWidth="1"/>
+    <col min="3" max="3" width="16.08984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="3" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>184</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="B2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>187</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" t="s">
         <v>188</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>189</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" t="s">
         <v>139</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>296</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" t="s">
         <v>297</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="C5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>298</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" t="s">
         <v>299</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="C6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>190</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" t="s">
         <v>157</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>300</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" t="s">
         <v>301</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>191</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" t="s">
         <v>302</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>195</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" t="s">
         <v>303</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>201</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" t="s">
         <v>304</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+      <c r="C11" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>206</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" t="s">
         <v>305</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>306</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" t="s">
         <v>307</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>308</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" t="s">
         <v>309</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>151</v>
+      <c r="C14" t="s">
+        <v>151</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB14423E-3B10-4144-B6F3-4B0EE1BD3C57}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="91.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>345</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="D3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="260.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C4" t="s">
+        <v>356</v>
+      </c>
+      <c r="D4" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="146" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>347</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="C5" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>348</v>
+      </c>
+      <c r="B6" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>349</v>
+      </c>
+      <c r="B7" t="s">
+        <v>361</v>
+      </c>
+      <c r="D7" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>350</v>
+      </c>
+      <c r="B8" t="s">
+        <v>363</v>
+      </c>
+      <c r="D8" t="s">
+        <v>364</v>
       </c>
     </row>
   </sheetData>

--- a/resources/property classes.xlsx
+++ b/resources/property classes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmapil-my.sharepoint.com/personal/abahls_cmap_illinois_gov/Documents/Documents/github_repos/effective_property_tax/resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abahls\Documents\GitHub\effective_property_tax\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{2A60A013-1040-4DEC-B76C-0C647DD12EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DEE2F40-C6AF-4ABA-861A-13FCD93F345B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E95C164E-E1BB-45F5-9E3A-2A96C1DD5F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="37320" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cook" sheetId="1" r:id="rId1"/>
@@ -21,10 +21,11 @@
     <sheet name="lake 2018 later" sheetId="8" r:id="rId6"/>
     <sheet name="mchenry" sheetId="6" r:id="rId7"/>
     <sheet name="will" sheetId="7" r:id="rId8"/>
+    <sheet name="Notes" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cook!$A$1:$G$152</definedName>
-    <definedName name="Export_Output_2" localSheetId="0">Cook!$A$1:$E$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cook!$A$1:$G$150</definedName>
+    <definedName name="Export_Output_2" localSheetId="0">Cook!$A$1:$E$134</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="365">
   <si>
     <t>overall_class</t>
   </si>
@@ -1073,17 +1074,84 @@
     <t>land_use_code</t>
   </si>
   <si>
-    <t>Commercial incentive land</t>
-  </si>
-  <si>
-    <t>5000 - Locally Assessed Railroad</t>
+    <t>Cook</t>
+  </si>
+  <si>
+    <t>https://prodassets.cookcountyassessor.com/s3fs-public/form_documents/classcode.pdf</t>
+  </si>
+  <si>
+    <t>https://www.cookcountyassessor.com/classifications-real-property</t>
+  </si>
+  <si>
+    <t>DuPage</t>
+  </si>
+  <si>
+    <t>Kane</t>
+  </si>
+  <si>
+    <t>Kendall</t>
+  </si>
+  <si>
+    <t>Lake</t>
+  </si>
+  <si>
+    <t>McHenry</t>
+  </si>
+  <si>
+    <t>Will</t>
+  </si>
+  <si>
+    <t>A-Apartment classed properties are 2-6 units and are residential properties.  M-Multiple classed properties are more than 6 unit apartments and are commercial properties.</t>
+  </si>
+  <si>
+    <t>email with Helen Krengel  &lt;Helen.Krengel@dupagecounty.gov&gt;</t>
+  </si>
+  <si>
+    <t>changes</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>The 0050 class is for commercial residential property.  So those parcels generally are apartment buildings</t>
+  </si>
+  <si>
+    <t>email with John Emerson &lt;EmersonJohn@KaneCountyIL.gov&gt;</t>
+  </si>
+  <si>
+    <t>0050 to commercial</t>
+  </si>
+  <si>
+    <t>0011 would just be Farm, not open space as this class only applies to property that is farmland and has buildings on it.
+0028 is used for property where land, either all or part, is in a IDNR program to conserve open space.  A property owner submits a plan and other information to the IDNR who then determines what portion of the property would qualify for this use.  
+0090 is for Tax Exempt Properties (government owned, religious, etc.) and has nothing to with railroads.  
+4500 is State Assessed Railroad. Would not fall into the Exempt category.
+5000 Railroad is local assessed railroad and would not be considered as exempt.  Local assessed railroad would be the buildings that are on the railroad right of way not the tracks themselves so this is probably you were told that it is called commercial.</t>
+  </si>
+  <si>
+    <t>Andy Nicoletti, ANicoletti@kendallcountyil.gov</t>
+  </si>
+  <si>
+    <t>relatively straightforward; can look up individual cases on the PIN search</t>
+  </si>
+  <si>
+    <t>changed 50 to commercial, based on names its clear which is which</t>
+  </si>
+  <si>
+    <t>50 to commercial</t>
+  </si>
+  <si>
+    <t>no apartment category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no change </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1117,6 +1185,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1154,7 +1228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1166,6 +1240,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1446,17 +1526,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G152"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G150"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="80.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" customWidth="1"/>
+    <col min="3" max="3" width="80.6328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="34.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1479,7 +1559,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1503,7 +1583,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>100</v>
       </c>
@@ -1527,7 +1607,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>190</v>
       </c>
@@ -1551,7 +1631,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>200</v>
       </c>
@@ -1575,7 +1655,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>201</v>
       </c>
@@ -1599,7 +1679,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>202</v>
       </c>
@@ -1623,7 +1703,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>203</v>
       </c>
@@ -1647,7 +1727,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>204</v>
       </c>
@@ -1671,7 +1751,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>205</v>
       </c>
@@ -1695,7 +1775,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>206</v>
       </c>
@@ -1719,7 +1799,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>207</v>
       </c>
@@ -1743,7 +1823,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>208</v>
       </c>
@@ -1767,7 +1847,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>209</v>
       </c>
@@ -1791,7 +1871,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>210</v>
       </c>
@@ -1815,7 +1895,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>211</v>
       </c>
@@ -1839,7 +1919,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>212</v>
       </c>
@@ -1863,7 +1943,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>213</v>
       </c>
@@ -1887,7 +1967,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>218</v>
       </c>
@@ -1911,7 +1991,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>219</v>
       </c>
@@ -1935,7 +2015,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>224</v>
       </c>
@@ -1959,7 +2039,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>225</v>
       </c>
@@ -1983,7 +2063,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>234</v>
       </c>
@@ -2007,7 +2087,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>239</v>
       </c>
@@ -2031,7 +2111,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>241</v>
       </c>
@@ -2055,7 +2135,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>278</v>
       </c>
@@ -2079,7 +2159,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>288</v>
       </c>
@@ -2103,7 +2183,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>290</v>
       </c>
@@ -2127,7 +2207,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>295</v>
       </c>
@@ -2151,7 +2231,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>297</v>
       </c>
@@ -2175,7 +2255,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>299</v>
       </c>
@@ -2199,7 +2279,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>300</v>
       </c>
@@ -2223,7 +2303,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>301</v>
       </c>
@@ -2247,7 +2327,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>313</v>
       </c>
@@ -2271,7 +2351,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>314</v>
       </c>
@@ -2295,7 +2375,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>315</v>
       </c>
@@ -2319,7 +2399,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>318</v>
       </c>
@@ -2343,7 +2423,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>319</v>
       </c>
@@ -2367,7 +2447,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>390</v>
       </c>
@@ -2391,7 +2471,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>391</v>
       </c>
@@ -2415,7 +2495,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>396</v>
       </c>
@@ -2439,7 +2519,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>397</v>
       </c>
@@ -2463,7 +2543,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>399</v>
       </c>
@@ -2487,7 +2567,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>401</v>
       </c>
@@ -2511,7 +2591,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>417</v>
       </c>
@@ -2535,7 +2615,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>418</v>
       </c>
@@ -2559,7 +2639,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>422</v>
       </c>
@@ -2583,7 +2663,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>427</v>
       </c>
@@ -2607,7 +2687,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>428</v>
       </c>
@@ -2631,7 +2711,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>430</v>
       </c>
@@ -2655,7 +2735,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>435</v>
       </c>
@@ -2679,7 +2759,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>480</v>
       </c>
@@ -2703,7 +2783,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>483</v>
       </c>
@@ -2727,7 +2807,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>490</v>
       </c>
@@ -2751,7 +2831,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>491</v>
       </c>
@@ -2775,7 +2855,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>492</v>
       </c>
@@ -2799,7 +2879,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>493</v>
       </c>
@@ -2823,7 +2903,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>497</v>
       </c>
@@ -2847,7 +2927,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>499</v>
       </c>
@@ -2871,7 +2951,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>500</v>
       </c>
@@ -2895,7 +2975,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>501</v>
       </c>
@@ -2919,7 +2999,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>516</v>
       </c>
@@ -2943,7 +3023,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>517</v>
       </c>
@@ -2967,7 +3047,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>522</v>
       </c>
@@ -2991,7 +3071,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>523</v>
       </c>
@@ -3015,7 +3095,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>526</v>
       </c>
@@ -3039,12 +3119,12 @@
         <v>151</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>527</v>
       </c>
       <c r="B67" t="str">
-        <f t="shared" ref="B67:B132" si="1">TEXT(A67,"000")</f>
+        <f t="shared" ref="B67:B130" si="1">TEXT(A67,"000")</f>
         <v>527</v>
       </c>
       <c r="C67" t="s">
@@ -3063,7 +3143,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>528</v>
       </c>
@@ -3087,7 +3167,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>529</v>
       </c>
@@ -3111,7 +3191,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>530</v>
       </c>
@@ -3135,7 +3215,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>531</v>
       </c>
@@ -3159,7 +3239,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>532</v>
       </c>
@@ -3183,7 +3263,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>533</v>
       </c>
@@ -3207,7 +3287,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>535</v>
       </c>
@@ -3231,7 +3311,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>550</v>
       </c>
@@ -3255,7 +3335,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>580</v>
       </c>
@@ -3279,7 +3359,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>581</v>
       </c>
@@ -3303,7 +3383,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>583</v>
       </c>
@@ -3327,7 +3407,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>587</v>
       </c>
@@ -3351,7 +3431,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>589</v>
       </c>
@@ -3375,7 +3455,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>590</v>
       </c>
@@ -3399,7 +3479,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>591</v>
       </c>
@@ -3423,7 +3503,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>592</v>
       </c>
@@ -3447,7 +3527,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>593</v>
       </c>
@@ -3471,7 +3551,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>597</v>
       </c>
@@ -3495,7 +3575,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>599</v>
       </c>
@@ -3519,7 +3599,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>637</v>
       </c>
@@ -3543,7 +3623,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>638</v>
       </c>
@@ -3567,7 +3647,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>654</v>
       </c>
@@ -3591,7 +3671,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>655</v>
       </c>
@@ -3615,7 +3695,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>663</v>
       </c>
@@ -3639,7 +3719,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>668</v>
       </c>
@@ -3663,7 +3743,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>670</v>
       </c>
@@ -3687,7 +3767,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>671</v>
       </c>
@@ -3711,7 +3791,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>673</v>
       </c>
@@ -3735,7 +3815,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>677</v>
       </c>
@@ -3759,7 +3839,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>679</v>
       </c>
@@ -3783,7 +3863,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>680</v>
       </c>
@@ -3807,7 +3887,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>683</v>
       </c>
@@ -3831,7 +3911,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>687</v>
       </c>
@@ -3855,7 +3935,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>693</v>
       </c>
@@ -3879,7 +3959,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>717</v>
       </c>
@@ -3903,7 +3983,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>722</v>
       </c>
@@ -3927,7 +4007,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>723</v>
       </c>
@@ -3951,7 +4031,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>728</v>
       </c>
@@ -3975,7 +4055,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>729</v>
       </c>
@@ -3999,7 +4079,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>730</v>
       </c>
@@ -4023,7 +4103,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>731</v>
       </c>
@@ -4047,7 +4127,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>746</v>
       </c>
@@ -4071,7 +4151,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>748</v>
       </c>
@@ -4095,7 +4175,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>752</v>
       </c>
@@ -4119,7 +4199,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>760</v>
       </c>
@@ -4143,7 +4223,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>765</v>
       </c>
@@ -4167,7 +4247,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>767</v>
       </c>
@@ -4191,7 +4271,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>774</v>
       </c>
@@ -4215,7 +4295,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>790</v>
       </c>
@@ -4239,7 +4319,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>791</v>
       </c>
@@ -4263,7 +4343,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>792</v>
       </c>
@@ -4287,7 +4367,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>797</v>
       </c>
@@ -4311,7 +4391,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>799</v>
       </c>
@@ -4335,16 +4415,16 @@
         <v>151</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B121" t="str">
         <f t="shared" si="1"/>
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C121" t="s">
-        <v>342</v>
+        <v>121</v>
       </c>
       <c r="D121" t="s">
         <v>122</v>
@@ -4359,16 +4439,16 @@
         <v>151</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122">
-        <v>801</v>
+        <v>817</v>
       </c>
       <c r="B122" t="str">
         <f t="shared" si="1"/>
-        <v>801</v>
+        <v>817</v>
       </c>
       <c r="C122" t="s">
-        <v>121</v>
+        <v>70</v>
       </c>
       <c r="D122" t="s">
         <v>122</v>
@@ -4383,16 +4463,16 @@
         <v>151</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="B123" t="str">
         <f t="shared" si="1"/>
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="C123" t="s">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D123" t="s">
         <v>122</v>
@@ -4407,16 +4487,16 @@
         <v>151</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="B124" t="str">
         <f t="shared" si="1"/>
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="C124" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="D124" t="s">
         <v>122</v>
@@ -4431,16 +4511,16 @@
         <v>151</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="B125" t="str">
         <f t="shared" si="1"/>
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="C125" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D125" t="s">
         <v>122</v>
@@ -4455,16 +4535,16 @@
         <v>151</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="B126" t="str">
         <f t="shared" si="1"/>
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C126" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D126" t="s">
         <v>122</v>
@@ -4479,16 +4559,16 @@
         <v>151</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="B127" t="str">
         <f t="shared" si="1"/>
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="C127" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D127" t="s">
         <v>122</v>
@@ -4503,16 +4583,16 @@
         <v>151</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="B128" t="str">
         <f t="shared" si="1"/>
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="C128" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="D128" t="s">
         <v>122</v>
@@ -4527,16 +4607,16 @@
         <v>151</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="B129" t="str">
         <f t="shared" si="1"/>
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="C129" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D129" t="s">
         <v>122</v>
@@ -4551,19 +4631,19 @@
         <v>151</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130">
-        <v>831</v>
+        <v>880</v>
       </c>
       <c r="B130" t="str">
         <f t="shared" si="1"/>
-        <v>831</v>
+        <v>880</v>
       </c>
       <c r="C130" t="s">
-        <v>125</v>
+        <v>85</v>
       </c>
       <c r="D130" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E130" t="s">
         <v>123</v>
@@ -4572,22 +4652,22 @@
         <v>0.101743</v>
       </c>
       <c r="G130" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131">
-        <v>833</v>
+        <v>881</v>
       </c>
       <c r="B131" t="str">
-        <f t="shared" si="1"/>
-        <v>833</v>
+        <f t="shared" ref="B131:B150" si="2">TEXT(A131,"000")</f>
+        <v>881</v>
       </c>
       <c r="C131" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="D131" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E131" t="s">
         <v>123</v>
@@ -4596,19 +4676,19 @@
         <v>0.101743</v>
       </c>
       <c r="G131" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="B132" t="str">
-        <f t="shared" si="1"/>
-        <v>880</v>
+        <f t="shared" si="2"/>
+        <v>883</v>
       </c>
       <c r="C132" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D132" t="s">
         <v>126</v>
@@ -4620,19 +4700,19 @@
         <v>0.101743</v>
       </c>
       <c r="G132" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="B133" t="str">
-        <f t="shared" ref="B133:B152" si="2">TEXT(A133,"000")</f>
-        <v>881</v>
+        <f t="shared" si="2"/>
+        <v>887</v>
       </c>
       <c r="C133" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="D133" t="s">
         <v>126</v>
@@ -4647,16 +4727,16 @@
         <v>157</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="B134" t="str">
         <f t="shared" si="2"/>
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="C134" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="D134" t="s">
         <v>126</v>
@@ -4668,19 +4748,19 @@
         <v>0.101743</v>
       </c>
       <c r="G134" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="B135" t="str">
         <f t="shared" si="2"/>
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="C135" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="D135" t="s">
         <v>126</v>
@@ -4695,19 +4775,19 @@
         <v>157</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="B136" t="str">
         <f t="shared" si="2"/>
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C136" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="D136" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E136" t="s">
         <v>123</v>
@@ -4716,22 +4796,22 @@
         <v>0.101743</v>
       </c>
       <c r="G136" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B137" t="str">
         <f t="shared" si="2"/>
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C137" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="D137" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E137" t="s">
         <v>123</v>
@@ -4740,22 +4820,22 @@
         <v>0.101743</v>
       </c>
       <c r="G137" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="B138" t="str">
         <f t="shared" si="2"/>
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="C138" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="D138" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E138" t="s">
         <v>123</v>
@@ -4764,19 +4844,19 @@
         <v>0.101743</v>
       </c>
       <c r="G138" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="B139" t="str">
         <f t="shared" si="2"/>
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="C139" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D139" t="s">
         <v>122</v>
@@ -4791,16 +4871,16 @@
         <v>151</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="B140" t="str">
         <f t="shared" si="2"/>
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="C140" t="s">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="D140" t="s">
         <v>126</v>
@@ -4812,67 +4892,67 @@
         <v>0.101743</v>
       </c>
       <c r="G140" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="B141" t="str">
         <f t="shared" si="2"/>
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="C141" t="s">
-        <v>94</v>
-      </c>
-      <c r="D141" t="s">
-        <v>122</v>
+        <v>129</v>
+      </c>
+      <c r="D141">
+        <v>9</v>
       </c>
       <c r="E141" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F141">
-        <v>0.101743</v>
+        <v>0.1</v>
       </c>
       <c r="G141" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142">
-        <v>899</v>
+        <v>913</v>
       </c>
       <c r="B142" t="str">
         <f t="shared" si="2"/>
-        <v>899</v>
+        <v>913</v>
       </c>
       <c r="C142" t="s">
-        <v>128</v>
-      </c>
-      <c r="D142" t="s">
-        <v>126</v>
+        <v>131</v>
+      </c>
+      <c r="D142">
+        <v>9</v>
       </c>
       <c r="E142" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F142">
-        <v>0.101743</v>
+        <v>0.1</v>
       </c>
       <c r="G142" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143">
-        <v>900</v>
+        <v>914</v>
       </c>
       <c r="B143" t="str">
         <f t="shared" si="2"/>
-        <v>900</v>
+        <v>914</v>
       </c>
       <c r="C143" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D143">
         <v>9</v>
@@ -4887,16 +4967,16 @@
         <v>145</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="B144" t="str">
         <f t="shared" si="2"/>
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C144" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D144">
         <v>9</v>
@@ -4911,16 +4991,16 @@
         <v>145</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="B145" t="str">
         <f t="shared" si="2"/>
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="C145" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D145">
         <v>9</v>
@@ -4935,16 +5015,16 @@
         <v>145</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="B146" t="str">
         <f t="shared" si="2"/>
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="C146" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D146">
         <v>9</v>
@@ -4959,16 +5039,16 @@
         <v>145</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147">
-        <v>918</v>
+        <v>990</v>
       </c>
       <c r="B147" t="str">
         <f t="shared" si="2"/>
-        <v>918</v>
+        <v>990</v>
       </c>
       <c r="C147" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D147">
         <v>9</v>
@@ -4983,16 +5063,16 @@
         <v>145</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148">
-        <v>919</v>
+        <v>991</v>
       </c>
       <c r="B148" t="str">
         <f t="shared" si="2"/>
-        <v>919</v>
+        <v>991</v>
       </c>
       <c r="C148" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D148">
         <v>9</v>
@@ -5007,16 +5087,16 @@
         <v>145</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149">
-        <v>990</v>
+        <v>996</v>
       </c>
       <c r="B149" t="str">
         <f t="shared" si="2"/>
-        <v>990</v>
+        <v>996</v>
       </c>
       <c r="C149" t="s">
-        <v>136</v>
+        <v>46</v>
       </c>
       <c r="D149">
         <v>9</v>
@@ -5031,16 +5111,16 @@
         <v>145</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150">
-        <v>991</v>
+        <v>997</v>
       </c>
       <c r="B150" t="str">
         <f t="shared" si="2"/>
-        <v>991</v>
+        <v>997</v>
       </c>
       <c r="C150" t="s">
-        <v>137</v>
+        <v>47</v>
       </c>
       <c r="D150">
         <v>9</v>
@@ -5055,56 +5135,8 @@
         <v>145</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A151">
-        <v>996</v>
-      </c>
-      <c r="B151" t="str">
-        <f t="shared" si="2"/>
-        <v>996</v>
-      </c>
-      <c r="C151" t="s">
-        <v>46</v>
-      </c>
-      <c r="D151">
-        <v>9</v>
-      </c>
-      <c r="E151" t="s">
-        <v>130</v>
-      </c>
-      <c r="F151">
-        <v>0.1</v>
-      </c>
-      <c r="G151" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A152">
-        <v>997</v>
-      </c>
-      <c r="B152" t="str">
-        <f t="shared" si="2"/>
-        <v>997</v>
-      </c>
-      <c r="C152" t="s">
-        <v>47</v>
-      </c>
-      <c r="D152">
-        <v>9</v>
-      </c>
-      <c r="E152" t="s">
-        <v>130</v>
-      </c>
-      <c r="F152">
-        <v>0.1</v>
-      </c>
-      <c r="G152" t="s">
-        <v>145</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G152" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G150" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -5113,12 +5145,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="45.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>310</v>
       </c>
@@ -5129,7 +5161,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>180</v>
       </c>
@@ -5140,7 +5172,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>182</v>
       </c>
@@ -5151,7 +5183,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>184</v>
       </c>
@@ -5162,7 +5194,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>185</v>
       </c>
@@ -5173,7 +5205,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>187</v>
       </c>
@@ -5184,7 +5216,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>189</v>
       </c>
@@ -5195,7 +5227,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>190</v>
       </c>
@@ -5206,7 +5238,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>191</v>
       </c>
@@ -5217,7 +5249,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>193</v>
       </c>
@@ -5228,7 +5260,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>195</v>
       </c>
@@ -5239,7 +5271,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>197</v>
       </c>
@@ -5250,7 +5282,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>199</v>
       </c>
@@ -5261,7 +5293,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>201</v>
       </c>
@@ -5272,7 +5304,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>202</v>
       </c>
@@ -5283,7 +5315,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>204</v>
       </c>
@@ -5294,7 +5326,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>206</v>
       </c>
@@ -5313,9 +5345,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>176</v>
       </c>
@@ -5323,7 +5355,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>138</v>
       </c>
@@ -5331,7 +5363,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>140</v>
       </c>
@@ -5339,7 +5371,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>141</v>
       </c>
@@ -5347,7 +5379,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>143</v>
       </c>
@@ -5355,7 +5387,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>144</v>
       </c>
@@ -5363,7 +5395,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>146</v>
       </c>
@@ -5371,7 +5403,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>147</v>
       </c>
@@ -5379,7 +5411,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>148</v>
       </c>
@@ -5387,15 +5419,15 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>149</v>
       </c>
       <c r="B10" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>150</v>
       </c>
@@ -5403,7 +5435,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>152</v>
       </c>
@@ -5411,7 +5443,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>153</v>
       </c>
@@ -5419,7 +5451,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>154</v>
       </c>
@@ -5427,7 +5459,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>155</v>
       </c>
@@ -5435,7 +5467,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>156</v>
       </c>
@@ -5443,7 +5475,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>158</v>
       </c>
@@ -5451,7 +5483,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>159</v>
       </c>
@@ -5459,7 +5491,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>161</v>
       </c>
@@ -5467,7 +5499,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>162</v>
       </c>
@@ -5475,7 +5507,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>164</v>
       </c>
@@ -5483,7 +5515,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>166</v>
       </c>
@@ -5491,7 +5523,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>167</v>
       </c>
@@ -5499,7 +5531,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>168</v>
       </c>
@@ -5507,7 +5539,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>169</v>
       </c>
@@ -5515,7 +5547,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>170</v>
       </c>
@@ -5523,7 +5555,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>171</v>
       </c>
@@ -5531,7 +5563,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>172</v>
       </c>
@@ -5539,7 +5571,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>173</v>
       </c>
@@ -5547,7 +5579,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>174</v>
       </c>
@@ -5555,7 +5587,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>175</v>
       </c>
@@ -5571,13 +5603,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>310</v>
       </c>
@@ -5588,7 +5620,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>138</v>
       </c>
@@ -5599,7 +5631,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>140</v>
       </c>
@@ -5610,7 +5642,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>141</v>
       </c>
@@ -5621,7 +5653,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>144</v>
       </c>
@@ -5632,7 +5664,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>146</v>
       </c>
@@ -5643,7 +5675,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>147</v>
       </c>
@@ -5654,7 +5686,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>148</v>
       </c>
@@ -5665,7 +5697,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>149</v>
       </c>
@@ -5676,7 +5708,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>150</v>
       </c>
@@ -5687,7 +5719,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>152</v>
       </c>
@@ -5698,7 +5730,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>153</v>
       </c>
@@ -5709,7 +5741,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>154</v>
       </c>
@@ -5720,7 +5752,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>156</v>
       </c>
@@ -5731,7 +5763,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>221</v>
       </c>
@@ -5742,7 +5774,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>158</v>
       </c>
@@ -5753,7 +5785,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>224</v>
       </c>
@@ -5764,7 +5796,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>226</v>
       </c>
@@ -5775,7 +5807,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>159</v>
       </c>
@@ -5786,7 +5818,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>230</v>
       </c>
@@ -5805,12 +5837,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>310</v>
       </c>
@@ -5821,7 +5853,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>102</v>
       </c>
@@ -5832,7 +5864,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>103</v>
       </c>
@@ -5843,7 +5875,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>104</v>
       </c>
@@ -5854,7 +5886,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>105</v>
       </c>
@@ -5865,7 +5897,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>106</v>
       </c>
@@ -5876,7 +5908,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>118</v>
       </c>
@@ -5887,7 +5919,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>119</v>
       </c>
@@ -5898,7 +5930,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>120</v>
       </c>
@@ -5909,7 +5941,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>181</v>
       </c>
@@ -5920,7 +5952,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>191</v>
       </c>
@@ -5931,7 +5963,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>314</v>
       </c>
@@ -5942,7 +5974,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>317</v>
       </c>
@@ -5953,7 +5985,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>320</v>
       </c>
@@ -5964,7 +5996,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>321</v>
       </c>
@@ -5975,7 +6007,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>328</v>
       </c>
@@ -5986,7 +6018,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>401</v>
       </c>
@@ -5997,7 +6029,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>402</v>
       </c>
@@ -6008,7 +6040,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>403</v>
       </c>
@@ -6019,7 +6051,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>415</v>
       </c>
@@ -6030,7 +6062,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>610</v>
       </c>
@@ -6041,7 +6073,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>999</v>
       </c>
@@ -6059,13 +6091,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>339</v>
       </c>
@@ -6076,7 +6108,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="str">
         <f>LEFT(B2,2)</f>
         <v>11</v>
@@ -6088,9 +6120,9 @@
         <v>139</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="str">
-        <f t="shared" ref="A3:A24" si="0">LEFT(B3,2)</f>
+        <f t="shared" ref="A3:A23" si="0">LEFT(B3,2)</f>
         <v>12</v>
       </c>
       <c r="B3" t="s">
@@ -6100,7 +6132,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="str">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -6112,7 +6144,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="str">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -6124,7 +6156,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="str">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -6136,7 +6168,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="str">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -6148,7 +6180,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="str">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -6160,7 +6192,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="str">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -6172,7 +6204,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="str">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -6184,7 +6216,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="str">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -6196,7 +6228,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="str">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -6208,147 +6240,135 @@
         <v>228</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="str">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="B13" t="s">
-        <v>343</v>
-      </c>
-      <c r="C13" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="str">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="str">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="B15" t="s">
+        <v>330</v>
+      </c>
+      <c r="C15" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="str">
         <f t="shared" si="0"/>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B16" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C16" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="str">
         <f t="shared" si="0"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B17" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C17" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="str">
         <f t="shared" si="0"/>
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="B18" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C18" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="str">
         <f t="shared" si="0"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B19" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C19" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="str">
         <f t="shared" si="0"/>
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B20" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C20" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="str">
         <f t="shared" si="0"/>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C21" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="str">
         <f t="shared" si="0"/>
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B22" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C22" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="str">
         <f t="shared" si="0"/>
-        <v>90</v>
+        <v>MH</v>
       </c>
       <c r="B23" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C23" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="str">
-        <f t="shared" si="0"/>
-        <v>MH</v>
-      </c>
-      <c r="B24" t="s">
-        <v>338</v>
-      </c>
-      <c r="C24" t="s">
         <v>145</v>
       </c>
     </row>
@@ -6361,12 +6381,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="33" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>313</v>
       </c>
@@ -6386,7 +6407,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>138</v>
       </c>
@@ -6407,7 +6428,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>140</v>
       </c>
@@ -6428,7 +6449,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>257</v>
       </c>
@@ -6448,7 +6469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>141</v>
       </c>
@@ -6469,7 +6490,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>143</v>
       </c>
@@ -6489,7 +6510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>144</v>
       </c>
@@ -6510,7 +6531,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>146</v>
       </c>
@@ -6531,7 +6552,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>147</v>
       </c>
@@ -6552,7 +6573,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>148</v>
       </c>
@@ -6573,7 +6594,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>149</v>
       </c>
@@ -6587,14 +6608,14 @@
         <v>273</v>
       </c>
       <c r="E11" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="F11">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>150</v>
       </c>
@@ -6615,7 +6636,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>152</v>
       </c>
@@ -6636,7 +6657,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>153</v>
       </c>
@@ -6657,7 +6678,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>154</v>
       </c>
@@ -6678,7 +6699,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>155</v>
       </c>
@@ -6699,7 +6720,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
         <v>156</v>
       </c>
@@ -6720,7 +6741,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
         <v>158</v>
       </c>
@@ -6741,7 +6762,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>224</v>
       </c>
@@ -6762,7 +6783,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
         <v>159</v>
       </c>
@@ -6783,7 +6804,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
         <v>230</v>
       </c>
@@ -6804,7 +6825,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
         <v>292</v>
       </c>
@@ -6833,12 +6854,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.36328125" customWidth="1"/>
+    <col min="3" max="3" width="16.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>310</v>
       </c>
@@ -6849,7 +6871,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>184</v>
       </c>
@@ -6860,7 +6882,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>187</v>
       </c>
@@ -6871,7 +6893,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>189</v>
       </c>
@@ -6882,7 +6904,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>296</v>
       </c>
@@ -6893,7 +6915,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>298</v>
       </c>
@@ -6904,7 +6926,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>190</v>
       </c>
@@ -6915,7 +6937,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>300</v>
       </c>
@@ -6926,7 +6948,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>191</v>
       </c>
@@ -6937,7 +6959,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>195</v>
       </c>
@@ -6948,7 +6970,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>201</v>
       </c>
@@ -6959,7 +6981,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>206</v>
       </c>
@@ -6970,7 +6992,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>306</v>
       </c>
@@ -6981,7 +7003,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>308</v>
       </c>
@@ -6990,6 +7012,108 @@
       </c>
       <c r="C14" t="s">
         <v>151</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB14423E-3B10-4144-B6F3-4B0EE1BD3C57}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="91.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>345</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="D3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="260.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C4" t="s">
+        <v>356</v>
+      </c>
+      <c r="D4" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="146" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>347</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="C5" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>348</v>
+      </c>
+      <c r="B6" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>349</v>
+      </c>
+      <c r="B7" t="s">
+        <v>361</v>
+      </c>
+      <c r="D7" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>350</v>
+      </c>
+      <c r="B8" t="s">
+        <v>363</v>
+      </c>
+      <c r="D8" t="s">
+        <v>364</v>
       </c>
     </row>
   </sheetData>

--- a/resources/property classes.xlsx
+++ b/resources/property classes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abahls\Documents\GitHub\effective_property_tax\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E95C164E-E1BB-45F5-9E3A-2A96C1DD5F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{007AB29C-F9F5-43F2-8C87-9EAAFE19135C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37320" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cook" sheetId="1" r:id="rId1"/>
@@ -24,8 +24,8 @@
     <sheet name="Notes" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cook!$A$1:$G$150</definedName>
-    <definedName name="Export_Output_2" localSheetId="0">Cook!$A$1:$E$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cook!$A$1:$G$155</definedName>
+    <definedName name="Export_Output_2" localSheetId="0">Cook!$A$1:$E$139</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="369">
   <si>
     <t>overall_class</t>
   </si>
@@ -1145,6 +1145,18 @@
   </si>
   <si>
     <t xml:space="preserve">no change </t>
+  </si>
+  <si>
+    <t>Not-for-profit gasoline station</t>
+  </si>
+  <si>
+    <t>Not-for-profit land</t>
+  </si>
+  <si>
+    <t>Any residential area located on a parcel used primarily for commercial or industrial purposes</t>
+  </si>
+  <si>
+    <t>Commercial incentive land</t>
   </si>
 </sst>
 </file>
@@ -1526,17 +1538,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G150"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G155"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.453125" customWidth="1"/>
-    <col min="3" max="3" width="80.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="3" max="3" width="80.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="34.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1559,7 +1571,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1583,12 +1595,12 @@
         <v>177</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>100</v>
       </c>
       <c r="B3" t="str">
-        <f t="shared" ref="B3:B66" si="0">TEXT(A3,"000")</f>
+        <f t="shared" ref="B3:B69" si="0">TEXT(A3,"000")</f>
         <v>100</v>
       </c>
       <c r="C3" t="s">
@@ -1607,7 +1619,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>190</v>
       </c>
@@ -1631,7 +1643,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>200</v>
       </c>
@@ -1655,7 +1667,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>201</v>
       </c>
@@ -1679,7 +1691,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>202</v>
       </c>
@@ -1703,7 +1715,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>203</v>
       </c>
@@ -1727,7 +1739,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>204</v>
       </c>
@@ -1751,7 +1763,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>205</v>
       </c>
@@ -1775,7 +1787,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>206</v>
       </c>
@@ -1799,7 +1811,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>207</v>
       </c>
@@ -1823,7 +1835,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>208</v>
       </c>
@@ -1847,7 +1859,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>209</v>
       </c>
@@ -1871,7 +1883,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>210</v>
       </c>
@@ -1895,7 +1907,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>211</v>
       </c>
@@ -1919,7 +1931,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>212</v>
       </c>
@@ -1943,7 +1955,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>213</v>
       </c>
@@ -1967,7 +1979,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>218</v>
       </c>
@@ -1991,7 +2003,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>219</v>
       </c>
@@ -2015,7 +2027,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>224</v>
       </c>
@@ -2039,7 +2051,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>225</v>
       </c>
@@ -2063,7 +2075,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>234</v>
       </c>
@@ -2087,16 +2099,16 @@
         <v>145</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B24" t="str">
         <f t="shared" si="0"/>
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>367</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -2108,19 +2120,19 @@
         <v>0.1</v>
       </c>
       <c r="G24" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" si="0"/>
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D25">
         <v>2</v>
@@ -2132,19 +2144,19 @@
         <v>0.1</v>
       </c>
       <c r="G25" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>278</v>
+        <v>241</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="0"/>
-        <v>278</v>
+        <v>241</v>
       </c>
       <c r="C26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D26">
         <v>2</v>
@@ -2159,16 +2171,16 @@
         <v>145</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="B27" t="str">
         <f t="shared" si="0"/>
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="C27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -2183,16 +2195,16 @@
         <v>145</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="0"/>
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D28">
         <v>2</v>
@@ -2207,16 +2219,16 @@
         <v>145</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="0"/>
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="C29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D29">
         <v>2</v>
@@ -2231,16 +2243,16 @@
         <v>145</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="0"/>
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D30">
         <v>2</v>
@@ -2255,16 +2267,16 @@
         <v>145</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="0"/>
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D31">
         <v>2</v>
@@ -2279,19 +2291,19 @@
         <v>145</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B32" t="str">
         <f t="shared" si="0"/>
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
@@ -2303,16 +2315,16 @@
         <v>145</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B33" t="str">
         <f t="shared" si="0"/>
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D33">
         <v>3</v>
@@ -2327,16 +2339,16 @@
         <v>145</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="B34" t="str">
         <f t="shared" si="0"/>
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="C34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D34">
         <v>3</v>
@@ -2351,16 +2363,16 @@
         <v>145</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B35" t="str">
         <f t="shared" si="0"/>
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D35">
         <v>3</v>
@@ -2375,16 +2387,16 @@
         <v>145</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B36" t="str">
         <f t="shared" si="0"/>
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D36">
         <v>3</v>
@@ -2399,16 +2411,16 @@
         <v>145</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B37" t="str">
         <f t="shared" si="0"/>
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D37">
         <v>3</v>
@@ -2423,16 +2435,16 @@
         <v>145</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B38" t="str">
         <f t="shared" si="0"/>
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D38">
         <v>3</v>
@@ -2447,16 +2459,16 @@
         <v>145</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>390</v>
+        <v>319</v>
       </c>
       <c r="B39" t="str">
         <f t="shared" si="0"/>
-        <v>390</v>
+        <v>319</v>
       </c>
       <c r="C39" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D39">
         <v>3</v>
@@ -2471,16 +2483,16 @@
         <v>145</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B40" t="str">
         <f t="shared" si="0"/>
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D40">
         <v>3</v>
@@ -2495,16 +2507,16 @@
         <v>145</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B41" t="str">
         <f t="shared" si="0"/>
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C41" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D41">
         <v>3</v>
@@ -2519,16 +2531,16 @@
         <v>145</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B42" t="str">
         <f t="shared" si="0"/>
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D42">
         <v>3</v>
@@ -2543,16 +2555,16 @@
         <v>145</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B43" t="str">
         <f t="shared" si="0"/>
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D43">
         <v>3</v>
@@ -2567,40 +2579,40 @@
         <v>145</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B44" t="str">
         <f t="shared" si="0"/>
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C44" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E44" t="s">
-        <v>179</v>
+        <v>10</v>
       </c>
       <c r="F44">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G44" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="B45" t="str">
         <f t="shared" si="0"/>
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="C45" t="s">
-        <v>50</v>
+        <v>366</v>
       </c>
       <c r="D45">
         <v>4</v>
@@ -2615,16 +2627,16 @@
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" si="0"/>
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="C46" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D46">
         <v>4</v>
@@ -2639,16 +2651,16 @@
         <v>151</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="B47" t="str">
         <f t="shared" si="0"/>
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C47" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D47">
         <v>4</v>
@@ -2663,16 +2675,16 @@
         <v>151</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="B48" t="str">
         <f t="shared" si="0"/>
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="C48" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D48">
         <v>4</v>
@@ -2687,16 +2699,16 @@
         <v>151</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="B49" t="str">
         <f t="shared" si="0"/>
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="C49" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D49">
         <v>4</v>
@@ -2711,16 +2723,16 @@
         <v>151</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="B50" t="str">
         <f t="shared" si="0"/>
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="C50" t="s">
-        <v>55</v>
+        <v>365</v>
       </c>
       <c r="D50">
         <v>4</v>
@@ -2735,16 +2747,16 @@
         <v>151</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="B51" t="str">
         <f t="shared" si="0"/>
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="C51" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D51">
         <v>4</v>
@@ -2759,16 +2771,16 @@
         <v>151</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>480</v>
+        <v>428</v>
       </c>
       <c r="B52" t="str">
         <f t="shared" si="0"/>
-        <v>480</v>
+        <v>428</v>
       </c>
       <c r="C52" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D52">
         <v>4</v>
@@ -2780,19 +2792,19 @@
         <v>0.2</v>
       </c>
       <c r="G52" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>483</v>
+        <v>430</v>
       </c>
       <c r="B53" t="str">
         <f t="shared" si="0"/>
-        <v>483</v>
+        <v>430</v>
       </c>
       <c r="C53" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D53">
         <v>4</v>
@@ -2804,19 +2816,19 @@
         <v>0.2</v>
       </c>
       <c r="G53" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>490</v>
+        <v>435</v>
       </c>
       <c r="B54" t="str">
         <f t="shared" si="0"/>
-        <v>490</v>
+        <v>435</v>
       </c>
       <c r="C54" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D54">
         <v>4</v>
@@ -2831,16 +2843,16 @@
         <v>151</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="B55" t="str">
         <f t="shared" si="0"/>
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="C55" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D55">
         <v>4</v>
@@ -2852,19 +2864,19 @@
         <v>0.2</v>
       </c>
       <c r="G55" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="B56" t="str">
         <f t="shared" si="0"/>
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="C56" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D56">
         <v>4</v>
@@ -2876,19 +2888,19 @@
         <v>0.2</v>
       </c>
       <c r="G56" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B57" t="str">
         <f t="shared" si="0"/>
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C57" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D57">
         <v>4</v>
@@ -2900,19 +2912,19 @@
         <v>0.2</v>
       </c>
       <c r="G57" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="B58" t="str">
         <f t="shared" si="0"/>
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="C58" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D58">
         <v>4</v>
@@ -2927,16 +2939,16 @@
         <v>151</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="B59" t="str">
         <f t="shared" si="0"/>
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="C59" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D59">
         <v>4</v>
@@ -2951,88 +2963,88 @@
         <v>151</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
+        <v>493</v>
+      </c>
+      <c r="B60" t="str">
+        <f t="shared" si="0"/>
+        <v>493</v>
+      </c>
+      <c r="C60" t="s">
+        <v>62</v>
+      </c>
+      <c r="D60">
+        <v>4</v>
+      </c>
+      <c r="E60" t="s">
+        <v>179</v>
+      </c>
+      <c r="F60">
+        <v>0.2</v>
+      </c>
+      <c r="G60" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>497</v>
+      </c>
+      <c r="B61" t="str">
+        <f t="shared" si="0"/>
+        <v>497</v>
+      </c>
+      <c r="C61" t="s">
+        <v>63</v>
+      </c>
+      <c r="D61">
+        <v>4</v>
+      </c>
+      <c r="E61" t="s">
+        <v>179</v>
+      </c>
+      <c r="F61">
+        <v>0.2</v>
+      </c>
+      <c r="G61" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>499</v>
+      </c>
+      <c r="B62" t="str">
+        <f t="shared" si="0"/>
+        <v>499</v>
+      </c>
+      <c r="C62" t="s">
+        <v>64</v>
+      </c>
+      <c r="D62">
+        <v>4</v>
+      </c>
+      <c r="E62" t="s">
+        <v>179</v>
+      </c>
+      <c r="F62">
+        <v>0.2</v>
+      </c>
+      <c r="G62" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63">
         <v>500</v>
       </c>
-      <c r="B60" t="str">
+      <c r="B63" t="str">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C63" t="s">
         <v>65</v>
-      </c>
-      <c r="D60" t="s">
-        <v>66</v>
-      </c>
-      <c r="E60" t="s">
-        <v>67</v>
-      </c>
-      <c r="F60">
-        <v>0.25</v>
-      </c>
-      <c r="G60" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A61">
-        <v>501</v>
-      </c>
-      <c r="B61" t="str">
-        <f t="shared" si="0"/>
-        <v>501</v>
-      </c>
-      <c r="C61" t="s">
-        <v>68</v>
-      </c>
-      <c r="D61" t="s">
-        <v>66</v>
-      </c>
-      <c r="E61" t="s">
-        <v>67</v>
-      </c>
-      <c r="F61">
-        <v>0.25</v>
-      </c>
-      <c r="G61" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A62">
-        <v>516</v>
-      </c>
-      <c r="B62" t="str">
-        <f t="shared" si="0"/>
-        <v>516</v>
-      </c>
-      <c r="C62" t="s">
-        <v>69</v>
-      </c>
-      <c r="D62" t="s">
-        <v>66</v>
-      </c>
-      <c r="E62" t="s">
-        <v>67</v>
-      </c>
-      <c r="F62">
-        <v>0.25</v>
-      </c>
-      <c r="G62" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A63">
-        <v>517</v>
-      </c>
-      <c r="B63" t="str">
-        <f t="shared" si="0"/>
-        <v>517</v>
-      </c>
-      <c r="C63" t="s">
-        <v>70</v>
       </c>
       <c r="D63" t="s">
         <v>66</v>
@@ -3047,16 +3059,16 @@
         <v>151</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>522</v>
+        <v>501</v>
       </c>
       <c r="B64" t="str">
         <f t="shared" si="0"/>
-        <v>522</v>
+        <v>501</v>
       </c>
       <c r="C64" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D64" t="s">
         <v>66</v>
@@ -3071,16 +3083,16 @@
         <v>151</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="B65" t="str">
         <f t="shared" si="0"/>
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="C65" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D65" t="s">
         <v>66</v>
@@ -3095,16 +3107,16 @@
         <v>151</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="B66" t="str">
         <f t="shared" si="0"/>
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="C66" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D66" t="s">
         <v>66</v>
@@ -3119,16 +3131,16 @@
         <v>151</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="B67" t="str">
-        <f t="shared" ref="B67:B130" si="1">TEXT(A67,"000")</f>
-        <v>527</v>
+        <f t="shared" si="0"/>
+        <v>522</v>
       </c>
       <c r="C67" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D67" t="s">
         <v>66</v>
@@ -3143,2000 +3155,2117 @@
         <v>151</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68">
+        <v>523</v>
+      </c>
+      <c r="B68" t="str">
+        <f t="shared" si="0"/>
+        <v>523</v>
+      </c>
+      <c r="C68" t="s">
+        <v>72</v>
+      </c>
+      <c r="D68" t="s">
+        <v>66</v>
+      </c>
+      <c r="E68" t="s">
+        <v>67</v>
+      </c>
+      <c r="F68">
+        <v>0.25</v>
+      </c>
+      <c r="G68" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>526</v>
+      </c>
+      <c r="B69" t="str">
+        <f t="shared" si="0"/>
+        <v>526</v>
+      </c>
+      <c r="C69" t="s">
+        <v>73</v>
+      </c>
+      <c r="D69" t="s">
+        <v>66</v>
+      </c>
+      <c r="E69" t="s">
+        <v>67</v>
+      </c>
+      <c r="F69">
+        <v>0.25</v>
+      </c>
+      <c r="G69" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>527</v>
+      </c>
+      <c r="B70" t="str">
+        <f t="shared" ref="B70:B135" si="1">TEXT(A70,"000")</f>
+        <v>527</v>
+      </c>
+      <c r="C70" t="s">
+        <v>74</v>
+      </c>
+      <c r="D70" t="s">
+        <v>66</v>
+      </c>
+      <c r="E70" t="s">
+        <v>67</v>
+      </c>
+      <c r="F70">
+        <v>0.25</v>
+      </c>
+      <c r="G70" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71">
         <v>528</v>
       </c>
-      <c r="B68" t="str">
+      <c r="B71" t="str">
         <f t="shared" si="1"/>
         <v>528</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C71" t="s">
         <v>75</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D71" t="s">
         <v>66</v>
       </c>
-      <c r="E68" t="s">
+      <c r="E71" t="s">
         <v>67</v>
       </c>
-      <c r="F68">
+      <c r="F71">
         <v>0.25</v>
       </c>
-      <c r="G68" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A69">
+      <c r="G71" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72">
         <v>529</v>
       </c>
-      <c r="B69" t="str">
+      <c r="B72" t="str">
         <f t="shared" si="1"/>
         <v>529</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C72" t="s">
         <v>76</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D72" t="s">
         <v>66</v>
       </c>
-      <c r="E69" t="s">
+      <c r="E72" t="s">
         <v>67</v>
       </c>
-      <c r="F69">
+      <c r="F72">
         <v>0.25</v>
       </c>
-      <c r="G69" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A70">
+      <c r="G72" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73">
         <v>530</v>
       </c>
-      <c r="B70" t="str">
+      <c r="B73" t="str">
         <f t="shared" si="1"/>
         <v>530</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C73" t="s">
         <v>77</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D73" t="s">
         <v>66</v>
       </c>
-      <c r="E70" t="s">
+      <c r="E73" t="s">
         <v>67</v>
       </c>
-      <c r="F70">
+      <c r="F73">
         <v>0.25</v>
       </c>
-      <c r="G70" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A71">
+      <c r="G73" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74">
         <v>531</v>
       </c>
-      <c r="B71" t="str">
+      <c r="B74" t="str">
         <f t="shared" si="1"/>
         <v>531</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C74" t="s">
         <v>78</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D74" t="s">
         <v>66</v>
       </c>
-      <c r="E71" t="s">
+      <c r="E74" t="s">
         <v>67</v>
       </c>
-      <c r="F71">
+      <c r="F74">
         <v>0.25</v>
       </c>
-      <c r="G71" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A72">
+      <c r="G74" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75">
         <v>532</v>
       </c>
-      <c r="B72" t="str">
+      <c r="B75" t="str">
         <f t="shared" si="1"/>
         <v>532</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C75" t="s">
         <v>79</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D75" t="s">
         <v>66</v>
       </c>
-      <c r="E72" t="s">
+      <c r="E75" t="s">
         <v>67</v>
       </c>
-      <c r="F72">
+      <c r="F75">
         <v>0.25</v>
       </c>
-      <c r="G72" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A73">
+      <c r="G75" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76">
         <v>533</v>
       </c>
-      <c r="B73" t="str">
+      <c r="B76" t="str">
         <f t="shared" si="1"/>
         <v>533</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C76" t="s">
         <v>80</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D76" t="s">
         <v>66</v>
       </c>
-      <c r="E73" t="s">
+      <c r="E76" t="s">
         <v>67</v>
       </c>
-      <c r="F73">
+      <c r="F76">
         <v>0.25</v>
       </c>
-      <c r="G73" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A74">
+      <c r="G76" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77">
         <v>535</v>
       </c>
-      <c r="B74" t="str">
+      <c r="B77" t="str">
         <f t="shared" si="1"/>
         <v>535</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C77" t="s">
         <v>81</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D77" t="s">
         <v>66</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E77" t="s">
         <v>67</v>
       </c>
-      <c r="F74">
+      <c r="F77">
         <v>0.25</v>
       </c>
-      <c r="G74" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A75">
+      <c r="G77" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78">
         <v>550</v>
       </c>
-      <c r="B75" t="str">
+      <c r="B78" t="str">
         <f t="shared" si="1"/>
         <v>550</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C78" t="s">
         <v>82</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D78" t="s">
         <v>83</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E78" t="s">
         <v>84</v>
       </c>
-      <c r="F75">
+      <c r="F78">
         <v>0.25</v>
       </c>
-      <c r="G75" t="s">
+      <c r="G78" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A76">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79">
         <v>580</v>
       </c>
-      <c r="B76" t="str">
+      <c r="B79" t="str">
         <f t="shared" si="1"/>
         <v>580</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C79" t="s">
         <v>85</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D79" t="s">
         <v>83</v>
       </c>
-      <c r="E76" t="s">
+      <c r="E79" t="s">
         <v>84</v>
       </c>
-      <c r="F76">
+      <c r="F79">
         <v>0.25</v>
       </c>
-      <c r="G76" t="s">
+      <c r="G79" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A77">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80">
         <v>581</v>
       </c>
-      <c r="B77" t="str">
+      <c r="B80" t="str">
         <f t="shared" si="1"/>
         <v>581</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C80" t="s">
         <v>86</v>
       </c>
-      <c r="D77" t="s">
+      <c r="D80" t="s">
         <v>83</v>
       </c>
-      <c r="E77" t="s">
+      <c r="E80" t="s">
         <v>84</v>
       </c>
-      <c r="F77">
+      <c r="F80">
         <v>0.25</v>
       </c>
-      <c r="G77" t="s">
+      <c r="G80" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A78">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81">
         <v>583</v>
       </c>
-      <c r="B78" t="str">
+      <c r="B81" t="str">
         <f t="shared" si="1"/>
         <v>583</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C81" t="s">
         <v>87</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D81" t="s">
         <v>83</v>
       </c>
-      <c r="E78" t="s">
+      <c r="E81" t="s">
         <v>84</v>
       </c>
-      <c r="F78">
+      <c r="F81">
         <v>0.25</v>
       </c>
-      <c r="G78" t="s">
+      <c r="G81" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A79">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82">
         <v>587</v>
       </c>
-      <c r="B79" t="str">
+      <c r="B82" t="str">
         <f t="shared" si="1"/>
         <v>587</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C82" t="s">
         <v>88</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D82" t="s">
         <v>83</v>
       </c>
-      <c r="E79" t="s">
+      <c r="E82" t="s">
         <v>84</v>
       </c>
-      <c r="F79">
+      <c r="F82">
         <v>0.25</v>
       </c>
-      <c r="G79" t="s">
+      <c r="G82" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A80">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83">
         <v>589</v>
       </c>
-      <c r="B80" t="str">
+      <c r="B83" t="str">
         <f t="shared" si="1"/>
         <v>589</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C83" t="s">
         <v>89</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D83" t="s">
         <v>83</v>
       </c>
-      <c r="E80" t="s">
+      <c r="E83" t="s">
         <v>84</v>
       </c>
-      <c r="F80">
+      <c r="F83">
         <v>0.25</v>
       </c>
-      <c r="G80" t="s">
+      <c r="G83" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A81">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84">
         <v>590</v>
       </c>
-      <c r="B81" t="str">
+      <c r="B84" t="str">
         <f t="shared" si="1"/>
         <v>590</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C84" t="s">
         <v>90</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D84" t="s">
         <v>66</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E84" t="s">
         <v>67</v>
       </c>
-      <c r="F81">
+      <c r="F84">
         <v>0.25</v>
       </c>
-      <c r="G81" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A82">
+      <c r="G84" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85">
         <v>591</v>
       </c>
-      <c r="B82" t="str">
+      <c r="B85" t="str">
         <f t="shared" si="1"/>
         <v>591</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C85" t="s">
         <v>91</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D85" t="s">
         <v>66</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E85" t="s">
         <v>67</v>
       </c>
-      <c r="F82">
+      <c r="F85">
         <v>0.25</v>
       </c>
-      <c r="G82" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A83">
+      <c r="G85" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86">
         <v>592</v>
       </c>
-      <c r="B83" t="str">
+      <c r="B86" t="str">
         <f t="shared" si="1"/>
         <v>592</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C86" t="s">
         <v>92</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D86" t="s">
         <v>66</v>
       </c>
-      <c r="E83" t="s">
+      <c r="E86" t="s">
         <v>67</v>
       </c>
-      <c r="F83">
+      <c r="F86">
         <v>0.25</v>
       </c>
-      <c r="G83" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A84">
+      <c r="G86" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87">
         <v>593</v>
       </c>
-      <c r="B84" t="str">
+      <c r="B87" t="str">
         <f t="shared" si="1"/>
         <v>593</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C87" t="s">
         <v>93</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D87" t="s">
         <v>66</v>
       </c>
-      <c r="E84" t="s">
+      <c r="E87" t="s">
         <v>67</v>
       </c>
-      <c r="F84">
+      <c r="F87">
         <v>0.25</v>
       </c>
-      <c r="G84" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A85">
+      <c r="G87" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88">
         <v>597</v>
       </c>
-      <c r="B85" t="str">
+      <c r="B88" t="str">
         <f t="shared" si="1"/>
         <v>597</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C88" t="s">
         <v>94</v>
       </c>
-      <c r="D85" t="s">
+      <c r="D88" t="s">
         <v>66</v>
       </c>
-      <c r="E85" t="s">
+      <c r="E88" t="s">
         <v>67</v>
       </c>
-      <c r="F85">
+      <c r="F88">
         <v>0.25</v>
       </c>
-      <c r="G85" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A86">
+      <c r="G88" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89">
         <v>599</v>
       </c>
-      <c r="B86" t="str">
+      <c r="B89" t="str">
         <f t="shared" si="1"/>
         <v>599</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C89" t="s">
         <v>95</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D89" t="s">
         <v>66</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E89" t="s">
         <v>67</v>
       </c>
-      <c r="F86">
+      <c r="F89">
         <v>0.25</v>
       </c>
-      <c r="G86" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A87">
+      <c r="G89" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90">
         <v>637</v>
       </c>
-      <c r="B87" t="str">
+      <c r="B90" t="str">
         <f t="shared" si="1"/>
         <v>637</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C90" t="s">
         <v>96</v>
       </c>
-      <c r="D87" t="s">
+      <c r="D90" t="s">
         <v>97</v>
       </c>
-      <c r="E87" t="s">
+      <c r="E90" t="s">
         <v>98</v>
       </c>
-      <c r="F87">
+      <c r="F90">
         <v>0.1</v>
       </c>
-      <c r="G87" t="s">
+      <c r="G90" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A88">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91">
         <v>638</v>
       </c>
-      <c r="B88" t="str">
+      <c r="B91" t="str">
         <f t="shared" si="1"/>
         <v>638</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C91" t="s">
         <v>99</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D91" t="s">
         <v>97</v>
       </c>
-      <c r="E88" t="s">
+      <c r="E91" t="s">
         <v>98</v>
       </c>
-      <c r="F88">
+      <c r="F91">
         <v>0.1</v>
       </c>
-      <c r="G88" t="s">
+      <c r="G91" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A89">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92">
         <v>654</v>
       </c>
-      <c r="B89" t="str">
+      <c r="B92" t="str">
         <f t="shared" si="1"/>
         <v>654</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C92" t="s">
         <v>100</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D92" t="s">
         <v>97</v>
       </c>
-      <c r="E89" t="s">
+      <c r="E92" t="s">
         <v>98</v>
       </c>
-      <c r="F89">
+      <c r="F92">
         <v>0.1</v>
       </c>
-      <c r="G89" t="s">
+      <c r="G92" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A90">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93">
         <v>655</v>
       </c>
-      <c r="B90" t="str">
+      <c r="B93" t="str">
         <f t="shared" si="1"/>
         <v>655</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C93" t="s">
         <v>101</v>
       </c>
-      <c r="D90" t="s">
+      <c r="D93" t="s">
         <v>97</v>
       </c>
-      <c r="E90" t="s">
+      <c r="E93" t="s">
         <v>98</v>
       </c>
-      <c r="F90">
+      <c r="F93">
         <v>0.1</v>
       </c>
-      <c r="G90" t="s">
+      <c r="G93" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A91">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94">
         <v>663</v>
       </c>
-      <c r="B91" t="str">
+      <c r="B94" t="str">
         <f t="shared" si="1"/>
         <v>663</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C94" t="s">
         <v>93</v>
       </c>
-      <c r="D91" t="s">
+      <c r="D94" t="s">
         <v>102</v>
       </c>
-      <c r="E91" t="s">
+      <c r="E94" t="s">
         <v>103</v>
       </c>
-      <c r="F91">
+      <c r="F94">
         <v>0.108333</v>
       </c>
-      <c r="G91" t="s">
+      <c r="G94" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A92">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95">
         <v>668</v>
       </c>
-      <c r="B92" t="str">
+      <c r="B95" t="str">
         <f t="shared" si="1"/>
         <v>668</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C95" t="s">
         <v>104</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D95" t="s">
         <v>97</v>
       </c>
-      <c r="E92" t="s">
+      <c r="E95" t="s">
         <v>98</v>
       </c>
-      <c r="F92">
+      <c r="F95">
         <v>0.1</v>
       </c>
-      <c r="G92" t="s">
+      <c r="G95" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A93">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96">
         <v>670</v>
       </c>
-      <c r="B93" t="str">
+      <c r="B96" t="str">
         <f t="shared" si="1"/>
         <v>670</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C96" t="s">
         <v>85</v>
       </c>
-      <c r="D93" t="s">
+      <c r="D96" t="s">
         <v>102</v>
       </c>
-      <c r="E93" t="s">
+      <c r="E96" t="s">
         <v>103</v>
       </c>
-      <c r="F93">
+      <c r="F96">
         <v>0.108333</v>
       </c>
-      <c r="G93" t="s">
+      <c r="G96" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A94">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97">
         <v>671</v>
       </c>
-      <c r="B94" t="str">
+      <c r="B97" t="str">
         <f t="shared" si="1"/>
         <v>671</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C97" t="s">
         <v>105</v>
       </c>
-      <c r="D94" t="s">
+      <c r="D97" t="s">
         <v>102</v>
       </c>
-      <c r="E94" t="s">
+      <c r="E97" t="s">
         <v>103</v>
       </c>
-      <c r="F94">
+      <c r="F97">
         <v>0.108333</v>
       </c>
-      <c r="G94" t="s">
+      <c r="G97" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A95">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98">
         <v>673</v>
       </c>
-      <c r="B95" t="str">
+      <c r="B98" t="str">
         <f t="shared" si="1"/>
         <v>673</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C98" t="s">
         <v>87</v>
       </c>
-      <c r="D95" t="s">
+      <c r="D98" t="s">
         <v>102</v>
       </c>
-      <c r="E95" t="s">
+      <c r="E98" t="s">
         <v>103</v>
       </c>
-      <c r="F95">
+      <c r="F98">
         <v>0.108333</v>
       </c>
-      <c r="G95" t="s">
+      <c r="G98" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A96">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99">
         <v>677</v>
       </c>
-      <c r="B96" t="str">
+      <c r="B99" t="str">
         <f t="shared" si="1"/>
         <v>677</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C99" t="s">
         <v>88</v>
       </c>
-      <c r="D96" t="s">
+      <c r="D99" t="s">
         <v>102</v>
       </c>
-      <c r="E96" t="s">
+      <c r="E99" t="s">
         <v>103</v>
       </c>
-      <c r="F96">
+      <c r="F99">
         <v>0.108333</v>
       </c>
-      <c r="G96" t="s">
+      <c r="G99" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A97">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100">
         <v>679</v>
       </c>
-      <c r="B97" t="str">
+      <c r="B100" t="str">
         <f t="shared" si="1"/>
         <v>679</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C100" t="s">
         <v>89</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D100" t="s">
         <v>102</v>
       </c>
-      <c r="E97" t="s">
+      <c r="E100" t="s">
         <v>103</v>
       </c>
-      <c r="F97">
+      <c r="F100">
         <v>0.108333</v>
       </c>
-      <c r="G97" t="s">
+      <c r="G100" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A98">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101">
         <v>680</v>
       </c>
-      <c r="B98" t="str">
+      <c r="B101" t="str">
         <f t="shared" si="1"/>
         <v>680</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C101" t="s">
         <v>85</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D101" t="s">
         <v>106</v>
       </c>
-      <c r="E98" t="s">
+      <c r="E101" t="s">
         <v>107</v>
       </c>
-      <c r="F98">
+      <c r="F101">
         <v>0.2</v>
       </c>
-      <c r="G98" t="s">
+      <c r="G101" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A99">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102">
         <v>683</v>
       </c>
-      <c r="B99" t="str">
+      <c r="B102" t="str">
         <f t="shared" si="1"/>
         <v>683</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C102" t="s">
         <v>87</v>
       </c>
-      <c r="D99" t="s">
+      <c r="D102" t="s">
         <v>106</v>
       </c>
-      <c r="E99" t="s">
+      <c r="E102" t="s">
         <v>107</v>
       </c>
-      <c r="F99">
+      <c r="F102">
         <v>0.2</v>
       </c>
-      <c r="G99" t="s">
+      <c r="G102" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A100">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103">
         <v>687</v>
       </c>
-      <c r="B100" t="str">
+      <c r="B103" t="str">
         <f t="shared" si="1"/>
         <v>687</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C103" t="s">
         <v>88</v>
       </c>
-      <c r="D100" t="s">
+      <c r="D103" t="s">
         <v>106</v>
       </c>
-      <c r="E100" t="s">
+      <c r="E103" t="s">
         <v>107</v>
       </c>
-      <c r="F100">
+      <c r="F103">
         <v>0.2</v>
       </c>
-      <c r="G100" t="s">
+      <c r="G103" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A101">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104">
         <v>693</v>
       </c>
-      <c r="B101" t="str">
+      <c r="B104" t="str">
         <f t="shared" si="1"/>
         <v>693</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C104" t="s">
         <v>93</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D104" t="s">
         <v>106</v>
       </c>
-      <c r="E101" t="s">
+      <c r="E104" t="s">
         <v>107</v>
       </c>
-      <c r="F101">
+      <c r="F104">
         <v>0.2</v>
       </c>
-      <c r="G101" t="s">
+      <c r="G104" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A102">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105">
         <v>717</v>
       </c>
-      <c r="B102" t="str">
+      <c r="B105" t="str">
         <f t="shared" si="1"/>
         <v>717</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C105" t="s">
         <v>108</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D105" t="s">
         <v>109</v>
       </c>
-      <c r="E102" t="s">
+      <c r="E105" t="s">
         <v>110</v>
       </c>
-      <c r="F102">
+      <c r="F105">
         <v>0.101743</v>
       </c>
-      <c r="G102" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A103">
+      <c r="G105" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106">
         <v>722</v>
       </c>
-      <c r="B103" t="str">
+      <c r="B106" t="str">
         <f t="shared" si="1"/>
         <v>722</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C106" t="s">
         <v>111</v>
       </c>
-      <c r="D103" t="s">
+      <c r="D106" t="s">
         <v>109</v>
       </c>
-      <c r="E103" t="s">
+      <c r="E106" t="s">
         <v>110</v>
       </c>
-      <c r="F103">
+      <c r="F106">
         <v>0.101743</v>
       </c>
-      <c r="G103" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A104">
+      <c r="G106" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107">
         <v>723</v>
       </c>
-      <c r="B104" t="str">
+      <c r="B107" t="str">
         <f t="shared" si="1"/>
         <v>723</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C107" t="s">
         <v>112</v>
       </c>
-      <c r="D104" t="s">
+      <c r="D107" t="s">
         <v>109</v>
       </c>
-      <c r="E104" t="s">
+      <c r="E107" t="s">
         <v>110</v>
       </c>
-      <c r="F104">
+      <c r="F107">
         <v>0.101743</v>
       </c>
-      <c r="G104" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A105">
+      <c r="G107" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108">
         <v>728</v>
       </c>
-      <c r="B105" t="str">
+      <c r="B108" t="str">
         <f t="shared" si="1"/>
         <v>728</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C108" t="s">
         <v>75</v>
       </c>
-      <c r="D105" t="s">
+      <c r="D108" t="s">
         <v>109</v>
       </c>
-      <c r="E105" t="s">
+      <c r="E108" t="s">
         <v>110</v>
       </c>
-      <c r="F105">
+      <c r="F108">
         <v>0.101743</v>
       </c>
-      <c r="G105" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A106">
+      <c r="G108" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109">
         <v>729</v>
       </c>
-      <c r="B106" t="str">
+      <c r="B109" t="str">
         <f t="shared" si="1"/>
         <v>729</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C109" t="s">
         <v>76</v>
       </c>
-      <c r="D106" t="s">
+      <c r="D109" t="s">
         <v>109</v>
       </c>
-      <c r="E106" t="s">
+      <c r="E109" t="s">
         <v>110</v>
       </c>
-      <c r="F106">
+      <c r="F109">
         <v>0.101743</v>
       </c>
-      <c r="G106" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A107">
+      <c r="G109" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110">
         <v>730</v>
       </c>
-      <c r="B107" t="str">
+      <c r="B110" t="str">
         <f t="shared" si="1"/>
         <v>730</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C110" t="s">
         <v>77</v>
       </c>
-      <c r="D107" t="s">
+      <c r="D110" t="s">
         <v>109</v>
       </c>
-      <c r="E107" t="s">
+      <c r="E110" t="s">
         <v>110</v>
       </c>
-      <c r="F107">
+      <c r="F110">
         <v>0.101743</v>
       </c>
-      <c r="G107" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A108">
+      <c r="G110" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111">
         <v>731</v>
       </c>
-      <c r="B108" t="str">
+      <c r="B111" t="str">
         <f t="shared" si="1"/>
         <v>731</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C111" t="s">
         <v>78</v>
       </c>
-      <c r="D108" t="s">
+      <c r="D111" t="s">
         <v>109</v>
       </c>
-      <c r="E108" t="s">
+      <c r="E111" t="s">
         <v>110</v>
       </c>
-      <c r="F108">
+      <c r="F111">
         <v>0.101743</v>
       </c>
-      <c r="G108" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A109">
+      <c r="G111" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112">
         <v>746</v>
       </c>
-      <c r="B109" t="str">
+      <c r="B112" t="str">
         <f t="shared" si="1"/>
         <v>746</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C112" t="s">
         <v>113</v>
       </c>
-      <c r="D109" t="s">
+      <c r="D112" t="s">
         <v>114</v>
       </c>
-      <c r="E109" t="s">
+      <c r="E112" t="s">
         <v>115</v>
       </c>
-      <c r="F109">
+      <c r="F112">
         <v>0.101743</v>
       </c>
-      <c r="G109" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A110">
+      <c r="G112" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113">
         <v>748</v>
       </c>
-      <c r="B110" t="str">
+      <c r="B113" t="str">
         <f t="shared" si="1"/>
         <v>748</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C113" t="s">
         <v>76</v>
       </c>
-      <c r="D110" t="s">
+      <c r="D113" t="s">
         <v>114</v>
       </c>
-      <c r="E110" t="s">
+      <c r="E113" t="s">
         <v>115</v>
       </c>
-      <c r="F110">
+      <c r="F113">
         <v>0.101743</v>
       </c>
-      <c r="G110" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A111">
+      <c r="G113" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114">
         <v>752</v>
       </c>
-      <c r="B111" t="str">
+      <c r="B114" t="str">
         <f t="shared" si="1"/>
         <v>752</v>
       </c>
-      <c r="C111" t="s">
+      <c r="C114" t="s">
         <v>111</v>
       </c>
-      <c r="D111" t="s">
+      <c r="D114" t="s">
         <v>114</v>
       </c>
-      <c r="E111" t="s">
+      <c r="E114" t="s">
         <v>115</v>
       </c>
-      <c r="F111">
+      <c r="F114">
         <v>0.101743</v>
       </c>
-      <c r="G111" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A112">
+      <c r="G114" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115">
         <v>760</v>
       </c>
-      <c r="B112" t="str">
+      <c r="B115" t="str">
         <f t="shared" si="1"/>
         <v>760</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C115" t="s">
         <v>77</v>
       </c>
-      <c r="D112" t="s">
+      <c r="D115" t="s">
         <v>114</v>
       </c>
-      <c r="E112" t="s">
+      <c r="E115" t="s">
         <v>115</v>
       </c>
-      <c r="F112">
+      <c r="F115">
         <v>0.101743</v>
       </c>
-      <c r="G112" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A113">
+      <c r="G115" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116">
         <v>765</v>
       </c>
-      <c r="B113" t="str">
+      <c r="B116" t="str">
         <f t="shared" si="1"/>
         <v>765</v>
       </c>
-      <c r="C113" t="s">
+      <c r="C116" t="s">
         <v>116</v>
       </c>
-      <c r="D113" t="s">
+      <c r="D116" t="s">
         <v>114</v>
       </c>
-      <c r="E113" t="s">
+      <c r="E116" t="s">
         <v>115</v>
       </c>
-      <c r="F113">
+      <c r="F116">
         <v>0.101743</v>
       </c>
-      <c r="G113" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A114">
+      <c r="G116" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117">
         <v>767</v>
       </c>
-      <c r="B114" t="str">
+      <c r="B117" t="str">
         <f t="shared" si="1"/>
         <v>767</v>
       </c>
-      <c r="C114" t="s">
+      <c r="C117" t="s">
         <v>94</v>
       </c>
-      <c r="D114" t="s">
+      <c r="D117" t="s">
         <v>114</v>
       </c>
-      <c r="E114" t="s">
+      <c r="E117" t="s">
         <v>115</v>
       </c>
-      <c r="F114">
+      <c r="F117">
         <v>0.101743</v>
       </c>
-      <c r="G114" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A115">
+      <c r="G117" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118">
         <v>774</v>
       </c>
-      <c r="B115" t="str">
+      <c r="B118" t="str">
         <f t="shared" si="1"/>
         <v>774</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C118" t="s">
         <v>117</v>
       </c>
-      <c r="D115" t="s">
+      <c r="D118" t="s">
         <v>114</v>
       </c>
-      <c r="E115" t="s">
+      <c r="E118" t="s">
         <v>115</v>
       </c>
-      <c r="F115">
+      <c r="F118">
         <v>0.101743</v>
       </c>
-      <c r="G115" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A116">
+      <c r="G118" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119">
         <v>790</v>
       </c>
-      <c r="B116" t="str">
+      <c r="B119" t="str">
         <f t="shared" si="1"/>
         <v>790</v>
       </c>
-      <c r="C116" t="s">
+      <c r="C119" t="s">
         <v>118</v>
       </c>
-      <c r="D116" t="s">
+      <c r="D119" t="s">
         <v>109</v>
       </c>
-      <c r="E116" t="s">
+      <c r="E119" t="s">
         <v>110</v>
       </c>
-      <c r="F116">
+      <c r="F119">
         <v>0.101743</v>
       </c>
-      <c r="G116" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A117">
+      <c r="G119" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120">
         <v>791</v>
       </c>
-      <c r="B117" t="str">
+      <c r="B120" t="str">
         <f t="shared" si="1"/>
         <v>791</v>
       </c>
-      <c r="C117" t="s">
+      <c r="C120" t="s">
         <v>119</v>
       </c>
-      <c r="D117" t="s">
+      <c r="D120" t="s">
         <v>109</v>
       </c>
-      <c r="E117" t="s">
+      <c r="E120" t="s">
         <v>110</v>
       </c>
-      <c r="F117">
+      <c r="F120">
         <v>0.101743</v>
       </c>
-      <c r="G117" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A118">
+      <c r="G120" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121">
         <v>792</v>
       </c>
-      <c r="B118" t="str">
+      <c r="B121" t="str">
         <f t="shared" si="1"/>
         <v>792</v>
       </c>
-      <c r="C118" t="s">
+      <c r="C121" t="s">
         <v>92</v>
       </c>
-      <c r="D118" t="s">
+      <c r="D121" t="s">
         <v>109</v>
       </c>
-      <c r="E118" t="s">
+      <c r="E121" t="s">
         <v>110</v>
       </c>
-      <c r="F118">
+      <c r="F121">
         <v>0.101743</v>
       </c>
-      <c r="G118" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A119">
+      <c r="G121" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122">
         <v>797</v>
       </c>
-      <c r="B119" t="str">
+      <c r="B122" t="str">
         <f t="shared" si="1"/>
         <v>797</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C122" t="s">
         <v>94</v>
       </c>
-      <c r="D119" t="s">
+      <c r="D122" t="s">
         <v>109</v>
       </c>
-      <c r="E119" t="s">
+      <c r="E122" t="s">
         <v>110</v>
       </c>
-      <c r="F119">
+      <c r="F122">
         <v>0.101743</v>
       </c>
-      <c r="G119" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A120">
+      <c r="G122" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123">
         <v>799</v>
       </c>
-      <c r="B120" t="str">
+      <c r="B123" t="str">
         <f t="shared" si="1"/>
         <v>799</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C123" t="s">
         <v>120</v>
       </c>
-      <c r="D120" t="s">
+      <c r="D123" t="s">
         <v>109</v>
       </c>
-      <c r="E120" t="s">
+      <c r="E123" t="s">
         <v>110</v>
       </c>
-      <c r="F120">
+      <c r="F123">
         <v>0.101743</v>
       </c>
-      <c r="G120" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A121">
+      <c r="G123" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>800</v>
+      </c>
+      <c r="B124" t="str">
+        <f t="shared" si="1"/>
+        <v>800</v>
+      </c>
+      <c r="C124" t="s">
+        <v>368</v>
+      </c>
+      <c r="D124" t="s">
+        <v>122</v>
+      </c>
+      <c r="E124" t="s">
+        <v>123</v>
+      </c>
+      <c r="F124">
+        <v>0.101743</v>
+      </c>
+      <c r="G124" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125">
         <v>801</v>
       </c>
-      <c r="B121" t="str">
+      <c r="B125" t="str">
         <f t="shared" si="1"/>
         <v>801</v>
       </c>
-      <c r="C121" t="s">
+      <c r="C125" t="s">
         <v>121</v>
       </c>
-      <c r="D121" t="s">
+      <c r="D125" t="s">
         <v>122</v>
       </c>
-      <c r="E121" t="s">
+      <c r="E125" t="s">
         <v>123</v>
       </c>
-      <c r="F121">
+      <c r="F125">
         <v>0.101743</v>
       </c>
-      <c r="G121" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A122">
+      <c r="G125" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126">
         <v>817</v>
       </c>
-      <c r="B122" t="str">
+      <c r="B126" t="str">
         <f t="shared" si="1"/>
         <v>817</v>
       </c>
-      <c r="C122" t="s">
+      <c r="C126" t="s">
         <v>70</v>
       </c>
-      <c r="D122" t="s">
+      <c r="D126" t="s">
         <v>122</v>
       </c>
-      <c r="E122" t="s">
+      <c r="E126" t="s">
         <v>123</v>
       </c>
-      <c r="F122">
+      <c r="F126">
         <v>0.101743</v>
       </c>
-      <c r="G122" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A123">
+      <c r="G126" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127">
         <v>823</v>
       </c>
-      <c r="B123" t="str">
+      <c r="B127" t="str">
         <f t="shared" si="1"/>
         <v>823</v>
       </c>
-      <c r="C123" t="s">
+      <c r="C127" t="s">
         <v>124</v>
       </c>
-      <c r="D123" t="s">
+      <c r="D127" t="s">
         <v>122</v>
       </c>
-      <c r="E123" t="s">
+      <c r="E127" t="s">
         <v>123</v>
       </c>
-      <c r="F123">
+      <c r="F127">
         <v>0.101743</v>
       </c>
-      <c r="G123" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A124">
+      <c r="G127" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>826</v>
+      </c>
+      <c r="B128" t="str">
+        <f t="shared" si="1"/>
+        <v>826</v>
+      </c>
+      <c r="D128" t="s">
+        <v>122</v>
+      </c>
+      <c r="E128" t="s">
+        <v>123</v>
+      </c>
+      <c r="F128">
+        <v>0.101743</v>
+      </c>
+      <c r="G128" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129">
         <v>827</v>
       </c>
-      <c r="B124" t="str">
+      <c r="B129" t="str">
         <f t="shared" si="1"/>
         <v>827</v>
       </c>
-      <c r="C124" t="s">
+      <c r="C129" t="s">
         <v>74</v>
       </c>
-      <c r="D124" t="s">
+      <c r="D129" t="s">
         <v>122</v>
       </c>
-      <c r="E124" t="s">
+      <c r="E129" t="s">
         <v>123</v>
       </c>
-      <c r="F124">
+      <c r="F129">
         <v>0.101743</v>
       </c>
-      <c r="G124" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A125">
+      <c r="G129" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130">
         <v>828</v>
       </c>
-      <c r="B125" t="str">
+      <c r="B130" t="str">
         <f t="shared" si="1"/>
         <v>828</v>
       </c>
-      <c r="C125" t="s">
+      <c r="C130" t="s">
         <v>75</v>
       </c>
-      <c r="D125" t="s">
+      <c r="D130" t="s">
         <v>122</v>
       </c>
-      <c r="E125" t="s">
+      <c r="E130" t="s">
         <v>123</v>
       </c>
-      <c r="F125">
+      <c r="F130">
         <v>0.101743</v>
       </c>
-      <c r="G125" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A126">
+      <c r="G130" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A131">
         <v>829</v>
       </c>
-      <c r="B126" t="str">
+      <c r="B131" t="str">
         <f t="shared" si="1"/>
         <v>829</v>
       </c>
-      <c r="C126" t="s">
+      <c r="C131" t="s">
         <v>76</v>
       </c>
-      <c r="D126" t="s">
+      <c r="D131" t="s">
         <v>122</v>
       </c>
-      <c r="E126" t="s">
+      <c r="E131" t="s">
         <v>123</v>
       </c>
-      <c r="F126">
+      <c r="F131">
         <v>0.101743</v>
       </c>
-      <c r="G126" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A127">
+      <c r="G131" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A132">
         <v>830</v>
       </c>
-      <c r="B127" t="str">
+      <c r="B132" t="str">
         <f t="shared" si="1"/>
         <v>830</v>
       </c>
-      <c r="C127" t="s">
+      <c r="C132" t="s">
         <v>77</v>
       </c>
-      <c r="D127" t="s">
+      <c r="D132" t="s">
         <v>122</v>
       </c>
-      <c r="E127" t="s">
+      <c r="E132" t="s">
         <v>123</v>
       </c>
-      <c r="F127">
+      <c r="F132">
         <v>0.101743</v>
       </c>
-      <c r="G127" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A128">
+      <c r="G132" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A133">
         <v>831</v>
       </c>
-      <c r="B128" t="str">
+      <c r="B133" t="str">
         <f t="shared" si="1"/>
         <v>831</v>
       </c>
-      <c r="C128" t="s">
+      <c r="C133" t="s">
         <v>125</v>
       </c>
-      <c r="D128" t="s">
+      <c r="D133" t="s">
         <v>122</v>
       </c>
-      <c r="E128" t="s">
+      <c r="E133" t="s">
         <v>123</v>
       </c>
-      <c r="F128">
+      <c r="F133">
         <v>0.101743</v>
       </c>
-      <c r="G128" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A129">
+      <c r="G133" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A134">
         <v>833</v>
       </c>
-      <c r="B129" t="str">
+      <c r="B134" t="str">
         <f t="shared" si="1"/>
         <v>833</v>
       </c>
-      <c r="C129" t="s">
+      <c r="C134" t="s">
         <v>80</v>
       </c>
-      <c r="D129" t="s">
+      <c r="D134" t="s">
         <v>122</v>
       </c>
-      <c r="E129" t="s">
+      <c r="E134" t="s">
         <v>123</v>
       </c>
-      <c r="F129">
+      <c r="F134">
         <v>0.101743</v>
       </c>
-      <c r="G129" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A130">
+      <c r="G134" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A135">
         <v>880</v>
       </c>
-      <c r="B130" t="str">
+      <c r="B135" t="str">
         <f t="shared" si="1"/>
         <v>880</v>
       </c>
-      <c r="C130" t="s">
+      <c r="C135" t="s">
         <v>85</v>
       </c>
-      <c r="D130" t="s">
+      <c r="D135" t="s">
         <v>126</v>
       </c>
-      <c r="E130" t="s">
+      <c r="E135" t="s">
         <v>123</v>
       </c>
-      <c r="F130">
+      <c r="F135">
         <v>0.101743</v>
       </c>
-      <c r="G130" t="s">
+      <c r="G135" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A131">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A136">
         <v>881</v>
       </c>
-      <c r="B131" t="str">
-        <f t="shared" ref="B131:B150" si="2">TEXT(A131,"000")</f>
+      <c r="B136" t="str">
+        <f t="shared" ref="B136:B155" si="2">TEXT(A136,"000")</f>
         <v>881</v>
       </c>
-      <c r="C131" t="s">
+      <c r="C136" t="s">
         <v>105</v>
       </c>
-      <c r="D131" t="s">
+      <c r="D136" t="s">
         <v>126</v>
       </c>
-      <c r="E131" t="s">
+      <c r="E136" t="s">
         <v>123</v>
       </c>
-      <c r="F131">
+      <c r="F136">
         <v>0.101743</v>
       </c>
-      <c r="G131" t="s">
+      <c r="G136" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A132">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A137">
         <v>883</v>
       </c>
-      <c r="B132" t="str">
+      <c r="B137" t="str">
         <f t="shared" si="2"/>
         <v>883</v>
       </c>
-      <c r="C132" t="s">
+      <c r="C137" t="s">
         <v>80</v>
       </c>
-      <c r="D132" t="s">
+      <c r="D137" t="s">
         <v>126</v>
       </c>
-      <c r="E132" t="s">
+      <c r="E137" t="s">
         <v>123</v>
       </c>
-      <c r="F132">
+      <c r="F137">
         <v>0.101743</v>
       </c>
-      <c r="G132" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A133">
+      <c r="G137" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138">
         <v>887</v>
       </c>
-      <c r="B133" t="str">
+      <c r="B138" t="str">
         <f t="shared" si="2"/>
         <v>887</v>
       </c>
-      <c r="C133" t="s">
+      <c r="C138" t="s">
         <v>88</v>
       </c>
-      <c r="D133" t="s">
+      <c r="D138" t="s">
         <v>126</v>
       </c>
-      <c r="E133" t="s">
+      <c r="E138" t="s">
         <v>123</v>
       </c>
-      <c r="F133">
+      <c r="F138">
         <v>0.101743</v>
       </c>
-      <c r="G133" t="s">
+      <c r="G138" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A134">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A139">
         <v>889</v>
       </c>
-      <c r="B134" t="str">
+      <c r="B139" t="str">
         <f t="shared" si="2"/>
         <v>889</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C139" t="s">
         <v>89</v>
       </c>
-      <c r="D134" t="s">
+      <c r="D139" t="s">
         <v>126</v>
       </c>
-      <c r="E134" t="s">
+      <c r="E139" t="s">
         <v>123</v>
       </c>
-      <c r="F134">
+      <c r="F139">
         <v>0.101743</v>
       </c>
-      <c r="G134" t="s">
+      <c r="G139" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A135">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A140">
         <v>890</v>
       </c>
-      <c r="B135" t="str">
+      <c r="B140" t="str">
         <f t="shared" si="2"/>
         <v>890</v>
       </c>
-      <c r="C135" t="s">
+      <c r="C140" t="s">
         <v>127</v>
       </c>
-      <c r="D135" t="s">
+      <c r="D140" t="s">
         <v>126</v>
       </c>
-      <c r="E135" t="s">
+      <c r="E140" t="s">
         <v>123</v>
       </c>
-      <c r="F135">
+      <c r="F140">
         <v>0.101743</v>
       </c>
-      <c r="G135" t="s">
+      <c r="G140" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A136">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A141">
         <v>891</v>
       </c>
-      <c r="B136" t="str">
+      <c r="B141" t="str">
         <f t="shared" si="2"/>
         <v>891</v>
       </c>
-      <c r="C136" t="s">
+      <c r="C141" t="s">
         <v>117</v>
       </c>
-      <c r="D136" t="s">
+      <c r="D141" t="s">
         <v>122</v>
       </c>
-      <c r="E136" t="s">
+      <c r="E141" t="s">
         <v>123</v>
       </c>
-      <c r="F136">
+      <c r="F141">
         <v>0.101743</v>
       </c>
-      <c r="G136" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A137">
+      <c r="G141" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142">
         <v>892</v>
       </c>
-      <c r="B137" t="str">
+      <c r="B142" t="str">
         <f t="shared" si="2"/>
         <v>892</v>
       </c>
-      <c r="C137" t="s">
+      <c r="C142" t="s">
         <v>92</v>
       </c>
-      <c r="D137" t="s">
+      <c r="D142" t="s">
         <v>122</v>
       </c>
-      <c r="E137" t="s">
+      <c r="E142" t="s">
         <v>123</v>
       </c>
-      <c r="F137">
+      <c r="F142">
         <v>0.101743</v>
       </c>
-      <c r="G137" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A138">
+      <c r="G142" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143">
         <v>893</v>
       </c>
-      <c r="B138" t="str">
+      <c r="B143" t="str">
         <f t="shared" si="2"/>
         <v>893</v>
       </c>
-      <c r="C138" t="s">
+      <c r="C143" t="s">
         <v>93</v>
       </c>
-      <c r="D138" t="s">
+      <c r="D143" t="s">
         <v>126</v>
       </c>
-      <c r="E138" t="s">
+      <c r="E143" t="s">
         <v>123</v>
       </c>
-      <c r="F138">
+      <c r="F143">
         <v>0.101743</v>
       </c>
-      <c r="G138" t="s">
+      <c r="G143" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A139">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144">
         <v>897</v>
       </c>
-      <c r="B139" t="str">
+      <c r="B144" t="str">
         <f t="shared" si="2"/>
         <v>897</v>
       </c>
-      <c r="C139" t="s">
+      <c r="C144" t="s">
         <v>94</v>
       </c>
-      <c r="D139" t="s">
+      <c r="D144" t="s">
         <v>122</v>
       </c>
-      <c r="E139" t="s">
+      <c r="E144" t="s">
         <v>123</v>
       </c>
-      <c r="F139">
+      <c r="F144">
         <v>0.101743</v>
       </c>
-      <c r="G139" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A140">
+      <c r="G144" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145">
         <v>899</v>
       </c>
-      <c r="B140" t="str">
+      <c r="B145" t="str">
         <f t="shared" si="2"/>
         <v>899</v>
       </c>
-      <c r="C140" t="s">
+      <c r="C145" t="s">
         <v>128</v>
       </c>
-      <c r="D140" t="s">
+      <c r="D145" t="s">
         <v>126</v>
       </c>
-      <c r="E140" t="s">
+      <c r="E145" t="s">
         <v>123</v>
       </c>
-      <c r="F140">
+      <c r="F145">
         <v>0.101743</v>
       </c>
-      <c r="G140" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A141">
+      <c r="G145" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146">
         <v>900</v>
       </c>
-      <c r="B141" t="str">
+      <c r="B146" t="str">
         <f t="shared" si="2"/>
         <v>900</v>
       </c>
-      <c r="C141" t="s">
+      <c r="C146" t="s">
         <v>129</v>
       </c>
-      <c r="D141">
+      <c r="D146">
         <v>9</v>
       </c>
-      <c r="E141" t="s">
+      <c r="E146" t="s">
         <v>130</v>
       </c>
-      <c r="F141">
+      <c r="F146">
         <v>0.1</v>
       </c>
-      <c r="G141" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A142">
+      <c r="G146" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147">
         <v>913</v>
       </c>
-      <c r="B142" t="str">
+      <c r="B147" t="str">
         <f t="shared" si="2"/>
         <v>913</v>
       </c>
-      <c r="C142" t="s">
+      <c r="C147" t="s">
         <v>131</v>
       </c>
-      <c r="D142">
+      <c r="D147">
         <v>9</v>
       </c>
-      <c r="E142" t="s">
+      <c r="E147" t="s">
         <v>130</v>
       </c>
-      <c r="F142">
+      <c r="F147">
         <v>0.1</v>
       </c>
-      <c r="G142" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A143">
+      <c r="G147" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148">
         <v>914</v>
       </c>
-      <c r="B143" t="str">
+      <c r="B148" t="str">
         <f t="shared" si="2"/>
         <v>914</v>
       </c>
-      <c r="C143" t="s">
+      <c r="C148" t="s">
         <v>132</v>
       </c>
-      <c r="D143">
+      <c r="D148">
         <v>9</v>
       </c>
-      <c r="E143" t="s">
+      <c r="E148" t="s">
         <v>130</v>
       </c>
-      <c r="F143">
+      <c r="F148">
         <v>0.1</v>
       </c>
-      <c r="G143" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A144">
+      <c r="G148" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149">
         <v>915</v>
       </c>
-      <c r="B144" t="str">
+      <c r="B149" t="str">
         <f t="shared" si="2"/>
         <v>915</v>
       </c>
-      <c r="C144" t="s">
+      <c r="C149" t="s">
         <v>133</v>
       </c>
-      <c r="D144">
+      <c r="D149">
         <v>9</v>
       </c>
-      <c r="E144" t="s">
+      <c r="E149" t="s">
         <v>130</v>
       </c>
-      <c r="F144">
+      <c r="F149">
         <v>0.1</v>
       </c>
-      <c r="G144" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A145">
+      <c r="G149" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A150">
         <v>918</v>
       </c>
-      <c r="B145" t="str">
+      <c r="B150" t="str">
         <f t="shared" si="2"/>
         <v>918</v>
       </c>
-      <c r="C145" t="s">
+      <c r="C150" t="s">
         <v>134</v>
       </c>
-      <c r="D145">
+      <c r="D150">
         <v>9</v>
       </c>
-      <c r="E145" t="s">
+      <c r="E150" t="s">
         <v>130</v>
       </c>
-      <c r="F145">
+      <c r="F150">
         <v>0.1</v>
       </c>
-      <c r="G145" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A146">
+      <c r="G150" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A151">
         <v>919</v>
       </c>
-      <c r="B146" t="str">
+      <c r="B151" t="str">
         <f t="shared" si="2"/>
         <v>919</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C151" t="s">
         <v>135</v>
       </c>
-      <c r="D146">
+      <c r="D151">
         <v>9</v>
       </c>
-      <c r="E146" t="s">
+      <c r="E151" t="s">
         <v>130</v>
       </c>
-      <c r="F146">
+      <c r="F151">
         <v>0.1</v>
       </c>
-      <c r="G146" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A147">
+      <c r="G151" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A152">
         <v>990</v>
       </c>
-      <c r="B147" t="str">
+      <c r="B152" t="str">
         <f t="shared" si="2"/>
         <v>990</v>
       </c>
-      <c r="C147" t="s">
+      <c r="C152" t="s">
         <v>136</v>
       </c>
-      <c r="D147">
+      <c r="D152">
         <v>9</v>
       </c>
-      <c r="E147" t="s">
+      <c r="E152" t="s">
         <v>130</v>
       </c>
-      <c r="F147">
+      <c r="F152">
         <v>0.1</v>
       </c>
-      <c r="G147" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A148">
+      <c r="G152" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A153">
         <v>991</v>
       </c>
-      <c r="B148" t="str">
+      <c r="B153" t="str">
         <f t="shared" si="2"/>
         <v>991</v>
       </c>
-      <c r="C148" t="s">
+      <c r="C153" t="s">
         <v>137</v>
       </c>
-      <c r="D148">
+      <c r="D153">
         <v>9</v>
       </c>
-      <c r="E148" t="s">
+      <c r="E153" t="s">
         <v>130</v>
       </c>
-      <c r="F148">
+      <c r="F153">
         <v>0.1</v>
       </c>
-      <c r="G148" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A149">
+      <c r="G153" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A154">
         <v>996</v>
       </c>
-      <c r="B149" t="str">
+      <c r="B154" t="str">
         <f t="shared" si="2"/>
         <v>996</v>
       </c>
-      <c r="C149" t="s">
+      <c r="C154" t="s">
         <v>46</v>
       </c>
-      <c r="D149">
+      <c r="D154">
         <v>9</v>
       </c>
-      <c r="E149" t="s">
+      <c r="E154" t="s">
         <v>130</v>
       </c>
-      <c r="F149">
+      <c r="F154">
         <v>0.1</v>
       </c>
-      <c r="G149" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A150">
+      <c r="G154" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A155">
         <v>997</v>
       </c>
-      <c r="B150" t="str">
+      <c r="B155" t="str">
         <f t="shared" si="2"/>
         <v>997</v>
       </c>
-      <c r="C150" t="s">
+      <c r="C155" t="s">
         <v>47</v>
       </c>
-      <c r="D150">
+      <c r="D155">
         <v>9</v>
       </c>
-      <c r="E150" t="s">
+      <c r="E155" t="s">
         <v>130</v>
       </c>
-      <c r="F150">
+      <c r="F155">
         <v>0.1</v>
       </c>
-      <c r="G150" t="s">
+      <c r="G155" t="s">
         <v>145</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G150" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G155" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -5145,12 +5274,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="48.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>310</v>
       </c>
@@ -5161,7 +5290,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>180</v>
       </c>
@@ -5172,7 +5301,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>182</v>
       </c>
@@ -5183,7 +5312,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>184</v>
       </c>
@@ -5194,7 +5323,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>185</v>
       </c>
@@ -5205,7 +5334,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>187</v>
       </c>
@@ -5216,7 +5345,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>189</v>
       </c>
@@ -5227,7 +5356,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>190</v>
       </c>
@@ -5238,7 +5367,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>191</v>
       </c>
@@ -5249,7 +5378,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>193</v>
       </c>
@@ -5260,7 +5389,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>195</v>
       </c>
@@ -5271,7 +5400,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>197</v>
       </c>
@@ -5282,7 +5411,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>199</v>
       </c>
@@ -5293,7 +5422,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>201</v>
       </c>
@@ -5304,7 +5433,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>202</v>
       </c>
@@ -5315,7 +5444,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>204</v>
       </c>
@@ -5326,7 +5455,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>206</v>
       </c>
@@ -5345,9 +5474,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>176</v>
       </c>
@@ -5355,7 +5484,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>138</v>
       </c>
@@ -5363,7 +5492,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>140</v>
       </c>
@@ -5371,7 +5500,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>141</v>
       </c>
@@ -5379,7 +5508,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>143</v>
       </c>
@@ -5387,7 +5516,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>144</v>
       </c>
@@ -5395,7 +5524,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>146</v>
       </c>
@@ -5403,7 +5532,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>147</v>
       </c>
@@ -5411,7 +5540,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>148</v>
       </c>
@@ -5419,7 +5548,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>149</v>
       </c>
@@ -5427,7 +5556,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>150</v>
       </c>
@@ -5435,7 +5564,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>152</v>
       </c>
@@ -5443,7 +5572,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>153</v>
       </c>
@@ -5451,7 +5580,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>154</v>
       </c>
@@ -5459,7 +5588,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>155</v>
       </c>
@@ -5467,7 +5596,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>156</v>
       </c>
@@ -5475,7 +5604,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>158</v>
       </c>
@@ -5483,7 +5612,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>159</v>
       </c>
@@ -5491,7 +5620,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>161</v>
       </c>
@@ -5499,7 +5628,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>162</v>
       </c>
@@ -5507,7 +5636,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>164</v>
       </c>
@@ -5515,7 +5644,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>166</v>
       </c>
@@ -5523,7 +5652,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>167</v>
       </c>
@@ -5531,7 +5660,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>168</v>
       </c>
@@ -5539,7 +5668,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>169</v>
       </c>
@@ -5547,7 +5676,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>170</v>
       </c>
@@ -5555,7 +5684,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>171</v>
       </c>
@@ -5563,7 +5692,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>172</v>
       </c>
@@ -5571,7 +5700,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>173</v>
       </c>
@@ -5579,7 +5708,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>174</v>
       </c>
@@ -5587,7 +5716,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>175</v>
       </c>
@@ -5603,13 +5732,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>310</v>
       </c>
@@ -5620,7 +5749,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>138</v>
       </c>
@@ -5631,7 +5760,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>140</v>
       </c>
@@ -5642,7 +5771,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>141</v>
       </c>
@@ -5653,7 +5782,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>144</v>
       </c>
@@ -5664,7 +5793,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>146</v>
       </c>
@@ -5675,7 +5804,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>147</v>
       </c>
@@ -5686,7 +5815,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>148</v>
       </c>
@@ -5697,7 +5826,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>149</v>
       </c>
@@ -5708,7 +5837,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>150</v>
       </c>
@@ -5719,7 +5848,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>152</v>
       </c>
@@ -5730,7 +5859,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>153</v>
       </c>
@@ -5741,7 +5870,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>154</v>
       </c>
@@ -5752,7 +5881,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>156</v>
       </c>
@@ -5763,7 +5892,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>221</v>
       </c>
@@ -5774,7 +5903,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>158</v>
       </c>
@@ -5785,7 +5914,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>224</v>
       </c>
@@ -5796,7 +5925,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>226</v>
       </c>
@@ -5807,7 +5936,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>159</v>
       </c>
@@ -5818,7 +5947,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>230</v>
       </c>
@@ -5837,12 +5966,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>310</v>
       </c>
@@ -5853,7 +5982,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>102</v>
       </c>
@@ -5864,7 +5993,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>103</v>
       </c>
@@ -5875,7 +6004,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>104</v>
       </c>
@@ -5886,7 +6015,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>105</v>
       </c>
@@ -5897,7 +6026,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>106</v>
       </c>
@@ -5908,7 +6037,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>118</v>
       </c>
@@ -5919,7 +6048,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>119</v>
       </c>
@@ -5930,7 +6059,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>120</v>
       </c>
@@ -5941,7 +6070,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>181</v>
       </c>
@@ -5952,7 +6081,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>191</v>
       </c>
@@ -5963,7 +6092,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>314</v>
       </c>
@@ -5974,7 +6103,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>317</v>
       </c>
@@ -5985,7 +6114,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>320</v>
       </c>
@@ -5996,7 +6125,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>321</v>
       </c>
@@ -6007,7 +6136,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>328</v>
       </c>
@@ -6018,7 +6147,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>401</v>
       </c>
@@ -6029,7 +6158,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>402</v>
       </c>
@@ -6040,7 +6169,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>403</v>
       </c>
@@ -6051,7 +6180,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>415</v>
       </c>
@@ -6062,7 +6191,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>610</v>
       </c>
@@ -6073,7 +6202,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>999</v>
       </c>
@@ -6092,12 +6221,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>339</v>
       </c>
@@ -6108,7 +6237,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
         <f>LEFT(B2,2)</f>
         <v>11</v>
@@ -6120,7 +6249,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f t="shared" ref="A3:A23" si="0">LEFT(B3,2)</f>
         <v>12</v>
@@ -6132,7 +6261,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -6144,7 +6273,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -6156,7 +6285,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -6168,7 +6297,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -6180,7 +6309,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -6192,7 +6321,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -6204,7 +6333,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -6216,7 +6345,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -6228,7 +6357,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -6240,7 +6369,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="str">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -6252,7 +6381,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="str">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -6264,7 +6393,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -6276,7 +6405,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -6288,7 +6417,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -6300,7 +6429,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f t="shared" si="0"/>
         <v>80</v>
@@ -6312,7 +6441,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f t="shared" si="0"/>
         <v>81</v>
@@ -6324,7 +6453,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f t="shared" si="0"/>
         <v>82</v>
@@ -6336,7 +6465,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f t="shared" si="0"/>
         <v>83</v>
@@ -6348,7 +6477,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f t="shared" si="0"/>
         <v>90</v>
@@ -6360,7 +6489,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f t="shared" si="0"/>
         <v>MH</v>
@@ -6381,13 +6510,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>313</v>
       </c>
@@ -6407,7 +6536,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>138</v>
       </c>
@@ -6428,7 +6557,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>140</v>
       </c>
@@ -6449,7 +6578,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>257</v>
       </c>
@@ -6469,7 +6598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>141</v>
       </c>
@@ -6490,7 +6619,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>143</v>
       </c>
@@ -6510,7 +6639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>144</v>
       </c>
@@ -6531,7 +6660,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>146</v>
       </c>
@@ -6552,7 +6681,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>147</v>
       </c>
@@ -6573,7 +6702,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>148</v>
       </c>
@@ -6594,7 +6723,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>149</v>
       </c>
@@ -6615,7 +6744,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>150</v>
       </c>
@@ -6636,7 +6765,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>152</v>
       </c>
@@ -6657,7 +6786,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>153</v>
       </c>
@@ -6678,7 +6807,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>154</v>
       </c>
@@ -6699,7 +6828,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>155</v>
       </c>
@@ -6720,7 +6849,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>156</v>
       </c>
@@ -6741,7 +6870,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>158</v>
       </c>
@@ -6762,7 +6891,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>224</v>
       </c>
@@ -6783,7 +6912,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>159</v>
       </c>
@@ -6804,7 +6933,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>230</v>
       </c>
@@ -6825,7 +6954,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>292</v>
       </c>
@@ -6854,13 +6983,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="27.36328125" customWidth="1"/>
-    <col min="3" max="3" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>310</v>
       </c>
@@ -6871,7 +7000,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>184</v>
       </c>
@@ -6882,7 +7011,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>187</v>
       </c>
@@ -6893,7 +7022,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>189</v>
       </c>
@@ -6904,7 +7033,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>296</v>
       </c>
@@ -6915,7 +7044,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>298</v>
       </c>
@@ -6926,7 +7055,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>190</v>
       </c>
@@ -6937,7 +7066,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>300</v>
       </c>
@@ -6948,7 +7077,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>191</v>
       </c>
@@ -6959,7 +7088,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>195</v>
       </c>
@@ -6970,7 +7099,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>201</v>
       </c>
@@ -6981,7 +7110,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>206</v>
       </c>
@@ -6992,7 +7121,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>306</v>
       </c>
@@ -7003,7 +7132,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>308</v>
       </c>
@@ -7022,18 +7151,18 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB14423E-3B10-4144-B6F3-4B0EE1BD3C57}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="91.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="59.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="91.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D1" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>342</v>
       </c>
@@ -7047,7 +7176,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>345</v>
       </c>
@@ -7061,7 +7190,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="260.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="260.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>346</v>
       </c>
@@ -7075,7 +7204,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="146" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="146.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>347</v>
       </c>
@@ -7086,7 +7215,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>348</v>
       </c>
@@ -7094,7 +7223,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>349</v>
       </c>
@@ -7105,7 +7234,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>350</v>
       </c>

--- a/resources/property classes.xlsx
+++ b/resources/property classes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abahls\Documents\GitHub\effective_property_tax\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{007AB29C-F9F5-43F2-8C87-9EAAFE19135C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A65F53-C540-46B7-ADF7-E31C33F55B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cook" sheetId="1" r:id="rId1"/>
@@ -24,8 +24,8 @@
     <sheet name="Notes" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cook!$A$1:$G$155</definedName>
-    <definedName name="Export_Output_2" localSheetId="0">Cook!$A$1:$E$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cook!$A$1:$G$157</definedName>
+    <definedName name="Export_Output_2" localSheetId="0">Cook!$A$1:$E$141</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="370">
   <si>
     <t>overall_class</t>
   </si>
@@ -1157,6 +1157,9 @@
   </si>
   <si>
     <t>Commercial incentive land</t>
+  </si>
+  <si>
+    <t>Industrial Incentive Land</t>
   </si>
 </sst>
 </file>
@@ -1538,7 +1541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G155"/>
+  <dimension ref="A1:G157"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
@@ -3208,7 +3211,7 @@
         <v>527</v>
       </c>
       <c r="B70" t="str">
-        <f t="shared" ref="B70:B135" si="1">TEXT(A70,"000")</f>
+        <f t="shared" ref="B70:B137" si="1">TEXT(A70,"000")</f>
         <v>527</v>
       </c>
       <c r="C70" t="s">
@@ -3733,23 +3736,23 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B92" t="str">
         <f t="shared" si="1"/>
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="C92" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="D92" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E92" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F92">
-        <v>0.1</v>
+        <v>0.108333</v>
       </c>
       <c r="G92" t="s">
         <v>157</v>
@@ -3757,14 +3760,14 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B93" t="str">
         <f t="shared" si="1"/>
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C93" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D93" t="s">
         <v>97</v>
@@ -3781,23 +3784,23 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="B94" t="str">
         <f t="shared" si="1"/>
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="C94" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D94" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E94" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F94">
-        <v>0.108333</v>
+        <v>0.1</v>
       </c>
       <c r="G94" t="s">
         <v>157</v>
@@ -3805,23 +3808,23 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="B95" t="str">
         <f t="shared" si="1"/>
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="C95" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D95" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E95" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F95">
-        <v>0.1</v>
+        <v>0.108333</v>
       </c>
       <c r="G95" t="s">
         <v>157</v>
@@ -3829,23 +3832,23 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B96" t="str">
         <f t="shared" si="1"/>
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C96" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="D96" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E96" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F96">
-        <v>0.108333</v>
+        <v>0.1</v>
       </c>
       <c r="G96" t="s">
         <v>157</v>
@@ -3853,14 +3856,14 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B97" t="str">
         <f t="shared" si="1"/>
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C97" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="D97" t="s">
         <v>102</v>
@@ -3877,14 +3880,14 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B98" t="str">
         <f t="shared" si="1"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C98" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="D98" t="s">
         <v>102</v>
@@ -3901,14 +3904,14 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="B99" t="str">
         <f t="shared" si="1"/>
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="C99" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D99" t="s">
         <v>102</v>
@@ -3925,14 +3928,14 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B100" t="str">
         <f t="shared" si="1"/>
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C100" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D100" t="s">
         <v>102</v>
@@ -3949,23 +3952,23 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B101" t="str">
         <f t="shared" si="1"/>
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C101" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D101" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E101" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F101">
-        <v>0.2</v>
+        <v>0.108333</v>
       </c>
       <c r="G101" t="s">
         <v>157</v>
@@ -3973,14 +3976,14 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B102" t="str">
         <f t="shared" si="1"/>
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="C102" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D102" t="s">
         <v>106</v>
@@ -3997,14 +4000,14 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="B103" t="str">
         <f t="shared" si="1"/>
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="C103" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D103" t="s">
         <v>106</v>
@@ -4021,14 +4024,14 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="B104" t="str">
         <f t="shared" si="1"/>
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="C104" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D104" t="s">
         <v>106</v>
@@ -4045,38 +4048,38 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>717</v>
+        <v>693</v>
       </c>
       <c r="B105" t="str">
         <f t="shared" si="1"/>
-        <v>717</v>
+        <v>693</v>
       </c>
       <c r="C105" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="D105" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E105" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F105">
-        <v>0.101743</v>
+        <v>0.2</v>
       </c>
       <c r="G105" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="B106" t="str">
         <f t="shared" si="1"/>
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="C106" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D106" t="s">
         <v>109</v>
@@ -4093,14 +4096,14 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B107" t="str">
         <f t="shared" si="1"/>
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C107" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D107" t="s">
         <v>109</v>
@@ -4117,14 +4120,14 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="B108" t="str">
         <f t="shared" si="1"/>
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="C108" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="D108" t="s">
         <v>109</v>
@@ -4141,14 +4144,14 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B109" t="str">
         <f t="shared" si="1"/>
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C109" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D109" t="s">
         <v>109</v>
@@ -4165,14 +4168,14 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B110" t="str">
         <f t="shared" si="1"/>
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C110" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D110" t="s">
         <v>109</v>
@@ -4189,14 +4192,14 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B111" t="str">
         <f t="shared" si="1"/>
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C111" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D111" t="s">
         <v>109</v>
@@ -4213,20 +4216,20 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>746</v>
+        <v>731</v>
       </c>
       <c r="B112" t="str">
         <f t="shared" si="1"/>
-        <v>746</v>
+        <v>731</v>
       </c>
       <c r="C112" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="D112" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E112" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F112">
         <v>0.101743</v>
@@ -4237,14 +4240,14 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B113" t="str">
         <f t="shared" si="1"/>
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C113" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="D113" t="s">
         <v>114</v>
@@ -4261,14 +4264,14 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B114" t="str">
         <f t="shared" si="1"/>
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="C114" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="D114" t="s">
         <v>114</v>
@@ -4285,14 +4288,14 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>760</v>
+        <v>752</v>
       </c>
       <c r="B115" t="str">
         <f t="shared" si="1"/>
-        <v>760</v>
+        <v>752</v>
       </c>
       <c r="C115" t="s">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="D115" t="s">
         <v>114</v>
@@ -4309,14 +4312,14 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="B116" t="str">
         <f t="shared" si="1"/>
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="C116" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="D116" t="s">
         <v>114</v>
@@ -4333,14 +4336,14 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="B117" t="str">
         <f t="shared" si="1"/>
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C117" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="D117" t="s">
         <v>114</v>
@@ -4357,14 +4360,14 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="B118" t="str">
         <f t="shared" si="1"/>
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="C118" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="D118" t="s">
         <v>114</v>
@@ -4381,20 +4384,20 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>790</v>
+        <v>774</v>
       </c>
       <c r="B119" t="str">
         <f t="shared" si="1"/>
-        <v>790</v>
+        <v>774</v>
       </c>
       <c r="C119" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D119" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E119" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F119">
         <v>0.101743</v>
@@ -4405,14 +4408,14 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B120" t="str">
         <f t="shared" si="1"/>
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C120" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D120" t="s">
         <v>109</v>
@@ -4429,14 +4432,14 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B121" t="str">
         <f t="shared" si="1"/>
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C121" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="D121" t="s">
         <v>109</v>
@@ -4453,14 +4456,14 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="B122" t="str">
         <f t="shared" si="1"/>
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="C122" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D122" t="s">
         <v>109</v>
@@ -4477,14 +4480,14 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B123" t="str">
         <f t="shared" si="1"/>
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C123" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="D123" t="s">
         <v>109</v>
@@ -4501,20 +4504,20 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B124" t="str">
         <f t="shared" si="1"/>
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="C124" t="s">
-        <v>368</v>
+        <v>120</v>
       </c>
       <c r="D124" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="E124" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="F124">
         <v>0.101743</v>
@@ -4525,14 +4528,14 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B125" t="str">
         <f t="shared" si="1"/>
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C125" t="s">
-        <v>121</v>
+        <v>368</v>
       </c>
       <c r="D125" t="s">
         <v>122</v>
@@ -4549,14 +4552,14 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>817</v>
+        <v>801</v>
       </c>
       <c r="B126" t="str">
         <f t="shared" si="1"/>
-        <v>817</v>
+        <v>801</v>
       </c>
       <c r="C126" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="D126" t="s">
         <v>122</v>
@@ -4573,14 +4576,14 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="B127" t="str">
         <f t="shared" si="1"/>
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="C127" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="D127" t="s">
         <v>122</v>
@@ -4597,11 +4600,14 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="B128" t="str">
         <f t="shared" si="1"/>
-        <v>826</v>
+        <v>823</v>
+      </c>
+      <c r="C128" t="s">
+        <v>124</v>
       </c>
       <c r="D128" t="s">
         <v>122</v>
@@ -4618,14 +4624,11 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B129" t="str">
         <f t="shared" si="1"/>
-        <v>827</v>
-      </c>
-      <c r="C129" t="s">
-        <v>74</v>
+        <v>826</v>
       </c>
       <c r="D129" t="s">
         <v>122</v>
@@ -4642,14 +4645,14 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B130" t="str">
         <f t="shared" si="1"/>
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C130" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D130" t="s">
         <v>122</v>
@@ -4666,14 +4669,14 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B131" t="str">
         <f t="shared" si="1"/>
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C131" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D131" t="s">
         <v>122</v>
@@ -4690,14 +4693,14 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B132" t="str">
         <f t="shared" si="1"/>
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C132" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D132" t="s">
         <v>122</v>
@@ -4714,14 +4717,14 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B133" t="str">
         <f t="shared" si="1"/>
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C133" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="D133" t="s">
         <v>122</v>
@@ -4738,14 +4741,14 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="B134" t="str">
         <f t="shared" si="1"/>
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C134" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="D134" t="s">
         <v>122</v>
@@ -4762,17 +4765,17 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>880</v>
+        <v>833</v>
       </c>
       <c r="B135" t="str">
         <f t="shared" si="1"/>
-        <v>880</v>
+        <v>833</v>
       </c>
       <c r="C135" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D135" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E135" t="s">
         <v>123</v>
@@ -4781,22 +4784,19 @@
         <v>0.101743</v>
       </c>
       <c r="G135" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>881</v>
+        <v>850</v>
       </c>
       <c r="B136" t="str">
-        <f t="shared" ref="B136:B155" si="2">TEXT(A136,"000")</f>
-        <v>881</v>
+        <f t="shared" si="1"/>
+        <v>850</v>
       </c>
       <c r="C136" t="s">
-        <v>105</v>
-      </c>
-      <c r="D136" t="s">
-        <v>126</v>
+        <v>369</v>
       </c>
       <c r="E136" t="s">
         <v>123</v>
@@ -4810,462 +4810,510 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137">
+        <v>880</v>
+      </c>
+      <c r="B137" t="str">
+        <f t="shared" si="1"/>
+        <v>880</v>
+      </c>
+      <c r="C137" t="s">
+        <v>85</v>
+      </c>
+      <c r="D137" t="s">
+        <v>126</v>
+      </c>
+      <c r="E137" t="s">
+        <v>123</v>
+      </c>
+      <c r="F137">
+        <v>0.101743</v>
+      </c>
+      <c r="G137" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>881</v>
+      </c>
+      <c r="B138" t="str">
+        <f t="shared" ref="B138:B157" si="2">TEXT(A138,"000")</f>
+        <v>881</v>
+      </c>
+      <c r="C138" t="s">
+        <v>105</v>
+      </c>
+      <c r="D138" t="s">
+        <v>126</v>
+      </c>
+      <c r="E138" t="s">
+        <v>123</v>
+      </c>
+      <c r="F138">
+        <v>0.101743</v>
+      </c>
+      <c r="G138" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A139">
         <v>883</v>
       </c>
-      <c r="B137" t="str">
+      <c r="B139" t="str">
         <f t="shared" si="2"/>
         <v>883</v>
       </c>
-      <c r="C137" t="s">
+      <c r="C139" t="s">
         <v>80</v>
       </c>
-      <c r="D137" t="s">
+      <c r="D139" t="s">
         <v>126</v>
       </c>
-      <c r="E137" t="s">
+      <c r="E139" t="s">
         <v>123</v>
       </c>
-      <c r="F137">
+      <c r="F139">
         <v>0.101743</v>
       </c>
-      <c r="G137" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A138">
+      <c r="G139" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A140">
         <v>887</v>
       </c>
-      <c r="B138" t="str">
+      <c r="B140" t="str">
         <f t="shared" si="2"/>
         <v>887</v>
       </c>
-      <c r="C138" t="s">
+      <c r="C140" t="s">
         <v>88</v>
       </c>
-      <c r="D138" t="s">
+      <c r="D140" t="s">
         <v>126</v>
       </c>
-      <c r="E138" t="s">
+      <c r="E140" t="s">
         <v>123</v>
       </c>
-      <c r="F138">
+      <c r="F140">
         <v>0.101743</v>
       </c>
-      <c r="G138" t="s">
+      <c r="G140" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A139">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A141">
         <v>889</v>
       </c>
-      <c r="B139" t="str">
+      <c r="B141" t="str">
         <f t="shared" si="2"/>
         <v>889</v>
       </c>
-      <c r="C139" t="s">
+      <c r="C141" t="s">
         <v>89</v>
       </c>
-      <c r="D139" t="s">
+      <c r="D141" t="s">
         <v>126</v>
       </c>
-      <c r="E139" t="s">
+      <c r="E141" t="s">
         <v>123</v>
       </c>
-      <c r="F139">
+      <c r="F141">
         <v>0.101743</v>
       </c>
-      <c r="G139" t="s">
+      <c r="G141" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A140">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142">
         <v>890</v>
       </c>
-      <c r="B140" t="str">
+      <c r="B142" t="str">
         <f t="shared" si="2"/>
         <v>890</v>
       </c>
-      <c r="C140" t="s">
+      <c r="C142" t="s">
         <v>127</v>
       </c>
-      <c r="D140" t="s">
+      <c r="D142" t="s">
         <v>126</v>
       </c>
-      <c r="E140" t="s">
+      <c r="E142" t="s">
         <v>123</v>
       </c>
-      <c r="F140">
+      <c r="F142">
         <v>0.101743</v>
       </c>
-      <c r="G140" t="s">
+      <c r="G142" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A141">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143">
         <v>891</v>
       </c>
-      <c r="B141" t="str">
+      <c r="B143" t="str">
         <f t="shared" si="2"/>
         <v>891</v>
       </c>
-      <c r="C141" t="s">
+      <c r="C143" t="s">
         <v>117</v>
       </c>
-      <c r="D141" t="s">
+      <c r="D143" t="s">
         <v>122</v>
       </c>
-      <c r="E141" t="s">
+      <c r="E143" t="s">
         <v>123</v>
       </c>
-      <c r="F141">
+      <c r="F143">
         <v>0.101743</v>
       </c>
-      <c r="G141" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A142">
+      <c r="G143" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144">
         <v>892</v>
       </c>
-      <c r="B142" t="str">
+      <c r="B144" t="str">
         <f t="shared" si="2"/>
         <v>892</v>
       </c>
-      <c r="C142" t="s">
+      <c r="C144" t="s">
         <v>92</v>
       </c>
-      <c r="D142" t="s">
+      <c r="D144" t="s">
         <v>122</v>
       </c>
-      <c r="E142" t="s">
+      <c r="E144" t="s">
         <v>123</v>
       </c>
-      <c r="F142">
+      <c r="F144">
         <v>0.101743</v>
       </c>
-      <c r="G142" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A143">
+      <c r="G144" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145">
         <v>893</v>
       </c>
-      <c r="B143" t="str">
+      <c r="B145" t="str">
         <f t="shared" si="2"/>
         <v>893</v>
       </c>
-      <c r="C143" t="s">
+      <c r="C145" t="s">
         <v>93</v>
       </c>
-      <c r="D143" t="s">
+      <c r="D145" t="s">
         <v>126</v>
       </c>
-      <c r="E143" t="s">
+      <c r="E145" t="s">
         <v>123</v>
       </c>
-      <c r="F143">
+      <c r="F145">
         <v>0.101743</v>
       </c>
-      <c r="G143" t="s">
+      <c r="G145" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A144">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146">
         <v>897</v>
       </c>
-      <c r="B144" t="str">
+      <c r="B146" t="str">
         <f t="shared" si="2"/>
         <v>897</v>
       </c>
-      <c r="C144" t="s">
+      <c r="C146" t="s">
         <v>94</v>
       </c>
-      <c r="D144" t="s">
+      <c r="D146" t="s">
         <v>122</v>
       </c>
-      <c r="E144" t="s">
+      <c r="E146" t="s">
         <v>123</v>
       </c>
-      <c r="F144">
+      <c r="F146">
         <v>0.101743</v>
       </c>
-      <c r="G144" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A145">
+      <c r="G146" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147">
         <v>899</v>
       </c>
-      <c r="B145" t="str">
+      <c r="B147" t="str">
         <f t="shared" si="2"/>
         <v>899</v>
       </c>
-      <c r="C145" t="s">
+      <c r="C147" t="s">
         <v>128</v>
       </c>
-      <c r="D145" t="s">
+      <c r="D147" t="s">
         <v>126</v>
       </c>
-      <c r="E145" t="s">
+      <c r="E147" t="s">
         <v>123</v>
       </c>
-      <c r="F145">
+      <c r="F147">
         <v>0.101743</v>
       </c>
-      <c r="G145" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A146">
+      <c r="G147" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148">
         <v>900</v>
       </c>
-      <c r="B146" t="str">
+      <c r="B148" t="str">
         <f t="shared" si="2"/>
         <v>900</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C148" t="s">
         <v>129</v>
       </c>
-      <c r="D146">
+      <c r="D148">
         <v>9</v>
       </c>
-      <c r="E146" t="s">
+      <c r="E148" t="s">
         <v>130</v>
       </c>
-      <c r="F146">
+      <c r="F148">
         <v>0.1</v>
       </c>
-      <c r="G146" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A147">
+      <c r="G148" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149">
         <v>913</v>
       </c>
-      <c r="B147" t="str">
+      <c r="B149" t="str">
         <f t="shared" si="2"/>
         <v>913</v>
       </c>
-      <c r="C147" t="s">
+      <c r="C149" t="s">
         <v>131</v>
       </c>
-      <c r="D147">
+      <c r="D149">
         <v>9</v>
       </c>
-      <c r="E147" t="s">
+      <c r="E149" t="s">
         <v>130</v>
       </c>
-      <c r="F147">
+      <c r="F149">
         <v>0.1</v>
       </c>
-      <c r="G147" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A148">
+      <c r="G149" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A150">
         <v>914</v>
       </c>
-      <c r="B148" t="str">
+      <c r="B150" t="str">
         <f t="shared" si="2"/>
         <v>914</v>
       </c>
-      <c r="C148" t="s">
+      <c r="C150" t="s">
         <v>132</v>
       </c>
-      <c r="D148">
+      <c r="D150">
         <v>9</v>
       </c>
-      <c r="E148" t="s">
+      <c r="E150" t="s">
         <v>130</v>
       </c>
-      <c r="F148">
+      <c r="F150">
         <v>0.1</v>
       </c>
-      <c r="G148" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A149">
+      <c r="G150" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A151">
         <v>915</v>
       </c>
-      <c r="B149" t="str">
+      <c r="B151" t="str">
         <f t="shared" si="2"/>
         <v>915</v>
       </c>
-      <c r="C149" t="s">
+      <c r="C151" t="s">
         <v>133</v>
       </c>
-      <c r="D149">
+      <c r="D151">
         <v>9</v>
       </c>
-      <c r="E149" t="s">
+      <c r="E151" t="s">
         <v>130</v>
       </c>
-      <c r="F149">
+      <c r="F151">
         <v>0.1</v>
       </c>
-      <c r="G149" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A150">
+      <c r="G151" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A152">
         <v>918</v>
       </c>
-      <c r="B150" t="str">
+      <c r="B152" t="str">
         <f t="shared" si="2"/>
         <v>918</v>
       </c>
-      <c r="C150" t="s">
+      <c r="C152" t="s">
         <v>134</v>
       </c>
-      <c r="D150">
+      <c r="D152">
         <v>9</v>
       </c>
-      <c r="E150" t="s">
+      <c r="E152" t="s">
         <v>130</v>
       </c>
-      <c r="F150">
+      <c r="F152">
         <v>0.1</v>
       </c>
-      <c r="G150" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A151">
+      <c r="G152" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A153">
         <v>919</v>
       </c>
-      <c r="B151" t="str">
+      <c r="B153" t="str">
         <f t="shared" si="2"/>
         <v>919</v>
       </c>
-      <c r="C151" t="s">
+      <c r="C153" t="s">
         <v>135</v>
       </c>
-      <c r="D151">
+      <c r="D153">
         <v>9</v>
       </c>
-      <c r="E151" t="s">
+      <c r="E153" t="s">
         <v>130</v>
       </c>
-      <c r="F151">
+      <c r="F153">
         <v>0.1</v>
       </c>
-      <c r="G151" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A152">
+      <c r="G153" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A154">
         <v>990</v>
       </c>
-      <c r="B152" t="str">
+      <c r="B154" t="str">
         <f t="shared" si="2"/>
         <v>990</v>
       </c>
-      <c r="C152" t="s">
+      <c r="C154" t="s">
         <v>136</v>
       </c>
-      <c r="D152">
+      <c r="D154">
         <v>9</v>
       </c>
-      <c r="E152" t="s">
+      <c r="E154" t="s">
         <v>130</v>
       </c>
-      <c r="F152">
+      <c r="F154">
         <v>0.1</v>
       </c>
-      <c r="G152" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A153">
+      <c r="G154" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A155">
         <v>991</v>
       </c>
-      <c r="B153" t="str">
+      <c r="B155" t="str">
         <f t="shared" si="2"/>
         <v>991</v>
       </c>
-      <c r="C153" t="s">
+      <c r="C155" t="s">
         <v>137</v>
       </c>
-      <c r="D153">
+      <c r="D155">
         <v>9</v>
       </c>
-      <c r="E153" t="s">
+      <c r="E155" t="s">
         <v>130</v>
       </c>
-      <c r="F153">
+      <c r="F155">
         <v>0.1</v>
       </c>
-      <c r="G153" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A154">
+      <c r="G155" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A156">
         <v>996</v>
       </c>
-      <c r="B154" t="str">
+      <c r="B156" t="str">
         <f t="shared" si="2"/>
         <v>996</v>
       </c>
-      <c r="C154" t="s">
+      <c r="C156" t="s">
         <v>46</v>
       </c>
-      <c r="D154">
+      <c r="D156">
         <v>9</v>
       </c>
-      <c r="E154" t="s">
+      <c r="E156" t="s">
         <v>130</v>
       </c>
-      <c r="F154">
+      <c r="F156">
         <v>0.1</v>
       </c>
-      <c r="G154" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A155">
+      <c r="G156" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A157">
         <v>997</v>
       </c>
-      <c r="B155" t="str">
+      <c r="B157" t="str">
         <f t="shared" si="2"/>
         <v>997</v>
       </c>
-      <c r="C155" t="s">
+      <c r="C157" t="s">
         <v>47</v>
       </c>
-      <c r="D155">
+      <c r="D157">
         <v>9</v>
       </c>
-      <c r="E155" t="s">
+      <c r="E157" t="s">
         <v>130</v>
       </c>
-      <c r="F155">
+      <c r="F157">
         <v>0.1</v>
       </c>
-      <c r="G155" t="s">
+      <c r="G157" t="s">
         <v>145</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G155" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G157" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
